--- a/donnees_exemple.xlsx
+++ b/donnees_exemple.xlsx
@@ -24,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -88,8 +88,21 @@
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -109,6 +122,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -171,7 +194,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -205,6 +228,18 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -731,13 +766,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1120,22 +1155,68 @@
       <c r="D29" s="7" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="7" t="n"/>
-      <c r="B30" s="7" t="n"/>
-      <c r="C30" s="7" t="n"/>
-      <c r="D30" s="7" t="n"/>
+      <c r="A30" s="18" t="inlineStr">
+        <is>
+          <t>RÈGLES PARTICULIÈRES</t>
+        </is>
+      </c>
+      <c r="B30" s="19" t="n"/>
+      <c r="C30" s="19" t="n"/>
+      <c r="D30" s="19" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="7" t="n"/>
+      <c r="A31" s="20" t="inlineStr">
+        <is>
+          <t>Réglages optionnels. Laissez « Oui » pour appliquer la règle, « Non » pour l'ignorer.</t>
+        </is>
+      </c>
       <c r="B31" s="7" t="n"/>
       <c r="C31" s="7" t="n"/>
       <c r="D31" s="7" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="7" t="n"/>
-      <c r="B32" s="7" t="n"/>
-      <c r="C32" s="7" t="n"/>
-      <c r="D32" s="7" t="n"/>
+      <c r="A32" s="21" t="inlineStr">
+        <is>
+          <t>Règle</t>
+        </is>
+      </c>
+      <c r="B32" s="21" t="inlineStr">
+        <is>
+          <t>Activée ?</t>
+        </is>
+      </c>
+      <c r="C32" s="21" t="inlineStr">
+        <is>
+          <t>Heure début</t>
+        </is>
+      </c>
+      <c r="D32" s="21" t="inlineStr">
+        <is>
+          <t>Heure fin</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="22" t="inlineStr">
+        <is>
+          <t>Pas d'EPS aux heures chaudes</t>
+        </is>
+      </c>
+      <c r="B33" s="23" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+      <c r="C33" s="23" t="inlineStr">
+        <is>
+          <t>12h00</t>
+        </is>
+      </c>
+      <c r="D33" s="23" t="inlineStr">
+        <is>
+          <t>15h00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/donnees_exemple.xlsx
+++ b/donnees_exemple.xlsx
@@ -24,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="14">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -101,8 +101,16 @@
       <b val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -132,6 +140,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004472C4"/>
       </patternFill>
     </fill>
   </fills>
@@ -194,7 +207,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -241,6 +254,8 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -766,7 +781,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1216,6 +1231,154 @@
         <is>
           <t>15h00</t>
         </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>DURÉE DES SÉANCES PAR MATIÈRE</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Optionnel. Durée d'une séance en heures consécutives. min = max → durée fixe. Matière absente → le moteur décide librement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="25" t="inlineStr">
+        <is>
+          <t>Matière</t>
+        </is>
+      </c>
+      <c r="B37" s="25" t="inlineStr">
+        <is>
+          <t>Durée min séance</t>
+        </is>
+      </c>
+      <c r="C37" s="25" t="inlineStr">
+        <is>
+          <t>Durée max séance</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Mathématiques</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Physique-Chimie</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>2</v>
+      </c>
+      <c r="C39" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>SVT</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>2</v>
+      </c>
+      <c r="C40" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Français</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Philosophie</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>2</v>
+      </c>
+      <c r="C43" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Histoire-Géographie</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Anglais</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Espagnol</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/donnees_exemple.xlsx
+++ b/donnees_exemple.xlsx
@@ -10,11 +10,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISEZ-MOI" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Paramètres" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Classes" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Salles spéciales" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Professeurs" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Services" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Disponibilités" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contraintes" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Professeurs" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Services" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Disponibilités" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contraintes" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2142,287 +2141,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>SALLES SPÉCIALES</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>Uniquement les salles particulières partagées entre plusieurs classes (laboratoires, salle informatique, terrain de sport…). Inutile de lister les salles de classe ordinaires.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="12" t="inlineStr">
-        <is>
-          <t>Nom de la salle</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="C3" s="12" t="inlineStr">
-        <is>
-          <t>Capacité</t>
-        </is>
-      </c>
-      <c r="D3" s="12" t="inlineStr">
-        <is>
-          <t>Remarques</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="16" t="inlineStr">
-        <is>
-          <t>Labo SVT</t>
-        </is>
-      </c>
-      <c r="B4" s="16" t="inlineStr">
-        <is>
-          <t>Laboratoire SVT</t>
-        </is>
-      </c>
-      <c r="C4" s="16" t="n">
-        <v>35</v>
-      </c>
-      <c r="D4" s="16" t="inlineStr">
-        <is>
-          <t>TP de SVT uniquement</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="16" t="inlineStr">
-        <is>
-          <t>Labo PC</t>
-        </is>
-      </c>
-      <c r="B5" s="16" t="inlineStr">
-        <is>
-          <t>Laboratoire Physique-Chimie</t>
-        </is>
-      </c>
-      <c r="C5" s="16" t="n">
-        <v>35</v>
-      </c>
-      <c r="D5" s="16" t="inlineStr">
-        <is>
-          <t>TP de Physique-Chimie</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="16" t="inlineStr">
-        <is>
-          <t>Salle Info</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>Salle informatique</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="n">
-        <v>30</v>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
-        <is>
-          <t>20 postes disponibles</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="16" t="inlineStr">
-        <is>
-          <t>Terrain EPS</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>Terrain EPS</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr"/>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>Terrain extérieur, indisponible quand il pleut fort</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="n"/>
-      <c r="B8" s="7" t="n"/>
-      <c r="C8" s="7" t="n"/>
-      <c r="D8" s="7" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="n"/>
-      <c r="B9" s="7" t="n"/>
-      <c r="C9" s="7" t="n"/>
-      <c r="D9" s="7" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="n"/>
-      <c r="B10" s="7" t="n"/>
-      <c r="C10" s="7" t="n"/>
-      <c r="D10" s="7" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="n"/>
-      <c r="B11" s="7" t="n"/>
-      <c r="C11" s="7" t="n"/>
-      <c r="D11" s="7" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="n"/>
-      <c r="B12" s="7" t="n"/>
-      <c r="C12" s="7" t="n"/>
-      <c r="D12" s="7" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="n"/>
-      <c r="B13" s="7" t="n"/>
-      <c r="C13" s="7" t="n"/>
-      <c r="D13" s="7" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="n"/>
-      <c r="B14" s="7" t="n"/>
-      <c r="C14" s="7" t="n"/>
-      <c r="D14" s="7" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="n"/>
-      <c r="B15" s="7" t="n"/>
-      <c r="C15" s="7" t="n"/>
-      <c r="D15" s="7" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="n"/>
-      <c r="B16" s="7" t="n"/>
-      <c r="C16" s="7" t="n"/>
-      <c r="D16" s="7" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="n"/>
-      <c r="B17" s="7" t="n"/>
-      <c r="C17" s="7" t="n"/>
-      <c r="D17" s="7" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="n"/>
-      <c r="B18" s="7" t="n"/>
-      <c r="C18" s="7" t="n"/>
-      <c r="D18" s="7" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="n"/>
-      <c r="B19" s="7" t="n"/>
-      <c r="C19" s="7" t="n"/>
-      <c r="D19" s="7" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="n"/>
-      <c r="B20" s="7" t="n"/>
-      <c r="C20" s="7" t="n"/>
-      <c r="D20" s="7" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="n"/>
-      <c r="B21" s="7" t="n"/>
-      <c r="C21" s="7" t="n"/>
-      <c r="D21" s="7" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="n"/>
-      <c r="B22" s="7" t="n"/>
-      <c r="C22" s="7" t="n"/>
-      <c r="D22" s="7" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="n"/>
-      <c r="B23" s="7" t="n"/>
-      <c r="C23" s="7" t="n"/>
-      <c r="D23" s="7" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="n"/>
-      <c r="B24" s="7" t="n"/>
-      <c r="C24" s="7" t="n"/>
-      <c r="D24" s="7" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="n"/>
-      <c r="B25" s="7" t="n"/>
-      <c r="C25" s="7" t="n"/>
-      <c r="D25" s="7" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="n"/>
-      <c r="B26" s="7" t="n"/>
-      <c r="C26" s="7" t="n"/>
-      <c r="D26" s="7" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="n"/>
-      <c r="B27" s="7" t="n"/>
-      <c r="C27" s="7" t="n"/>
-      <c r="D27" s="7" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="n"/>
-      <c r="B28" s="7" t="n"/>
-      <c r="C28" s="7" t="n"/>
-      <c r="D28" s="7" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="n"/>
-      <c r="B29" s="7" t="n"/>
-      <c r="C29" s="7" t="n"/>
-      <c r="D29" s="7" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="n"/>
-      <c r="B30" s="7" t="n"/>
-      <c r="C30" s="7" t="n"/>
-      <c r="D30" s="7" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-  </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="B4:B30" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Choisissez une valeur dans la liste" type="list">
-      <formula1>"Laboratoire SVT,Laboratoire Physique-Chimie,Salle informatique,Terrain EPS,Bibliothèque/CDI,Autre"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:F120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3712,13 +3430,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F400"/>
+  <dimension ref="A1:E400"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3766,11 +3484,6 @@
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>Taille du bloc (optionnel)</t>
-        </is>
-      </c>
-      <c r="F3" s="12" t="inlineStr">
-        <is>
           <t>Jour imposé (optionnel)</t>
         </is>
       </c>
@@ -3794,12 +3507,7 @@
       <c r="D4" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="E4" s="16" t="inlineStr">
-        <is>
-          <t>2h</t>
-        </is>
-      </c>
-      <c r="F4" s="16" t="inlineStr"/>
+      <c r="E4" s="16" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="16" t="inlineStr">
@@ -3820,12 +3528,7 @@
       <c r="D5" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="E5" s="16" t="inlineStr">
-        <is>
-          <t>2h</t>
-        </is>
-      </c>
-      <c r="F5" s="16" t="inlineStr"/>
+      <c r="E5" s="16" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="16" t="inlineStr">
@@ -3847,7 +3550,6 @@
         <v>3</v>
       </c>
       <c r="E6" s="16" t="inlineStr"/>
-      <c r="F6" s="16" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="16" t="inlineStr">
@@ -3869,7 +3571,6 @@
         <v>2</v>
       </c>
       <c r="E7" s="16" t="inlineStr"/>
-      <c r="F7" s="16" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="16" t="inlineStr">
@@ -3891,7 +3592,6 @@
         <v>1</v>
       </c>
       <c r="E8" s="16" t="inlineStr"/>
-      <c r="F8" s="16" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="16" t="inlineStr">
@@ -3913,7 +3613,6 @@
         <v>2</v>
       </c>
       <c r="E9" s="16" t="inlineStr"/>
-      <c r="F9" s="16" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="16" t="inlineStr">
@@ -3935,7 +3634,6 @@
         <v>2</v>
       </c>
       <c r="E10" s="16" t="inlineStr"/>
-      <c r="F10" s="16" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="16" t="inlineStr">
@@ -3958,11 +3656,6 @@
       </c>
       <c r="E11" s="16" t="inlineStr">
         <is>
-          <t>2h</t>
-        </is>
-      </c>
-      <c r="F11" s="16" t="inlineStr">
-        <is>
           <t>Vendredi</t>
         </is>
       </c>
@@ -3987,7 +3680,6 @@
         <v>1</v>
       </c>
       <c r="E12" s="16" t="inlineStr"/>
-      <c r="F12" s="16" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="16" t="inlineStr">
@@ -4009,7 +3701,6 @@
         <v>1</v>
       </c>
       <c r="E13" s="16" t="inlineStr"/>
-      <c r="F13" s="16" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="16" t="inlineStr">
@@ -4031,7 +3722,6 @@
         <v>1</v>
       </c>
       <c r="E14" s="16" t="inlineStr"/>
-      <c r="F14" s="16" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="16" t="inlineStr">
@@ -4052,12 +3742,7 @@
       <c r="D15" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="E15" s="16" t="inlineStr">
-        <is>
-          <t>2h</t>
-        </is>
-      </c>
-      <c r="F15" s="16" t="inlineStr"/>
+      <c r="E15" s="16" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="16" t="inlineStr">
@@ -4078,12 +3763,7 @@
       <c r="D16" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="E16" s="16" t="inlineStr">
-        <is>
-          <t>2h</t>
-        </is>
-      </c>
-      <c r="F16" s="16" t="inlineStr"/>
+      <c r="E16" s="16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="16" t="inlineStr">
@@ -4105,7 +3785,6 @@
         <v>3</v>
       </c>
       <c r="E17" s="16" t="inlineStr"/>
-      <c r="F17" s="16" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="16" t="inlineStr">
@@ -4127,7 +3806,6 @@
         <v>2</v>
       </c>
       <c r="E18" s="16" t="inlineStr"/>
-      <c r="F18" s="16" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="16" t="inlineStr">
@@ -4149,7 +3827,6 @@
         <v>1</v>
       </c>
       <c r="E19" s="16" t="inlineStr"/>
-      <c r="F19" s="16" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="16" t="inlineStr">
@@ -4171,7 +3848,6 @@
         <v>2</v>
       </c>
       <c r="E20" s="16" t="inlineStr"/>
-      <c r="F20" s="16" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="16" t="inlineStr">
@@ -4193,7 +3869,6 @@
         <v>2</v>
       </c>
       <c r="E21" s="16" t="inlineStr"/>
-      <c r="F21" s="16" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="16" t="inlineStr">
@@ -4214,12 +3889,7 @@
       <c r="D22" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="E22" s="16" t="inlineStr">
-        <is>
-          <t>2h</t>
-        </is>
-      </c>
-      <c r="F22" s="16" t="inlineStr"/>
+      <c r="E22" s="16" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="16" t="inlineStr">
@@ -4241,7 +3911,6 @@
         <v>1</v>
       </c>
       <c r="E23" s="16" t="inlineStr"/>
-      <c r="F23" s="16" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="16" t="inlineStr">
@@ -4263,7 +3932,6 @@
         <v>1</v>
       </c>
       <c r="E24" s="16" t="inlineStr"/>
-      <c r="F24" s="16" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="16" t="inlineStr">
@@ -4285,7 +3953,6 @@
         <v>1</v>
       </c>
       <c r="E25" s="16" t="inlineStr"/>
-      <c r="F25" s="16" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="16" t="inlineStr">
@@ -4306,12 +3973,7 @@
       <c r="D26" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="E26" s="16" t="inlineStr">
-        <is>
-          <t>2h</t>
-        </is>
-      </c>
-      <c r="F26" s="16" t="inlineStr"/>
+      <c r="E26" s="16" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="16" t="inlineStr">
@@ -4332,12 +3994,7 @@
       <c r="D27" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="E27" s="16" t="inlineStr">
-        <is>
-          <t>2h</t>
-        </is>
-      </c>
-      <c r="F27" s="16" t="inlineStr"/>
+      <c r="E27" s="16" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="16" t="inlineStr">
@@ -4359,7 +4016,6 @@
         <v>3</v>
       </c>
       <c r="E28" s="16" t="inlineStr"/>
-      <c r="F28" s="16" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="16" t="inlineStr">
@@ -4381,7 +4037,6 @@
         <v>2</v>
       </c>
       <c r="E29" s="16" t="inlineStr"/>
-      <c r="F29" s="16" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="16" t="inlineStr">
@@ -4403,7 +4058,6 @@
         <v>1</v>
       </c>
       <c r="E30" s="16" t="inlineStr"/>
-      <c r="F30" s="16" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="16" t="inlineStr">
@@ -4425,7 +4079,6 @@
         <v>2</v>
       </c>
       <c r="E31" s="16" t="inlineStr"/>
-      <c r="F31" s="16" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="16" t="inlineStr">
@@ -4447,7 +4100,6 @@
         <v>2</v>
       </c>
       <c r="E32" s="16" t="inlineStr"/>
-      <c r="F32" s="16" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="16" t="inlineStr">
@@ -4468,12 +4120,7 @@
       <c r="D33" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="E33" s="16" t="inlineStr">
-        <is>
-          <t>2h</t>
-        </is>
-      </c>
-      <c r="F33" s="16" t="inlineStr"/>
+      <c r="E33" s="16" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="16" t="inlineStr">
@@ -4495,7 +4142,6 @@
         <v>1</v>
       </c>
       <c r="E34" s="16" t="inlineStr"/>
-      <c r="F34" s="16" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="16" t="inlineStr">
@@ -4517,7 +4163,6 @@
         <v>1</v>
       </c>
       <c r="E35" s="16" t="inlineStr"/>
-      <c r="F35" s="16" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="16" t="inlineStr">
@@ -4539,7 +4184,6 @@
         <v>1</v>
       </c>
       <c r="E36" s="16" t="inlineStr"/>
-      <c r="F36" s="16" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="16" t="inlineStr">
@@ -4560,12 +4204,7 @@
       <c r="D37" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="E37" s="16" t="inlineStr">
-        <is>
-          <t>2h</t>
-        </is>
-      </c>
-      <c r="F37" s="16" t="inlineStr"/>
+      <c r="E37" s="16" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="16" t="inlineStr">
@@ -4586,12 +4225,7 @@
       <c r="D38" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="E38" s="16" t="inlineStr">
-        <is>
-          <t>2h</t>
-        </is>
-      </c>
-      <c r="F38" s="16" t="inlineStr"/>
+      <c r="E38" s="16" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="16" t="inlineStr">
@@ -4613,7 +4247,6 @@
         <v>3</v>
       </c>
       <c r="E39" s="16" t="inlineStr"/>
-      <c r="F39" s="16" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="16" t="inlineStr">
@@ -4635,7 +4268,6 @@
         <v>3</v>
       </c>
       <c r="E40" s="16" t="inlineStr"/>
-      <c r="F40" s="16" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="16" t="inlineStr">
@@ -4657,7 +4289,6 @@
         <v>1</v>
       </c>
       <c r="E41" s="16" t="inlineStr"/>
-      <c r="F41" s="16" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="16" t="inlineStr">
@@ -4678,12 +4309,7 @@
       <c r="D42" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="E42" s="16" t="inlineStr">
-        <is>
-          <t>2h</t>
-        </is>
-      </c>
-      <c r="F42" s="16" t="inlineStr"/>
+      <c r="E42" s="16" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="16" t="inlineStr">
@@ -4705,7 +4331,6 @@
         <v>2</v>
       </c>
       <c r="E43" s="16" t="inlineStr"/>
-      <c r="F43" s="16" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="16" t="inlineStr">
@@ -4726,12 +4351,7 @@
       <c r="D44" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="E44" s="16" t="inlineStr">
-        <is>
-          <t>2h</t>
-        </is>
-      </c>
-      <c r="F44" s="16" t="inlineStr"/>
+      <c r="E44" s="16" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="16" t="inlineStr">
@@ -4753,7 +4373,6 @@
         <v>2</v>
       </c>
       <c r="E45" s="16" t="inlineStr"/>
-      <c r="F45" s="16" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="16" t="inlineStr">
@@ -4775,7 +4394,6 @@
         <v>1</v>
       </c>
       <c r="E46" s="16" t="inlineStr"/>
-      <c r="F46" s="16" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="16" t="inlineStr">
@@ -4797,7 +4415,6 @@
         <v>1</v>
       </c>
       <c r="E47" s="16" t="inlineStr"/>
-      <c r="F47" s="16" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="16" t="inlineStr">
@@ -4819,7 +4436,6 @@
         <v>1</v>
       </c>
       <c r="E48" s="16" t="inlineStr"/>
-      <c r="F48" s="16" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="16" t="inlineStr">
@@ -4840,12 +4456,7 @@
       <c r="D49" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="E49" s="16" t="inlineStr">
-        <is>
-          <t>2h</t>
-        </is>
-      </c>
-      <c r="F49" s="16" t="inlineStr"/>
+      <c r="E49" s="16" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="16" t="inlineStr">
@@ -4866,12 +4477,7 @@
       <c r="D50" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="E50" s="16" t="inlineStr">
-        <is>
-          <t>2h</t>
-        </is>
-      </c>
-      <c r="F50" s="16" t="inlineStr"/>
+      <c r="E50" s="16" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="16" t="inlineStr">
@@ -4893,7 +4499,6 @@
         <v>3</v>
       </c>
       <c r="E51" s="16" t="inlineStr"/>
-      <c r="F51" s="16" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="16" t="inlineStr">
@@ -4915,7 +4520,6 @@
         <v>3</v>
       </c>
       <c r="E52" s="16" t="inlineStr"/>
-      <c r="F52" s="16" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="16" t="inlineStr">
@@ -4937,7 +4541,6 @@
         <v>1</v>
       </c>
       <c r="E53" s="16" t="inlineStr"/>
-      <c r="F53" s="16" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="16" t="inlineStr">
@@ -4958,12 +4561,7 @@
       <c r="D54" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="E54" s="16" t="inlineStr">
-        <is>
-          <t>2h</t>
-        </is>
-      </c>
-      <c r="F54" s="16" t="inlineStr"/>
+      <c r="E54" s="16" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="16" t="inlineStr">
@@ -4984,12 +4582,7 @@
       <c r="D55" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="E55" s="16" t="inlineStr">
-        <is>
-          <t>2h</t>
-        </is>
-      </c>
-      <c r="F55" s="16" t="inlineStr"/>
+      <c r="E55" s="16" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="16" t="inlineStr">
@@ -5010,12 +4603,7 @@
       <c r="D56" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="E56" s="16" t="inlineStr">
-        <is>
-          <t>2h</t>
-        </is>
-      </c>
-      <c r="F56" s="16" t="inlineStr"/>
+      <c r="E56" s="16" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="16" t="inlineStr">
@@ -5037,7 +4625,6 @@
         <v>2</v>
       </c>
       <c r="E57" s="16" t="inlineStr"/>
-      <c r="F57" s="16" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="16" t="inlineStr">
@@ -5059,7 +4646,6 @@
         <v>1</v>
       </c>
       <c r="E58" s="16" t="inlineStr"/>
-      <c r="F58" s="16" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="16" t="inlineStr">
@@ -5081,7 +4667,6 @@
         <v>1</v>
       </c>
       <c r="E59" s="16" t="inlineStr"/>
-      <c r="F59" s="16" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="16" t="inlineStr">
@@ -5103,7 +4688,6 @@
         <v>1</v>
       </c>
       <c r="E60" s="16" t="inlineStr"/>
-      <c r="F60" s="16" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="16" t="inlineStr">
@@ -5124,12 +4708,7 @@
       <c r="D61" s="16" t="n">
         <v>6</v>
       </c>
-      <c r="E61" s="16" t="inlineStr">
-        <is>
-          <t>2h</t>
-        </is>
-      </c>
-      <c r="F61" s="16" t="inlineStr"/>
+      <c r="E61" s="16" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="16" t="inlineStr">
@@ -5150,12 +4729,7 @@
       <c r="D62" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="E62" s="16" t="inlineStr">
-        <is>
-          <t>2h</t>
-        </is>
-      </c>
-      <c r="F62" s="16" t="inlineStr"/>
+      <c r="E62" s="16" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="16" t="inlineStr">
@@ -5177,7 +4751,6 @@
         <v>3</v>
       </c>
       <c r="E63" s="16" t="inlineStr"/>
-      <c r="F63" s="16" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="16" t="inlineStr">
@@ -5199,7 +4772,6 @@
         <v>2</v>
       </c>
       <c r="E64" s="16" t="inlineStr"/>
-      <c r="F64" s="16" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="16" t="inlineStr">
@@ -5220,12 +4792,7 @@
       <c r="D65" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="E65" s="16" t="inlineStr">
-        <is>
-          <t>2h</t>
-        </is>
-      </c>
-      <c r="F65" s="16" t="inlineStr"/>
+      <c r="E65" s="16" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="16" t="inlineStr">
@@ -5246,12 +4813,7 @@
       <c r="D66" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="E66" s="16" t="inlineStr">
-        <is>
-          <t>3h</t>
-        </is>
-      </c>
-      <c r="F66" s="16" t="inlineStr"/>
+      <c r="E66" s="16" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="16" t="inlineStr">
@@ -5272,12 +4834,7 @@
       <c r="D67" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="E67" s="16" t="inlineStr">
-        <is>
-          <t>2h</t>
-        </is>
-      </c>
-      <c r="F67" s="16" t="inlineStr"/>
+      <c r="E67" s="16" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="16" t="inlineStr">
@@ -5299,7 +4856,6 @@
         <v>2</v>
       </c>
       <c r="E68" s="16" t="inlineStr"/>
-      <c r="F68" s="16" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="16" t="inlineStr">
@@ -5321,7 +4877,6 @@
         <v>2</v>
       </c>
       <c r="E69" s="16" t="inlineStr"/>
-      <c r="F69" s="16" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="16" t="inlineStr">
@@ -5343,7 +4898,6 @@
         <v>1</v>
       </c>
       <c r="E70" s="16" t="inlineStr"/>
-      <c r="F70" s="16" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="16" t="inlineStr">
@@ -5364,12 +4918,7 @@
       <c r="D71" s="16" t="n">
         <v>6</v>
       </c>
-      <c r="E71" s="16" t="inlineStr">
-        <is>
-          <t>2h</t>
-        </is>
-      </c>
-      <c r="F71" s="16" t="inlineStr"/>
+      <c r="E71" s="16" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="16" t="inlineStr">
@@ -5390,12 +4939,7 @@
       <c r="D72" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="E72" s="16" t="inlineStr">
-        <is>
-          <t>2h</t>
-        </is>
-      </c>
-      <c r="F72" s="16" t="inlineStr"/>
+      <c r="E72" s="16" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="16" t="inlineStr">
@@ -5417,7 +4961,6 @@
         <v>3</v>
       </c>
       <c r="E73" s="16" t="inlineStr"/>
-      <c r="F73" s="16" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="16" t="inlineStr">
@@ -5439,7 +4982,6 @@
         <v>2</v>
       </c>
       <c r="E74" s="16" t="inlineStr"/>
-      <c r="F74" s="16" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="16" t="inlineStr">
@@ -5460,12 +5002,7 @@
       <c r="D75" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="E75" s="16" t="inlineStr">
-        <is>
-          <t>3h</t>
-        </is>
-      </c>
-      <c r="F75" s="16" t="inlineStr"/>
+      <c r="E75" s="16" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="16" t="inlineStr">
@@ -5486,12 +5023,7 @@
       <c r="D76" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="E76" s="16" t="inlineStr">
-        <is>
-          <t>3h</t>
-        </is>
-      </c>
-      <c r="F76" s="16" t="inlineStr"/>
+      <c r="E76" s="16" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="16" t="inlineStr">
@@ -5512,12 +5044,7 @@
       <c r="D77" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="E77" s="16" t="inlineStr">
-        <is>
-          <t>2h</t>
-        </is>
-      </c>
-      <c r="F77" s="16" t="inlineStr"/>
+      <c r="E77" s="16" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="16" t="inlineStr">
@@ -5539,7 +5066,6 @@
         <v>2</v>
       </c>
       <c r="E78" s="16" t="inlineStr"/>
-      <c r="F78" s="16" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="16" t="inlineStr">
@@ -5561,7 +5087,6 @@
         <v>3</v>
       </c>
       <c r="E79" s="16" t="inlineStr"/>
-      <c r="F79" s="16" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="16" t="inlineStr">
@@ -5582,12 +5107,7 @@
       <c r="D80" s="16" t="n">
         <v>6</v>
       </c>
-      <c r="E80" s="16" t="inlineStr">
-        <is>
-          <t>2h</t>
-        </is>
-      </c>
-      <c r="F80" s="16" t="inlineStr"/>
+      <c r="E80" s="16" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="16" t="inlineStr">
@@ -5609,7 +5129,6 @@
         <v>3</v>
       </c>
       <c r="E81" s="16" t="inlineStr"/>
-      <c r="F81" s="16" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="16" t="inlineStr">
@@ -5631,7 +5150,6 @@
         <v>3</v>
       </c>
       <c r="E82" s="16" t="inlineStr"/>
-      <c r="F82" s="16" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="16" t="inlineStr">
@@ -5653,7 +5171,6 @@
         <v>2</v>
       </c>
       <c r="E83" s="16" t="inlineStr"/>
-      <c r="F83" s="16" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="16" t="inlineStr">
@@ -5674,12 +5191,7 @@
       <c r="D84" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="E84" s="16" t="inlineStr">
-        <is>
-          <t>3h</t>
-        </is>
-      </c>
-      <c r="F84" s="16" t="inlineStr"/>
+      <c r="E84" s="16" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="16" t="inlineStr">
@@ -5702,11 +5214,6 @@
       </c>
       <c r="E85" s="16" t="inlineStr">
         <is>
-          <t>3h</t>
-        </is>
-      </c>
-      <c r="F85" s="16" t="inlineStr">
-        <is>
           <t>Mardi</t>
         </is>
       </c>
@@ -5730,12 +5237,7 @@
       <c r="D86" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="E86" s="16" t="inlineStr">
-        <is>
-          <t>2h</t>
-        </is>
-      </c>
-      <c r="F86" s="16" t="inlineStr"/>
+      <c r="E86" s="16" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="16" t="inlineStr">
@@ -5757,7 +5259,6 @@
         <v>2</v>
       </c>
       <c r="E87" s="16" t="inlineStr"/>
-      <c r="F87" s="16" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="16" t="inlineStr">
@@ -5778,12 +5279,7 @@
       <c r="D88" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="E88" s="16" t="inlineStr">
-        <is>
-          <t>2h</t>
-        </is>
-      </c>
-      <c r="F88" s="16" t="inlineStr"/>
+      <c r="E88" s="16" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="7" t="n"/>
@@ -5791,7 +5287,6 @@
       <c r="C89" s="7" t="n"/>
       <c r="D89" s="7" t="n"/>
       <c r="E89" s="7" t="n"/>
-      <c r="F89" s="7" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="7" t="n"/>
@@ -5799,7 +5294,6 @@
       <c r="C90" s="7" t="n"/>
       <c r="D90" s="7" t="n"/>
       <c r="E90" s="7" t="n"/>
-      <c r="F90" s="7" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="7" t="n"/>
@@ -5807,7 +5301,6 @@
       <c r="C91" s="7" t="n"/>
       <c r="D91" s="7" t="n"/>
       <c r="E91" s="7" t="n"/>
-      <c r="F91" s="7" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="7" t="n"/>
@@ -5815,7 +5308,6 @@
       <c r="C92" s="7" t="n"/>
       <c r="D92" s="7" t="n"/>
       <c r="E92" s="7" t="n"/>
-      <c r="F92" s="7" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="7" t="n"/>
@@ -5823,7 +5315,6 @@
       <c r="C93" s="7" t="n"/>
       <c r="D93" s="7" t="n"/>
       <c r="E93" s="7" t="n"/>
-      <c r="F93" s="7" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="7" t="n"/>
@@ -5831,7 +5322,6 @@
       <c r="C94" s="7" t="n"/>
       <c r="D94" s="7" t="n"/>
       <c r="E94" s="7" t="n"/>
-      <c r="F94" s="7" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="7" t="n"/>
@@ -5839,7 +5329,6 @@
       <c r="C95" s="7" t="n"/>
       <c r="D95" s="7" t="n"/>
       <c r="E95" s="7" t="n"/>
-      <c r="F95" s="7" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="7" t="n"/>
@@ -5847,7 +5336,6 @@
       <c r="C96" s="7" t="n"/>
       <c r="D96" s="7" t="n"/>
       <c r="E96" s="7" t="n"/>
-      <c r="F96" s="7" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="7" t="n"/>
@@ -5855,7 +5343,6 @@
       <c r="C97" s="7" t="n"/>
       <c r="D97" s="7" t="n"/>
       <c r="E97" s="7" t="n"/>
-      <c r="F97" s="7" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="7" t="n"/>
@@ -5863,7 +5350,6 @@
       <c r="C98" s="7" t="n"/>
       <c r="D98" s="7" t="n"/>
       <c r="E98" s="7" t="n"/>
-      <c r="F98" s="7" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="7" t="n"/>
@@ -5871,7 +5357,6 @@
       <c r="C99" s="7" t="n"/>
       <c r="D99" s="7" t="n"/>
       <c r="E99" s="7" t="n"/>
-      <c r="F99" s="7" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="7" t="n"/>
@@ -5879,7 +5364,6 @@
       <c r="C100" s="7" t="n"/>
       <c r="D100" s="7" t="n"/>
       <c r="E100" s="7" t="n"/>
-      <c r="F100" s="7" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="7" t="n"/>
@@ -5887,7 +5371,6 @@
       <c r="C101" s="7" t="n"/>
       <c r="D101" s="7" t="n"/>
       <c r="E101" s="7" t="n"/>
-      <c r="F101" s="7" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="7" t="n"/>
@@ -5895,7 +5378,6 @@
       <c r="C102" s="7" t="n"/>
       <c r="D102" s="7" t="n"/>
       <c r="E102" s="7" t="n"/>
-      <c r="F102" s="7" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="7" t="n"/>
@@ -5903,7 +5385,6 @@
       <c r="C103" s="7" t="n"/>
       <c r="D103" s="7" t="n"/>
       <c r="E103" s="7" t="n"/>
-      <c r="F103" s="7" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="7" t="n"/>
@@ -5911,7 +5392,6 @@
       <c r="C104" s="7" t="n"/>
       <c r="D104" s="7" t="n"/>
       <c r="E104" s="7" t="n"/>
-      <c r="F104" s="7" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="7" t="n"/>
@@ -5919,7 +5399,6 @@
       <c r="C105" s="7" t="n"/>
       <c r="D105" s="7" t="n"/>
       <c r="E105" s="7" t="n"/>
-      <c r="F105" s="7" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="7" t="n"/>
@@ -5927,7 +5406,6 @@
       <c r="C106" s="7" t="n"/>
       <c r="D106" s="7" t="n"/>
       <c r="E106" s="7" t="n"/>
-      <c r="F106" s="7" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="7" t="n"/>
@@ -5935,7 +5413,6 @@
       <c r="C107" s="7" t="n"/>
       <c r="D107" s="7" t="n"/>
       <c r="E107" s="7" t="n"/>
-      <c r="F107" s="7" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="7" t="n"/>
@@ -5943,7 +5420,6 @@
       <c r="C108" s="7" t="n"/>
       <c r="D108" s="7" t="n"/>
       <c r="E108" s="7" t="n"/>
-      <c r="F108" s="7" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="7" t="n"/>
@@ -5951,7 +5427,6 @@
       <c r="C109" s="7" t="n"/>
       <c r="D109" s="7" t="n"/>
       <c r="E109" s="7" t="n"/>
-      <c r="F109" s="7" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="7" t="n"/>
@@ -5959,7 +5434,6 @@
       <c r="C110" s="7" t="n"/>
       <c r="D110" s="7" t="n"/>
       <c r="E110" s="7" t="n"/>
-      <c r="F110" s="7" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="7" t="n"/>
@@ -5967,7 +5441,6 @@
       <c r="C111" s="7" t="n"/>
       <c r="D111" s="7" t="n"/>
       <c r="E111" s="7" t="n"/>
-      <c r="F111" s="7" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="7" t="n"/>
@@ -5975,7 +5448,6 @@
       <c r="C112" s="7" t="n"/>
       <c r="D112" s="7" t="n"/>
       <c r="E112" s="7" t="n"/>
-      <c r="F112" s="7" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="7" t="n"/>
@@ -5983,7 +5455,6 @@
       <c r="C113" s="7" t="n"/>
       <c r="D113" s="7" t="n"/>
       <c r="E113" s="7" t="n"/>
-      <c r="F113" s="7" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="7" t="n"/>
@@ -5991,7 +5462,6 @@
       <c r="C114" s="7" t="n"/>
       <c r="D114" s="7" t="n"/>
       <c r="E114" s="7" t="n"/>
-      <c r="F114" s="7" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="7" t="n"/>
@@ -5999,7 +5469,6 @@
       <c r="C115" s="7" t="n"/>
       <c r="D115" s="7" t="n"/>
       <c r="E115" s="7" t="n"/>
-      <c r="F115" s="7" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="7" t="n"/>
@@ -6007,7 +5476,6 @@
       <c r="C116" s="7" t="n"/>
       <c r="D116" s="7" t="n"/>
       <c r="E116" s="7" t="n"/>
-      <c r="F116" s="7" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="7" t="n"/>
@@ -6015,7 +5483,6 @@
       <c r="C117" s="7" t="n"/>
       <c r="D117" s="7" t="n"/>
       <c r="E117" s="7" t="n"/>
-      <c r="F117" s="7" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="7" t="n"/>
@@ -6023,7 +5490,6 @@
       <c r="C118" s="7" t="n"/>
       <c r="D118" s="7" t="n"/>
       <c r="E118" s="7" t="n"/>
-      <c r="F118" s="7" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="7" t="n"/>
@@ -6031,7 +5497,6 @@
       <c r="C119" s="7" t="n"/>
       <c r="D119" s="7" t="n"/>
       <c r="E119" s="7" t="n"/>
-      <c r="F119" s="7" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="7" t="n"/>
@@ -6039,7 +5504,6 @@
       <c r="C120" s="7" t="n"/>
       <c r="D120" s="7" t="n"/>
       <c r="E120" s="7" t="n"/>
-      <c r="F120" s="7" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="7" t="n"/>
@@ -6047,7 +5511,6 @@
       <c r="C121" s="7" t="n"/>
       <c r="D121" s="7" t="n"/>
       <c r="E121" s="7" t="n"/>
-      <c r="F121" s="7" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="7" t="n"/>
@@ -6055,7 +5518,6 @@
       <c r="C122" s="7" t="n"/>
       <c r="D122" s="7" t="n"/>
       <c r="E122" s="7" t="n"/>
-      <c r="F122" s="7" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="7" t="n"/>
@@ -6063,7 +5525,6 @@
       <c r="C123" s="7" t="n"/>
       <c r="D123" s="7" t="n"/>
       <c r="E123" s="7" t="n"/>
-      <c r="F123" s="7" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="7" t="n"/>
@@ -6071,7 +5532,6 @@
       <c r="C124" s="7" t="n"/>
       <c r="D124" s="7" t="n"/>
       <c r="E124" s="7" t="n"/>
-      <c r="F124" s="7" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="7" t="n"/>
@@ -6079,7 +5539,6 @@
       <c r="C125" s="7" t="n"/>
       <c r="D125" s="7" t="n"/>
       <c r="E125" s="7" t="n"/>
-      <c r="F125" s="7" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="7" t="n"/>
@@ -6087,7 +5546,6 @@
       <c r="C126" s="7" t="n"/>
       <c r="D126" s="7" t="n"/>
       <c r="E126" s="7" t="n"/>
-      <c r="F126" s="7" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="7" t="n"/>
@@ -6095,7 +5553,6 @@
       <c r="C127" s="7" t="n"/>
       <c r="D127" s="7" t="n"/>
       <c r="E127" s="7" t="n"/>
-      <c r="F127" s="7" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="7" t="n"/>
@@ -6103,7 +5560,6 @@
       <c r="C128" s="7" t="n"/>
       <c r="D128" s="7" t="n"/>
       <c r="E128" s="7" t="n"/>
-      <c r="F128" s="7" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="7" t="n"/>
@@ -6111,7 +5567,6 @@
       <c r="C129" s="7" t="n"/>
       <c r="D129" s="7" t="n"/>
       <c r="E129" s="7" t="n"/>
-      <c r="F129" s="7" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="7" t="n"/>
@@ -6119,7 +5574,6 @@
       <c r="C130" s="7" t="n"/>
       <c r="D130" s="7" t="n"/>
       <c r="E130" s="7" t="n"/>
-      <c r="F130" s="7" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="7" t="n"/>
@@ -6127,7 +5581,6 @@
       <c r="C131" s="7" t="n"/>
       <c r="D131" s="7" t="n"/>
       <c r="E131" s="7" t="n"/>
-      <c r="F131" s="7" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="7" t="n"/>
@@ -6135,7 +5588,6 @@
       <c r="C132" s="7" t="n"/>
       <c r="D132" s="7" t="n"/>
       <c r="E132" s="7" t="n"/>
-      <c r="F132" s="7" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="7" t="n"/>
@@ -6143,7 +5595,6 @@
       <c r="C133" s="7" t="n"/>
       <c r="D133" s="7" t="n"/>
       <c r="E133" s="7" t="n"/>
-      <c r="F133" s="7" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="7" t="n"/>
@@ -6151,7 +5602,6 @@
       <c r="C134" s="7" t="n"/>
       <c r="D134" s="7" t="n"/>
       <c r="E134" s="7" t="n"/>
-      <c r="F134" s="7" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="7" t="n"/>
@@ -6159,7 +5609,6 @@
       <c r="C135" s="7" t="n"/>
       <c r="D135" s="7" t="n"/>
       <c r="E135" s="7" t="n"/>
-      <c r="F135" s="7" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="7" t="n"/>
@@ -6167,7 +5616,6 @@
       <c r="C136" s="7" t="n"/>
       <c r="D136" s="7" t="n"/>
       <c r="E136" s="7" t="n"/>
-      <c r="F136" s="7" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="7" t="n"/>
@@ -6175,7 +5623,6 @@
       <c r="C137" s="7" t="n"/>
       <c r="D137" s="7" t="n"/>
       <c r="E137" s="7" t="n"/>
-      <c r="F137" s="7" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="7" t="n"/>
@@ -6183,7 +5630,6 @@
       <c r="C138" s="7" t="n"/>
       <c r="D138" s="7" t="n"/>
       <c r="E138" s="7" t="n"/>
-      <c r="F138" s="7" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="7" t="n"/>
@@ -6191,7 +5637,6 @@
       <c r="C139" s="7" t="n"/>
       <c r="D139" s="7" t="n"/>
       <c r="E139" s="7" t="n"/>
-      <c r="F139" s="7" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="7" t="n"/>
@@ -6199,7 +5644,6 @@
       <c r="C140" s="7" t="n"/>
       <c r="D140" s="7" t="n"/>
       <c r="E140" s="7" t="n"/>
-      <c r="F140" s="7" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="7" t="n"/>
@@ -6207,7 +5651,6 @@
       <c r="C141" s="7" t="n"/>
       <c r="D141" s="7" t="n"/>
       <c r="E141" s="7" t="n"/>
-      <c r="F141" s="7" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="7" t="n"/>
@@ -6215,7 +5658,6 @@
       <c r="C142" s="7" t="n"/>
       <c r="D142" s="7" t="n"/>
       <c r="E142" s="7" t="n"/>
-      <c r="F142" s="7" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="7" t="n"/>
@@ -6223,7 +5665,6 @@
       <c r="C143" s="7" t="n"/>
       <c r="D143" s="7" t="n"/>
       <c r="E143" s="7" t="n"/>
-      <c r="F143" s="7" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="7" t="n"/>
@@ -6231,7 +5672,6 @@
       <c r="C144" s="7" t="n"/>
       <c r="D144" s="7" t="n"/>
       <c r="E144" s="7" t="n"/>
-      <c r="F144" s="7" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="7" t="n"/>
@@ -6239,7 +5679,6 @@
       <c r="C145" s="7" t="n"/>
       <c r="D145" s="7" t="n"/>
       <c r="E145" s="7" t="n"/>
-      <c r="F145" s="7" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="7" t="n"/>
@@ -6247,7 +5686,6 @@
       <c r="C146" s="7" t="n"/>
       <c r="D146" s="7" t="n"/>
       <c r="E146" s="7" t="n"/>
-      <c r="F146" s="7" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="7" t="n"/>
@@ -6255,7 +5693,6 @@
       <c r="C147" s="7" t="n"/>
       <c r="D147" s="7" t="n"/>
       <c r="E147" s="7" t="n"/>
-      <c r="F147" s="7" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="7" t="n"/>
@@ -6263,7 +5700,6 @@
       <c r="C148" s="7" t="n"/>
       <c r="D148" s="7" t="n"/>
       <c r="E148" s="7" t="n"/>
-      <c r="F148" s="7" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="7" t="n"/>
@@ -6271,7 +5707,6 @@
       <c r="C149" s="7" t="n"/>
       <c r="D149" s="7" t="n"/>
       <c r="E149" s="7" t="n"/>
-      <c r="F149" s="7" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="7" t="n"/>
@@ -6279,7 +5714,6 @@
       <c r="C150" s="7" t="n"/>
       <c r="D150" s="7" t="n"/>
       <c r="E150" s="7" t="n"/>
-      <c r="F150" s="7" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="7" t="n"/>
@@ -6287,7 +5721,6 @@
       <c r="C151" s="7" t="n"/>
       <c r="D151" s="7" t="n"/>
       <c r="E151" s="7" t="n"/>
-      <c r="F151" s="7" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="7" t="n"/>
@@ -6295,7 +5728,6 @@
       <c r="C152" s="7" t="n"/>
       <c r="D152" s="7" t="n"/>
       <c r="E152" s="7" t="n"/>
-      <c r="F152" s="7" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="7" t="n"/>
@@ -6303,7 +5735,6 @@
       <c r="C153" s="7" t="n"/>
       <c r="D153" s="7" t="n"/>
       <c r="E153" s="7" t="n"/>
-      <c r="F153" s="7" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="7" t="n"/>
@@ -6311,7 +5742,6 @@
       <c r="C154" s="7" t="n"/>
       <c r="D154" s="7" t="n"/>
       <c r="E154" s="7" t="n"/>
-      <c r="F154" s="7" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="7" t="n"/>
@@ -6319,7 +5749,6 @@
       <c r="C155" s="7" t="n"/>
       <c r="D155" s="7" t="n"/>
       <c r="E155" s="7" t="n"/>
-      <c r="F155" s="7" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="7" t="n"/>
@@ -6327,7 +5756,6 @@
       <c r="C156" s="7" t="n"/>
       <c r="D156" s="7" t="n"/>
       <c r="E156" s="7" t="n"/>
-      <c r="F156" s="7" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="7" t="n"/>
@@ -6335,7 +5763,6 @@
       <c r="C157" s="7" t="n"/>
       <c r="D157" s="7" t="n"/>
       <c r="E157" s="7" t="n"/>
-      <c r="F157" s="7" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="7" t="n"/>
@@ -6343,7 +5770,6 @@
       <c r="C158" s="7" t="n"/>
       <c r="D158" s="7" t="n"/>
       <c r="E158" s="7" t="n"/>
-      <c r="F158" s="7" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="7" t="n"/>
@@ -6351,7 +5777,6 @@
       <c r="C159" s="7" t="n"/>
       <c r="D159" s="7" t="n"/>
       <c r="E159" s="7" t="n"/>
-      <c r="F159" s="7" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="7" t="n"/>
@@ -6359,7 +5784,6 @@
       <c r="C160" s="7" t="n"/>
       <c r="D160" s="7" t="n"/>
       <c r="E160" s="7" t="n"/>
-      <c r="F160" s="7" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="7" t="n"/>
@@ -6367,7 +5791,6 @@
       <c r="C161" s="7" t="n"/>
       <c r="D161" s="7" t="n"/>
       <c r="E161" s="7" t="n"/>
-      <c r="F161" s="7" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="7" t="n"/>
@@ -6375,7 +5798,6 @@
       <c r="C162" s="7" t="n"/>
       <c r="D162" s="7" t="n"/>
       <c r="E162" s="7" t="n"/>
-      <c r="F162" s="7" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="7" t="n"/>
@@ -6383,7 +5805,6 @@
       <c r="C163" s="7" t="n"/>
       <c r="D163" s="7" t="n"/>
       <c r="E163" s="7" t="n"/>
-      <c r="F163" s="7" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="7" t="n"/>
@@ -6391,7 +5812,6 @@
       <c r="C164" s="7" t="n"/>
       <c r="D164" s="7" t="n"/>
       <c r="E164" s="7" t="n"/>
-      <c r="F164" s="7" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="7" t="n"/>
@@ -6399,7 +5819,6 @@
       <c r="C165" s="7" t="n"/>
       <c r="D165" s="7" t="n"/>
       <c r="E165" s="7" t="n"/>
-      <c r="F165" s="7" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="7" t="n"/>
@@ -6407,7 +5826,6 @@
       <c r="C166" s="7" t="n"/>
       <c r="D166" s="7" t="n"/>
       <c r="E166" s="7" t="n"/>
-      <c r="F166" s="7" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="7" t="n"/>
@@ -6415,7 +5833,6 @@
       <c r="C167" s="7" t="n"/>
       <c r="D167" s="7" t="n"/>
       <c r="E167" s="7" t="n"/>
-      <c r="F167" s="7" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="7" t="n"/>
@@ -6423,7 +5840,6 @@
       <c r="C168" s="7" t="n"/>
       <c r="D168" s="7" t="n"/>
       <c r="E168" s="7" t="n"/>
-      <c r="F168" s="7" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="7" t="n"/>
@@ -6431,7 +5847,6 @@
       <c r="C169" s="7" t="n"/>
       <c r="D169" s="7" t="n"/>
       <c r="E169" s="7" t="n"/>
-      <c r="F169" s="7" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="7" t="n"/>
@@ -6439,7 +5854,6 @@
       <c r="C170" s="7" t="n"/>
       <c r="D170" s="7" t="n"/>
       <c r="E170" s="7" t="n"/>
-      <c r="F170" s="7" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="7" t="n"/>
@@ -6447,7 +5861,6 @@
       <c r="C171" s="7" t="n"/>
       <c r="D171" s="7" t="n"/>
       <c r="E171" s="7" t="n"/>
-      <c r="F171" s="7" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="7" t="n"/>
@@ -6455,7 +5868,6 @@
       <c r="C172" s="7" t="n"/>
       <c r="D172" s="7" t="n"/>
       <c r="E172" s="7" t="n"/>
-      <c r="F172" s="7" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="7" t="n"/>
@@ -6463,7 +5875,6 @@
       <c r="C173" s="7" t="n"/>
       <c r="D173" s="7" t="n"/>
       <c r="E173" s="7" t="n"/>
-      <c r="F173" s="7" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="7" t="n"/>
@@ -6471,7 +5882,6 @@
       <c r="C174" s="7" t="n"/>
       <c r="D174" s="7" t="n"/>
       <c r="E174" s="7" t="n"/>
-      <c r="F174" s="7" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="7" t="n"/>
@@ -6479,7 +5889,6 @@
       <c r="C175" s="7" t="n"/>
       <c r="D175" s="7" t="n"/>
       <c r="E175" s="7" t="n"/>
-      <c r="F175" s="7" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="7" t="n"/>
@@ -6487,7 +5896,6 @@
       <c r="C176" s="7" t="n"/>
       <c r="D176" s="7" t="n"/>
       <c r="E176" s="7" t="n"/>
-      <c r="F176" s="7" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="7" t="n"/>
@@ -6495,7 +5903,6 @@
       <c r="C177" s="7" t="n"/>
       <c r="D177" s="7" t="n"/>
       <c r="E177" s="7" t="n"/>
-      <c r="F177" s="7" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="7" t="n"/>
@@ -6503,7 +5910,6 @@
       <c r="C178" s="7" t="n"/>
       <c r="D178" s="7" t="n"/>
       <c r="E178" s="7" t="n"/>
-      <c r="F178" s="7" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="7" t="n"/>
@@ -6511,7 +5917,6 @@
       <c r="C179" s="7" t="n"/>
       <c r="D179" s="7" t="n"/>
       <c r="E179" s="7" t="n"/>
-      <c r="F179" s="7" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="7" t="n"/>
@@ -6519,7 +5924,6 @@
       <c r="C180" s="7" t="n"/>
       <c r="D180" s="7" t="n"/>
       <c r="E180" s="7" t="n"/>
-      <c r="F180" s="7" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="7" t="n"/>
@@ -6527,7 +5931,6 @@
       <c r="C181" s="7" t="n"/>
       <c r="D181" s="7" t="n"/>
       <c r="E181" s="7" t="n"/>
-      <c r="F181" s="7" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="7" t="n"/>
@@ -6535,7 +5938,6 @@
       <c r="C182" s="7" t="n"/>
       <c r="D182" s="7" t="n"/>
       <c r="E182" s="7" t="n"/>
-      <c r="F182" s="7" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="7" t="n"/>
@@ -6543,7 +5945,6 @@
       <c r="C183" s="7" t="n"/>
       <c r="D183" s="7" t="n"/>
       <c r="E183" s="7" t="n"/>
-      <c r="F183" s="7" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="7" t="n"/>
@@ -6551,7 +5952,6 @@
       <c r="C184" s="7" t="n"/>
       <c r="D184" s="7" t="n"/>
       <c r="E184" s="7" t="n"/>
-      <c r="F184" s="7" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="7" t="n"/>
@@ -6559,7 +5959,6 @@
       <c r="C185" s="7" t="n"/>
       <c r="D185" s="7" t="n"/>
       <c r="E185" s="7" t="n"/>
-      <c r="F185" s="7" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="7" t="n"/>
@@ -6567,7 +5966,6 @@
       <c r="C186" s="7" t="n"/>
       <c r="D186" s="7" t="n"/>
       <c r="E186" s="7" t="n"/>
-      <c r="F186" s="7" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="7" t="n"/>
@@ -6575,7 +5973,6 @@
       <c r="C187" s="7" t="n"/>
       <c r="D187" s="7" t="n"/>
       <c r="E187" s="7" t="n"/>
-      <c r="F187" s="7" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="7" t="n"/>
@@ -6583,7 +5980,6 @@
       <c r="C188" s="7" t="n"/>
       <c r="D188" s="7" t="n"/>
       <c r="E188" s="7" t="n"/>
-      <c r="F188" s="7" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="7" t="n"/>
@@ -6591,7 +5987,6 @@
       <c r="C189" s="7" t="n"/>
       <c r="D189" s="7" t="n"/>
       <c r="E189" s="7" t="n"/>
-      <c r="F189" s="7" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="7" t="n"/>
@@ -6599,7 +5994,6 @@
       <c r="C190" s="7" t="n"/>
       <c r="D190" s="7" t="n"/>
       <c r="E190" s="7" t="n"/>
-      <c r="F190" s="7" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="7" t="n"/>
@@ -6607,7 +6001,6 @@
       <c r="C191" s="7" t="n"/>
       <c r="D191" s="7" t="n"/>
       <c r="E191" s="7" t="n"/>
-      <c r="F191" s="7" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="7" t="n"/>
@@ -6615,7 +6008,6 @@
       <c r="C192" s="7" t="n"/>
       <c r="D192" s="7" t="n"/>
       <c r="E192" s="7" t="n"/>
-      <c r="F192" s="7" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="7" t="n"/>
@@ -6623,7 +6015,6 @@
       <c r="C193" s="7" t="n"/>
       <c r="D193" s="7" t="n"/>
       <c r="E193" s="7" t="n"/>
-      <c r="F193" s="7" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="7" t="n"/>
@@ -6631,7 +6022,6 @@
       <c r="C194" s="7" t="n"/>
       <c r="D194" s="7" t="n"/>
       <c r="E194" s="7" t="n"/>
-      <c r="F194" s="7" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="7" t="n"/>
@@ -6639,7 +6029,6 @@
       <c r="C195" s="7" t="n"/>
       <c r="D195" s="7" t="n"/>
       <c r="E195" s="7" t="n"/>
-      <c r="F195" s="7" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="7" t="n"/>
@@ -6647,7 +6036,6 @@
       <c r="C196" s="7" t="n"/>
       <c r="D196" s="7" t="n"/>
       <c r="E196" s="7" t="n"/>
-      <c r="F196" s="7" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="7" t="n"/>
@@ -6655,7 +6043,6 @@
       <c r="C197" s="7" t="n"/>
       <c r="D197" s="7" t="n"/>
       <c r="E197" s="7" t="n"/>
-      <c r="F197" s="7" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="7" t="n"/>
@@ -6663,7 +6050,6 @@
       <c r="C198" s="7" t="n"/>
       <c r="D198" s="7" t="n"/>
       <c r="E198" s="7" t="n"/>
-      <c r="F198" s="7" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="7" t="n"/>
@@ -6671,7 +6057,6 @@
       <c r="C199" s="7" t="n"/>
       <c r="D199" s="7" t="n"/>
       <c r="E199" s="7" t="n"/>
-      <c r="F199" s="7" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="7" t="n"/>
@@ -6679,7 +6064,6 @@
       <c r="C200" s="7" t="n"/>
       <c r="D200" s="7" t="n"/>
       <c r="E200" s="7" t="n"/>
-      <c r="F200" s="7" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="7" t="n"/>
@@ -6687,7 +6071,6 @@
       <c r="C201" s="7" t="n"/>
       <c r="D201" s="7" t="n"/>
       <c r="E201" s="7" t="n"/>
-      <c r="F201" s="7" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="7" t="n"/>
@@ -6695,7 +6078,6 @@
       <c r="C202" s="7" t="n"/>
       <c r="D202" s="7" t="n"/>
       <c r="E202" s="7" t="n"/>
-      <c r="F202" s="7" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="7" t="n"/>
@@ -6703,7 +6085,6 @@
       <c r="C203" s="7" t="n"/>
       <c r="D203" s="7" t="n"/>
       <c r="E203" s="7" t="n"/>
-      <c r="F203" s="7" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="7" t="n"/>
@@ -6711,7 +6092,6 @@
       <c r="C204" s="7" t="n"/>
       <c r="D204" s="7" t="n"/>
       <c r="E204" s="7" t="n"/>
-      <c r="F204" s="7" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="7" t="n"/>
@@ -6719,7 +6099,6 @@
       <c r="C205" s="7" t="n"/>
       <c r="D205" s="7" t="n"/>
       <c r="E205" s="7" t="n"/>
-      <c r="F205" s="7" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="7" t="n"/>
@@ -6727,7 +6106,6 @@
       <c r="C206" s="7" t="n"/>
       <c r="D206" s="7" t="n"/>
       <c r="E206" s="7" t="n"/>
-      <c r="F206" s="7" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="7" t="n"/>
@@ -6735,7 +6113,6 @@
       <c r="C207" s="7" t="n"/>
       <c r="D207" s="7" t="n"/>
       <c r="E207" s="7" t="n"/>
-      <c r="F207" s="7" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="7" t="n"/>
@@ -6743,7 +6120,6 @@
       <c r="C208" s="7" t="n"/>
       <c r="D208" s="7" t="n"/>
       <c r="E208" s="7" t="n"/>
-      <c r="F208" s="7" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="7" t="n"/>
@@ -6751,7 +6127,6 @@
       <c r="C209" s="7" t="n"/>
       <c r="D209" s="7" t="n"/>
       <c r="E209" s="7" t="n"/>
-      <c r="F209" s="7" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="7" t="n"/>
@@ -6759,7 +6134,6 @@
       <c r="C210" s="7" t="n"/>
       <c r="D210" s="7" t="n"/>
       <c r="E210" s="7" t="n"/>
-      <c r="F210" s="7" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="7" t="n"/>
@@ -6767,7 +6141,6 @@
       <c r="C211" s="7" t="n"/>
       <c r="D211" s="7" t="n"/>
       <c r="E211" s="7" t="n"/>
-      <c r="F211" s="7" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="7" t="n"/>
@@ -6775,7 +6148,6 @@
       <c r="C212" s="7" t="n"/>
       <c r="D212" s="7" t="n"/>
       <c r="E212" s="7" t="n"/>
-      <c r="F212" s="7" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="7" t="n"/>
@@ -6783,7 +6155,6 @@
       <c r="C213" s="7" t="n"/>
       <c r="D213" s="7" t="n"/>
       <c r="E213" s="7" t="n"/>
-      <c r="F213" s="7" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="7" t="n"/>
@@ -6791,7 +6162,6 @@
       <c r="C214" s="7" t="n"/>
       <c r="D214" s="7" t="n"/>
       <c r="E214" s="7" t="n"/>
-      <c r="F214" s="7" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="7" t="n"/>
@@ -6799,7 +6169,6 @@
       <c r="C215" s="7" t="n"/>
       <c r="D215" s="7" t="n"/>
       <c r="E215" s="7" t="n"/>
-      <c r="F215" s="7" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="7" t="n"/>
@@ -6807,7 +6176,6 @@
       <c r="C216" s="7" t="n"/>
       <c r="D216" s="7" t="n"/>
       <c r="E216" s="7" t="n"/>
-      <c r="F216" s="7" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="7" t="n"/>
@@ -6815,7 +6183,6 @@
       <c r="C217" s="7" t="n"/>
       <c r="D217" s="7" t="n"/>
       <c r="E217" s="7" t="n"/>
-      <c r="F217" s="7" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="7" t="n"/>
@@ -6823,7 +6190,6 @@
       <c r="C218" s="7" t="n"/>
       <c r="D218" s="7" t="n"/>
       <c r="E218" s="7" t="n"/>
-      <c r="F218" s="7" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="7" t="n"/>
@@ -6831,7 +6197,6 @@
       <c r="C219" s="7" t="n"/>
       <c r="D219" s="7" t="n"/>
       <c r="E219" s="7" t="n"/>
-      <c r="F219" s="7" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="7" t="n"/>
@@ -6839,7 +6204,6 @@
       <c r="C220" s="7" t="n"/>
       <c r="D220" s="7" t="n"/>
       <c r="E220" s="7" t="n"/>
-      <c r="F220" s="7" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="7" t="n"/>
@@ -6847,7 +6211,6 @@
       <c r="C221" s="7" t="n"/>
       <c r="D221" s="7" t="n"/>
       <c r="E221" s="7" t="n"/>
-      <c r="F221" s="7" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="7" t="n"/>
@@ -6855,7 +6218,6 @@
       <c r="C222" s="7" t="n"/>
       <c r="D222" s="7" t="n"/>
       <c r="E222" s="7" t="n"/>
-      <c r="F222" s="7" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="7" t="n"/>
@@ -6863,7 +6225,6 @@
       <c r="C223" s="7" t="n"/>
       <c r="D223" s="7" t="n"/>
       <c r="E223" s="7" t="n"/>
-      <c r="F223" s="7" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="7" t="n"/>
@@ -6871,7 +6232,6 @@
       <c r="C224" s="7" t="n"/>
       <c r="D224" s="7" t="n"/>
       <c r="E224" s="7" t="n"/>
-      <c r="F224" s="7" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="7" t="n"/>
@@ -6879,7 +6239,6 @@
       <c r="C225" s="7" t="n"/>
       <c r="D225" s="7" t="n"/>
       <c r="E225" s="7" t="n"/>
-      <c r="F225" s="7" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="7" t="n"/>
@@ -6887,7 +6246,6 @@
       <c r="C226" s="7" t="n"/>
       <c r="D226" s="7" t="n"/>
       <c r="E226" s="7" t="n"/>
-      <c r="F226" s="7" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="7" t="n"/>
@@ -6895,7 +6253,6 @@
       <c r="C227" s="7" t="n"/>
       <c r="D227" s="7" t="n"/>
       <c r="E227" s="7" t="n"/>
-      <c r="F227" s="7" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="7" t="n"/>
@@ -6903,7 +6260,6 @@
       <c r="C228" s="7" t="n"/>
       <c r="D228" s="7" t="n"/>
       <c r="E228" s="7" t="n"/>
-      <c r="F228" s="7" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="7" t="n"/>
@@ -6911,7 +6267,6 @@
       <c r="C229" s="7" t="n"/>
       <c r="D229" s="7" t="n"/>
       <c r="E229" s="7" t="n"/>
-      <c r="F229" s="7" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="7" t="n"/>
@@ -6919,7 +6274,6 @@
       <c r="C230" s="7" t="n"/>
       <c r="D230" s="7" t="n"/>
       <c r="E230" s="7" t="n"/>
-      <c r="F230" s="7" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="7" t="n"/>
@@ -6927,7 +6281,6 @@
       <c r="C231" s="7" t="n"/>
       <c r="D231" s="7" t="n"/>
       <c r="E231" s="7" t="n"/>
-      <c r="F231" s="7" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="7" t="n"/>
@@ -6935,7 +6288,6 @@
       <c r="C232" s="7" t="n"/>
       <c r="D232" s="7" t="n"/>
       <c r="E232" s="7" t="n"/>
-      <c r="F232" s="7" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="7" t="n"/>
@@ -6943,7 +6295,6 @@
       <c r="C233" s="7" t="n"/>
       <c r="D233" s="7" t="n"/>
       <c r="E233" s="7" t="n"/>
-      <c r="F233" s="7" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="7" t="n"/>
@@ -6951,7 +6302,6 @@
       <c r="C234" s="7" t="n"/>
       <c r="D234" s="7" t="n"/>
       <c r="E234" s="7" t="n"/>
-      <c r="F234" s="7" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="7" t="n"/>
@@ -6959,7 +6309,6 @@
       <c r="C235" s="7" t="n"/>
       <c r="D235" s="7" t="n"/>
       <c r="E235" s="7" t="n"/>
-      <c r="F235" s="7" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="7" t="n"/>
@@ -6967,7 +6316,6 @@
       <c r="C236" s="7" t="n"/>
       <c r="D236" s="7" t="n"/>
       <c r="E236" s="7" t="n"/>
-      <c r="F236" s="7" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="7" t="n"/>
@@ -6975,7 +6323,6 @@
       <c r="C237" s="7" t="n"/>
       <c r="D237" s="7" t="n"/>
       <c r="E237" s="7" t="n"/>
-      <c r="F237" s="7" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="7" t="n"/>
@@ -6983,7 +6330,6 @@
       <c r="C238" s="7" t="n"/>
       <c r="D238" s="7" t="n"/>
       <c r="E238" s="7" t="n"/>
-      <c r="F238" s="7" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="7" t="n"/>
@@ -6991,7 +6337,6 @@
       <c r="C239" s="7" t="n"/>
       <c r="D239" s="7" t="n"/>
       <c r="E239" s="7" t="n"/>
-      <c r="F239" s="7" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="7" t="n"/>
@@ -6999,7 +6344,6 @@
       <c r="C240" s="7" t="n"/>
       <c r="D240" s="7" t="n"/>
       <c r="E240" s="7" t="n"/>
-      <c r="F240" s="7" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="7" t="n"/>
@@ -7007,7 +6351,6 @@
       <c r="C241" s="7" t="n"/>
       <c r="D241" s="7" t="n"/>
       <c r="E241" s="7" t="n"/>
-      <c r="F241" s="7" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="7" t="n"/>
@@ -7015,7 +6358,6 @@
       <c r="C242" s="7" t="n"/>
       <c r="D242" s="7" t="n"/>
       <c r="E242" s="7" t="n"/>
-      <c r="F242" s="7" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="7" t="n"/>
@@ -7023,7 +6365,6 @@
       <c r="C243" s="7" t="n"/>
       <c r="D243" s="7" t="n"/>
       <c r="E243" s="7" t="n"/>
-      <c r="F243" s="7" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="7" t="n"/>
@@ -7031,7 +6372,6 @@
       <c r="C244" s="7" t="n"/>
       <c r="D244" s="7" t="n"/>
       <c r="E244" s="7" t="n"/>
-      <c r="F244" s="7" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="7" t="n"/>
@@ -7039,7 +6379,6 @@
       <c r="C245" s="7" t="n"/>
       <c r="D245" s="7" t="n"/>
       <c r="E245" s="7" t="n"/>
-      <c r="F245" s="7" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="7" t="n"/>
@@ -7047,7 +6386,6 @@
       <c r="C246" s="7" t="n"/>
       <c r="D246" s="7" t="n"/>
       <c r="E246" s="7" t="n"/>
-      <c r="F246" s="7" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="7" t="n"/>
@@ -7055,7 +6393,6 @@
       <c r="C247" s="7" t="n"/>
       <c r="D247" s="7" t="n"/>
       <c r="E247" s="7" t="n"/>
-      <c r="F247" s="7" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="7" t="n"/>
@@ -7063,7 +6400,6 @@
       <c r="C248" s="7" t="n"/>
       <c r="D248" s="7" t="n"/>
       <c r="E248" s="7" t="n"/>
-      <c r="F248" s="7" t="n"/>
     </row>
     <row r="249">
       <c r="A249" s="7" t="n"/>
@@ -7071,7 +6407,6 @@
       <c r="C249" s="7" t="n"/>
       <c r="D249" s="7" t="n"/>
       <c r="E249" s="7" t="n"/>
-      <c r="F249" s="7" t="n"/>
     </row>
     <row r="250">
       <c r="A250" s="7" t="n"/>
@@ -7079,7 +6414,6 @@
       <c r="C250" s="7" t="n"/>
       <c r="D250" s="7" t="n"/>
       <c r="E250" s="7" t="n"/>
-      <c r="F250" s="7" t="n"/>
     </row>
     <row r="251">
       <c r="A251" s="7" t="n"/>
@@ -7087,7 +6421,6 @@
       <c r="C251" s="7" t="n"/>
       <c r="D251" s="7" t="n"/>
       <c r="E251" s="7" t="n"/>
-      <c r="F251" s="7" t="n"/>
     </row>
     <row r="252">
       <c r="A252" s="7" t="n"/>
@@ -7095,7 +6428,6 @@
       <c r="C252" s="7" t="n"/>
       <c r="D252" s="7" t="n"/>
       <c r="E252" s="7" t="n"/>
-      <c r="F252" s="7" t="n"/>
     </row>
     <row r="253">
       <c r="A253" s="7" t="n"/>
@@ -7103,7 +6435,6 @@
       <c r="C253" s="7" t="n"/>
       <c r="D253" s="7" t="n"/>
       <c r="E253" s="7" t="n"/>
-      <c r="F253" s="7" t="n"/>
     </row>
     <row r="254">
       <c r="A254" s="7" t="n"/>
@@ -7111,7 +6442,6 @@
       <c r="C254" s="7" t="n"/>
       <c r="D254" s="7" t="n"/>
       <c r="E254" s="7" t="n"/>
-      <c r="F254" s="7" t="n"/>
     </row>
     <row r="255">
       <c r="A255" s="7" t="n"/>
@@ -7119,7 +6449,6 @@
       <c r="C255" s="7" t="n"/>
       <c r="D255" s="7" t="n"/>
       <c r="E255" s="7" t="n"/>
-      <c r="F255" s="7" t="n"/>
     </row>
     <row r="256">
       <c r="A256" s="7" t="n"/>
@@ -7127,7 +6456,6 @@
       <c r="C256" s="7" t="n"/>
       <c r="D256" s="7" t="n"/>
       <c r="E256" s="7" t="n"/>
-      <c r="F256" s="7" t="n"/>
     </row>
     <row r="257">
       <c r="A257" s="7" t="n"/>
@@ -7135,7 +6463,6 @@
       <c r="C257" s="7" t="n"/>
       <c r="D257" s="7" t="n"/>
       <c r="E257" s="7" t="n"/>
-      <c r="F257" s="7" t="n"/>
     </row>
     <row r="258">
       <c r="A258" s="7" t="n"/>
@@ -7143,7 +6470,6 @@
       <c r="C258" s="7" t="n"/>
       <c r="D258" s="7" t="n"/>
       <c r="E258" s="7" t="n"/>
-      <c r="F258" s="7" t="n"/>
     </row>
     <row r="259">
       <c r="A259" s="7" t="n"/>
@@ -7151,7 +6477,6 @@
       <c r="C259" s="7" t="n"/>
       <c r="D259" s="7" t="n"/>
       <c r="E259" s="7" t="n"/>
-      <c r="F259" s="7" t="n"/>
     </row>
     <row r="260">
       <c r="A260" s="7" t="n"/>
@@ -7159,7 +6484,6 @@
       <c r="C260" s="7" t="n"/>
       <c r="D260" s="7" t="n"/>
       <c r="E260" s="7" t="n"/>
-      <c r="F260" s="7" t="n"/>
     </row>
     <row r="261">
       <c r="A261" s="7" t="n"/>
@@ -7167,7 +6491,6 @@
       <c r="C261" s="7" t="n"/>
       <c r="D261" s="7" t="n"/>
       <c r="E261" s="7" t="n"/>
-      <c r="F261" s="7" t="n"/>
     </row>
     <row r="262">
       <c r="A262" s="7" t="n"/>
@@ -7175,7 +6498,6 @@
       <c r="C262" s="7" t="n"/>
       <c r="D262" s="7" t="n"/>
       <c r="E262" s="7" t="n"/>
-      <c r="F262" s="7" t="n"/>
     </row>
     <row r="263">
       <c r="A263" s="7" t="n"/>
@@ -7183,7 +6505,6 @@
       <c r="C263" s="7" t="n"/>
       <c r="D263" s="7" t="n"/>
       <c r="E263" s="7" t="n"/>
-      <c r="F263" s="7" t="n"/>
     </row>
     <row r="264">
       <c r="A264" s="7" t="n"/>
@@ -7191,7 +6512,6 @@
       <c r="C264" s="7" t="n"/>
       <c r="D264" s="7" t="n"/>
       <c r="E264" s="7" t="n"/>
-      <c r="F264" s="7" t="n"/>
     </row>
     <row r="265">
       <c r="A265" s="7" t="n"/>
@@ -7199,7 +6519,6 @@
       <c r="C265" s="7" t="n"/>
       <c r="D265" s="7" t="n"/>
       <c r="E265" s="7" t="n"/>
-      <c r="F265" s="7" t="n"/>
     </row>
     <row r="266">
       <c r="A266" s="7" t="n"/>
@@ -7207,7 +6526,6 @@
       <c r="C266" s="7" t="n"/>
       <c r="D266" s="7" t="n"/>
       <c r="E266" s="7" t="n"/>
-      <c r="F266" s="7" t="n"/>
     </row>
     <row r="267">
       <c r="A267" s="7" t="n"/>
@@ -7215,7 +6533,6 @@
       <c r="C267" s="7" t="n"/>
       <c r="D267" s="7" t="n"/>
       <c r="E267" s="7" t="n"/>
-      <c r="F267" s="7" t="n"/>
     </row>
     <row r="268">
       <c r="A268" s="7" t="n"/>
@@ -7223,7 +6540,6 @@
       <c r="C268" s="7" t="n"/>
       <c r="D268" s="7" t="n"/>
       <c r="E268" s="7" t="n"/>
-      <c r="F268" s="7" t="n"/>
     </row>
     <row r="269">
       <c r="A269" s="7" t="n"/>
@@ -7231,7 +6547,6 @@
       <c r="C269" s="7" t="n"/>
       <c r="D269" s="7" t="n"/>
       <c r="E269" s="7" t="n"/>
-      <c r="F269" s="7" t="n"/>
     </row>
     <row r="270">
       <c r="A270" s="7" t="n"/>
@@ -7239,7 +6554,6 @@
       <c r="C270" s="7" t="n"/>
       <c r="D270" s="7" t="n"/>
       <c r="E270" s="7" t="n"/>
-      <c r="F270" s="7" t="n"/>
     </row>
     <row r="271">
       <c r="A271" s="7" t="n"/>
@@ -7247,7 +6561,6 @@
       <c r="C271" s="7" t="n"/>
       <c r="D271" s="7" t="n"/>
       <c r="E271" s="7" t="n"/>
-      <c r="F271" s="7" t="n"/>
     </row>
     <row r="272">
       <c r="A272" s="7" t="n"/>
@@ -7255,7 +6568,6 @@
       <c r="C272" s="7" t="n"/>
       <c r="D272" s="7" t="n"/>
       <c r="E272" s="7" t="n"/>
-      <c r="F272" s="7" t="n"/>
     </row>
     <row r="273">
       <c r="A273" s="7" t="n"/>
@@ -7263,7 +6575,6 @@
       <c r="C273" s="7" t="n"/>
       <c r="D273" s="7" t="n"/>
       <c r="E273" s="7" t="n"/>
-      <c r="F273" s="7" t="n"/>
     </row>
     <row r="274">
       <c r="A274" s="7" t="n"/>
@@ -7271,7 +6582,6 @@
       <c r="C274" s="7" t="n"/>
       <c r="D274" s="7" t="n"/>
       <c r="E274" s="7" t="n"/>
-      <c r="F274" s="7" t="n"/>
     </row>
     <row r="275">
       <c r="A275" s="7" t="n"/>
@@ -7279,7 +6589,6 @@
       <c r="C275" s="7" t="n"/>
       <c r="D275" s="7" t="n"/>
       <c r="E275" s="7" t="n"/>
-      <c r="F275" s="7" t="n"/>
     </row>
     <row r="276">
       <c r="A276" s="7" t="n"/>
@@ -7287,7 +6596,6 @@
       <c r="C276" s="7" t="n"/>
       <c r="D276" s="7" t="n"/>
       <c r="E276" s="7" t="n"/>
-      <c r="F276" s="7" t="n"/>
     </row>
     <row r="277">
       <c r="A277" s="7" t="n"/>
@@ -7295,7 +6603,6 @@
       <c r="C277" s="7" t="n"/>
       <c r="D277" s="7" t="n"/>
       <c r="E277" s="7" t="n"/>
-      <c r="F277" s="7" t="n"/>
     </row>
     <row r="278">
       <c r="A278" s="7" t="n"/>
@@ -7303,7 +6610,6 @@
       <c r="C278" s="7" t="n"/>
       <c r="D278" s="7" t="n"/>
       <c r="E278" s="7" t="n"/>
-      <c r="F278" s="7" t="n"/>
     </row>
     <row r="279">
       <c r="A279" s="7" t="n"/>
@@ -7311,7 +6617,6 @@
       <c r="C279" s="7" t="n"/>
       <c r="D279" s="7" t="n"/>
       <c r="E279" s="7" t="n"/>
-      <c r="F279" s="7" t="n"/>
     </row>
     <row r="280">
       <c r="A280" s="7" t="n"/>
@@ -7319,7 +6624,6 @@
       <c r="C280" s="7" t="n"/>
       <c r="D280" s="7" t="n"/>
       <c r="E280" s="7" t="n"/>
-      <c r="F280" s="7" t="n"/>
     </row>
     <row r="281">
       <c r="A281" s="7" t="n"/>
@@ -7327,7 +6631,6 @@
       <c r="C281" s="7" t="n"/>
       <c r="D281" s="7" t="n"/>
       <c r="E281" s="7" t="n"/>
-      <c r="F281" s="7" t="n"/>
     </row>
     <row r="282">
       <c r="A282" s="7" t="n"/>
@@ -7335,7 +6638,6 @@
       <c r="C282" s="7" t="n"/>
       <c r="D282" s="7" t="n"/>
       <c r="E282" s="7" t="n"/>
-      <c r="F282" s="7" t="n"/>
     </row>
     <row r="283">
       <c r="A283" s="7" t="n"/>
@@ -7343,7 +6645,6 @@
       <c r="C283" s="7" t="n"/>
       <c r="D283" s="7" t="n"/>
       <c r="E283" s="7" t="n"/>
-      <c r="F283" s="7" t="n"/>
     </row>
     <row r="284">
       <c r="A284" s="7" t="n"/>
@@ -7351,7 +6652,6 @@
       <c r="C284" s="7" t="n"/>
       <c r="D284" s="7" t="n"/>
       <c r="E284" s="7" t="n"/>
-      <c r="F284" s="7" t="n"/>
     </row>
     <row r="285">
       <c r="A285" s="7" t="n"/>
@@ -7359,7 +6659,6 @@
       <c r="C285" s="7" t="n"/>
       <c r="D285" s="7" t="n"/>
       <c r="E285" s="7" t="n"/>
-      <c r="F285" s="7" t="n"/>
     </row>
     <row r="286">
       <c r="A286" s="7" t="n"/>
@@ -7367,7 +6666,6 @@
       <c r="C286" s="7" t="n"/>
       <c r="D286" s="7" t="n"/>
       <c r="E286" s="7" t="n"/>
-      <c r="F286" s="7" t="n"/>
     </row>
     <row r="287">
       <c r="A287" s="7" t="n"/>
@@ -7375,7 +6673,6 @@
       <c r="C287" s="7" t="n"/>
       <c r="D287" s="7" t="n"/>
       <c r="E287" s="7" t="n"/>
-      <c r="F287" s="7" t="n"/>
     </row>
     <row r="288">
       <c r="A288" s="7" t="n"/>
@@ -7383,7 +6680,6 @@
       <c r="C288" s="7" t="n"/>
       <c r="D288" s="7" t="n"/>
       <c r="E288" s="7" t="n"/>
-      <c r="F288" s="7" t="n"/>
     </row>
     <row r="289">
       <c r="A289" s="7" t="n"/>
@@ -7391,7 +6687,6 @@
       <c r="C289" s="7" t="n"/>
       <c r="D289" s="7" t="n"/>
       <c r="E289" s="7" t="n"/>
-      <c r="F289" s="7" t="n"/>
     </row>
     <row r="290">
       <c r="A290" s="7" t="n"/>
@@ -7399,7 +6694,6 @@
       <c r="C290" s="7" t="n"/>
       <c r="D290" s="7" t="n"/>
       <c r="E290" s="7" t="n"/>
-      <c r="F290" s="7" t="n"/>
     </row>
     <row r="291">
       <c r="A291" s="7" t="n"/>
@@ -7407,7 +6701,6 @@
       <c r="C291" s="7" t="n"/>
       <c r="D291" s="7" t="n"/>
       <c r="E291" s="7" t="n"/>
-      <c r="F291" s="7" t="n"/>
     </row>
     <row r="292">
       <c r="A292" s="7" t="n"/>
@@ -7415,7 +6708,6 @@
       <c r="C292" s="7" t="n"/>
       <c r="D292" s="7" t="n"/>
       <c r="E292" s="7" t="n"/>
-      <c r="F292" s="7" t="n"/>
     </row>
     <row r="293">
       <c r="A293" s="7" t="n"/>
@@ -7423,7 +6715,6 @@
       <c r="C293" s="7" t="n"/>
       <c r="D293" s="7" t="n"/>
       <c r="E293" s="7" t="n"/>
-      <c r="F293" s="7" t="n"/>
     </row>
     <row r="294">
       <c r="A294" s="7" t="n"/>
@@ -7431,7 +6722,6 @@
       <c r="C294" s="7" t="n"/>
       <c r="D294" s="7" t="n"/>
       <c r="E294" s="7" t="n"/>
-      <c r="F294" s="7" t="n"/>
     </row>
     <row r="295">
       <c r="A295" s="7" t="n"/>
@@ -7439,7 +6729,6 @@
       <c r="C295" s="7" t="n"/>
       <c r="D295" s="7" t="n"/>
       <c r="E295" s="7" t="n"/>
-      <c r="F295" s="7" t="n"/>
     </row>
     <row r="296">
       <c r="A296" s="7" t="n"/>
@@ -7447,7 +6736,6 @@
       <c r="C296" s="7" t="n"/>
       <c r="D296" s="7" t="n"/>
       <c r="E296" s="7" t="n"/>
-      <c r="F296" s="7" t="n"/>
     </row>
     <row r="297">
       <c r="A297" s="7" t="n"/>
@@ -7455,7 +6743,6 @@
       <c r="C297" s="7" t="n"/>
       <c r="D297" s="7" t="n"/>
       <c r="E297" s="7" t="n"/>
-      <c r="F297" s="7" t="n"/>
     </row>
     <row r="298">
       <c r="A298" s="7" t="n"/>
@@ -7463,7 +6750,6 @@
       <c r="C298" s="7" t="n"/>
       <c r="D298" s="7" t="n"/>
       <c r="E298" s="7" t="n"/>
-      <c r="F298" s="7" t="n"/>
     </row>
     <row r="299">
       <c r="A299" s="7" t="n"/>
@@ -7471,7 +6757,6 @@
       <c r="C299" s="7" t="n"/>
       <c r="D299" s="7" t="n"/>
       <c r="E299" s="7" t="n"/>
-      <c r="F299" s="7" t="n"/>
     </row>
     <row r="300">
       <c r="A300" s="7" t="n"/>
@@ -7479,7 +6764,6 @@
       <c r="C300" s="7" t="n"/>
       <c r="D300" s="7" t="n"/>
       <c r="E300" s="7" t="n"/>
-      <c r="F300" s="7" t="n"/>
     </row>
     <row r="301">
       <c r="A301" s="7" t="n"/>
@@ -7487,7 +6771,6 @@
       <c r="C301" s="7" t="n"/>
       <c r="D301" s="7" t="n"/>
       <c r="E301" s="7" t="n"/>
-      <c r="F301" s="7" t="n"/>
     </row>
     <row r="302">
       <c r="A302" s="7" t="n"/>
@@ -7495,7 +6778,6 @@
       <c r="C302" s="7" t="n"/>
       <c r="D302" s="7" t="n"/>
       <c r="E302" s="7" t="n"/>
-      <c r="F302" s="7" t="n"/>
     </row>
     <row r="303">
       <c r="A303" s="7" t="n"/>
@@ -7503,7 +6785,6 @@
       <c r="C303" s="7" t="n"/>
       <c r="D303" s="7" t="n"/>
       <c r="E303" s="7" t="n"/>
-      <c r="F303" s="7" t="n"/>
     </row>
     <row r="304">
       <c r="A304" s="7" t="n"/>
@@ -7511,7 +6792,6 @@
       <c r="C304" s="7" t="n"/>
       <c r="D304" s="7" t="n"/>
       <c r="E304" s="7" t="n"/>
-      <c r="F304" s="7" t="n"/>
     </row>
     <row r="305">
       <c r="A305" s="7" t="n"/>
@@ -7519,7 +6799,6 @@
       <c r="C305" s="7" t="n"/>
       <c r="D305" s="7" t="n"/>
       <c r="E305" s="7" t="n"/>
-      <c r="F305" s="7" t="n"/>
     </row>
     <row r="306">
       <c r="A306" s="7" t="n"/>
@@ -7527,7 +6806,6 @@
       <c r="C306" s="7" t="n"/>
       <c r="D306" s="7" t="n"/>
       <c r="E306" s="7" t="n"/>
-      <c r="F306" s="7" t="n"/>
     </row>
     <row r="307">
       <c r="A307" s="7" t="n"/>
@@ -7535,7 +6813,6 @@
       <c r="C307" s="7" t="n"/>
       <c r="D307" s="7" t="n"/>
       <c r="E307" s="7" t="n"/>
-      <c r="F307" s="7" t="n"/>
     </row>
     <row r="308">
       <c r="A308" s="7" t="n"/>
@@ -7543,7 +6820,6 @@
       <c r="C308" s="7" t="n"/>
       <c r="D308" s="7" t="n"/>
       <c r="E308" s="7" t="n"/>
-      <c r="F308" s="7" t="n"/>
     </row>
     <row r="309">
       <c r="A309" s="7" t="n"/>
@@ -7551,7 +6827,6 @@
       <c r="C309" s="7" t="n"/>
       <c r="D309" s="7" t="n"/>
       <c r="E309" s="7" t="n"/>
-      <c r="F309" s="7" t="n"/>
     </row>
     <row r="310">
       <c r="A310" s="7" t="n"/>
@@ -7559,7 +6834,6 @@
       <c r="C310" s="7" t="n"/>
       <c r="D310" s="7" t="n"/>
       <c r="E310" s="7" t="n"/>
-      <c r="F310" s="7" t="n"/>
     </row>
     <row r="311">
       <c r="A311" s="7" t="n"/>
@@ -7567,7 +6841,6 @@
       <c r="C311" s="7" t="n"/>
       <c r="D311" s="7" t="n"/>
       <c r="E311" s="7" t="n"/>
-      <c r="F311" s="7" t="n"/>
     </row>
     <row r="312">
       <c r="A312" s="7" t="n"/>
@@ -7575,7 +6848,6 @@
       <c r="C312" s="7" t="n"/>
       <c r="D312" s="7" t="n"/>
       <c r="E312" s="7" t="n"/>
-      <c r="F312" s="7" t="n"/>
     </row>
     <row r="313">
       <c r="A313" s="7" t="n"/>
@@ -7583,7 +6855,6 @@
       <c r="C313" s="7" t="n"/>
       <c r="D313" s="7" t="n"/>
       <c r="E313" s="7" t="n"/>
-      <c r="F313" s="7" t="n"/>
     </row>
     <row r="314">
       <c r="A314" s="7" t="n"/>
@@ -7591,7 +6862,6 @@
       <c r="C314" s="7" t="n"/>
       <c r="D314" s="7" t="n"/>
       <c r="E314" s="7" t="n"/>
-      <c r="F314" s="7" t="n"/>
     </row>
     <row r="315">
       <c r="A315" s="7" t="n"/>
@@ -7599,7 +6869,6 @@
       <c r="C315" s="7" t="n"/>
       <c r="D315" s="7" t="n"/>
       <c r="E315" s="7" t="n"/>
-      <c r="F315" s="7" t="n"/>
     </row>
     <row r="316">
       <c r="A316" s="7" t="n"/>
@@ -7607,7 +6876,6 @@
       <c r="C316" s="7" t="n"/>
       <c r="D316" s="7" t="n"/>
       <c r="E316" s="7" t="n"/>
-      <c r="F316" s="7" t="n"/>
     </row>
     <row r="317">
       <c r="A317" s="7" t="n"/>
@@ -7615,7 +6883,6 @@
       <c r="C317" s="7" t="n"/>
       <c r="D317" s="7" t="n"/>
       <c r="E317" s="7" t="n"/>
-      <c r="F317" s="7" t="n"/>
     </row>
     <row r="318">
       <c r="A318" s="7" t="n"/>
@@ -7623,7 +6890,6 @@
       <c r="C318" s="7" t="n"/>
       <c r="D318" s="7" t="n"/>
       <c r="E318" s="7" t="n"/>
-      <c r="F318" s="7" t="n"/>
     </row>
     <row r="319">
       <c r="A319" s="7" t="n"/>
@@ -7631,7 +6897,6 @@
       <c r="C319" s="7" t="n"/>
       <c r="D319" s="7" t="n"/>
       <c r="E319" s="7" t="n"/>
-      <c r="F319" s="7" t="n"/>
     </row>
     <row r="320">
       <c r="A320" s="7" t="n"/>
@@ -7639,7 +6904,6 @@
       <c r="C320" s="7" t="n"/>
       <c r="D320" s="7" t="n"/>
       <c r="E320" s="7" t="n"/>
-      <c r="F320" s="7" t="n"/>
     </row>
     <row r="321">
       <c r="A321" s="7" t="n"/>
@@ -7647,7 +6911,6 @@
       <c r="C321" s="7" t="n"/>
       <c r="D321" s="7" t="n"/>
       <c r="E321" s="7" t="n"/>
-      <c r="F321" s="7" t="n"/>
     </row>
     <row r="322">
       <c r="A322" s="7" t="n"/>
@@ -7655,7 +6918,6 @@
       <c r="C322" s="7" t="n"/>
       <c r="D322" s="7" t="n"/>
       <c r="E322" s="7" t="n"/>
-      <c r="F322" s="7" t="n"/>
     </row>
     <row r="323">
       <c r="A323" s="7" t="n"/>
@@ -7663,7 +6925,6 @@
       <c r="C323" s="7" t="n"/>
       <c r="D323" s="7" t="n"/>
       <c r="E323" s="7" t="n"/>
-      <c r="F323" s="7" t="n"/>
     </row>
     <row r="324">
       <c r="A324" s="7" t="n"/>
@@ -7671,7 +6932,6 @@
       <c r="C324" s="7" t="n"/>
       <c r="D324" s="7" t="n"/>
       <c r="E324" s="7" t="n"/>
-      <c r="F324" s="7" t="n"/>
     </row>
     <row r="325">
       <c r="A325" s="7" t="n"/>
@@ -7679,7 +6939,6 @@
       <c r="C325" s="7" t="n"/>
       <c r="D325" s="7" t="n"/>
       <c r="E325" s="7" t="n"/>
-      <c r="F325" s="7" t="n"/>
     </row>
     <row r="326">
       <c r="A326" s="7" t="n"/>
@@ -7687,7 +6946,6 @@
       <c r="C326" s="7" t="n"/>
       <c r="D326" s="7" t="n"/>
       <c r="E326" s="7" t="n"/>
-      <c r="F326" s="7" t="n"/>
     </row>
     <row r="327">
       <c r="A327" s="7" t="n"/>
@@ -7695,7 +6953,6 @@
       <c r="C327" s="7" t="n"/>
       <c r="D327" s="7" t="n"/>
       <c r="E327" s="7" t="n"/>
-      <c r="F327" s="7" t="n"/>
     </row>
     <row r="328">
       <c r="A328" s="7" t="n"/>
@@ -7703,7 +6960,6 @@
       <c r="C328" s="7" t="n"/>
       <c r="D328" s="7" t="n"/>
       <c r="E328" s="7" t="n"/>
-      <c r="F328" s="7" t="n"/>
     </row>
     <row r="329">
       <c r="A329" s="7" t="n"/>
@@ -7711,7 +6967,6 @@
       <c r="C329" s="7" t="n"/>
       <c r="D329" s="7" t="n"/>
       <c r="E329" s="7" t="n"/>
-      <c r="F329" s="7" t="n"/>
     </row>
     <row r="330">
       <c r="A330" s="7" t="n"/>
@@ -7719,7 +6974,6 @@
       <c r="C330" s="7" t="n"/>
       <c r="D330" s="7" t="n"/>
       <c r="E330" s="7" t="n"/>
-      <c r="F330" s="7" t="n"/>
     </row>
     <row r="331">
       <c r="A331" s="7" t="n"/>
@@ -7727,7 +6981,6 @@
       <c r="C331" s="7" t="n"/>
       <c r="D331" s="7" t="n"/>
       <c r="E331" s="7" t="n"/>
-      <c r="F331" s="7" t="n"/>
     </row>
     <row r="332">
       <c r="A332" s="7" t="n"/>
@@ -7735,7 +6988,6 @@
       <c r="C332" s="7" t="n"/>
       <c r="D332" s="7" t="n"/>
       <c r="E332" s="7" t="n"/>
-      <c r="F332" s="7" t="n"/>
     </row>
     <row r="333">
       <c r="A333" s="7" t="n"/>
@@ -7743,7 +6995,6 @@
       <c r="C333" s="7" t="n"/>
       <c r="D333" s="7" t="n"/>
       <c r="E333" s="7" t="n"/>
-      <c r="F333" s="7" t="n"/>
     </row>
     <row r="334">
       <c r="A334" s="7" t="n"/>
@@ -7751,7 +7002,6 @@
       <c r="C334" s="7" t="n"/>
       <c r="D334" s="7" t="n"/>
       <c r="E334" s="7" t="n"/>
-      <c r="F334" s="7" t="n"/>
     </row>
     <row r="335">
       <c r="A335" s="7" t="n"/>
@@ -7759,7 +7009,6 @@
       <c r="C335" s="7" t="n"/>
       <c r="D335" s="7" t="n"/>
       <c r="E335" s="7" t="n"/>
-      <c r="F335" s="7" t="n"/>
     </row>
     <row r="336">
       <c r="A336" s="7" t="n"/>
@@ -7767,7 +7016,6 @@
       <c r="C336" s="7" t="n"/>
       <c r="D336" s="7" t="n"/>
       <c r="E336" s="7" t="n"/>
-      <c r="F336" s="7" t="n"/>
     </row>
     <row r="337">
       <c r="A337" s="7" t="n"/>
@@ -7775,7 +7023,6 @@
       <c r="C337" s="7" t="n"/>
       <c r="D337" s="7" t="n"/>
       <c r="E337" s="7" t="n"/>
-      <c r="F337" s="7" t="n"/>
     </row>
     <row r="338">
       <c r="A338" s="7" t="n"/>
@@ -7783,7 +7030,6 @@
       <c r="C338" s="7" t="n"/>
       <c r="D338" s="7" t="n"/>
       <c r="E338" s="7" t="n"/>
-      <c r="F338" s="7" t="n"/>
     </row>
     <row r="339">
       <c r="A339" s="7" t="n"/>
@@ -7791,7 +7037,6 @@
       <c r="C339" s="7" t="n"/>
       <c r="D339" s="7" t="n"/>
       <c r="E339" s="7" t="n"/>
-      <c r="F339" s="7" t="n"/>
     </row>
     <row r="340">
       <c r="A340" s="7" t="n"/>
@@ -7799,7 +7044,6 @@
       <c r="C340" s="7" t="n"/>
       <c r="D340" s="7" t="n"/>
       <c r="E340" s="7" t="n"/>
-      <c r="F340" s="7" t="n"/>
     </row>
     <row r="341">
       <c r="A341" s="7" t="n"/>
@@ -7807,7 +7051,6 @@
       <c r="C341" s="7" t="n"/>
       <c r="D341" s="7" t="n"/>
       <c r="E341" s="7" t="n"/>
-      <c r="F341" s="7" t="n"/>
     </row>
     <row r="342">
       <c r="A342" s="7" t="n"/>
@@ -7815,7 +7058,6 @@
       <c r="C342" s="7" t="n"/>
       <c r="D342" s="7" t="n"/>
       <c r="E342" s="7" t="n"/>
-      <c r="F342" s="7" t="n"/>
     </row>
     <row r="343">
       <c r="A343" s="7" t="n"/>
@@ -7823,7 +7065,6 @@
       <c r="C343" s="7" t="n"/>
       <c r="D343" s="7" t="n"/>
       <c r="E343" s="7" t="n"/>
-      <c r="F343" s="7" t="n"/>
     </row>
     <row r="344">
       <c r="A344" s="7" t="n"/>
@@ -7831,7 +7072,6 @@
       <c r="C344" s="7" t="n"/>
       <c r="D344" s="7" t="n"/>
       <c r="E344" s="7" t="n"/>
-      <c r="F344" s="7" t="n"/>
     </row>
     <row r="345">
       <c r="A345" s="7" t="n"/>
@@ -7839,7 +7079,6 @@
       <c r="C345" s="7" t="n"/>
       <c r="D345" s="7" t="n"/>
       <c r="E345" s="7" t="n"/>
-      <c r="F345" s="7" t="n"/>
     </row>
     <row r="346">
       <c r="A346" s="7" t="n"/>
@@ -7847,7 +7086,6 @@
       <c r="C346" s="7" t="n"/>
       <c r="D346" s="7" t="n"/>
       <c r="E346" s="7" t="n"/>
-      <c r="F346" s="7" t="n"/>
     </row>
     <row r="347">
       <c r="A347" s="7" t="n"/>
@@ -7855,7 +7093,6 @@
       <c r="C347" s="7" t="n"/>
       <c r="D347" s="7" t="n"/>
       <c r="E347" s="7" t="n"/>
-      <c r="F347" s="7" t="n"/>
     </row>
     <row r="348">
       <c r="A348" s="7" t="n"/>
@@ -7863,7 +7100,6 @@
       <c r="C348" s="7" t="n"/>
       <c r="D348" s="7" t="n"/>
       <c r="E348" s="7" t="n"/>
-      <c r="F348" s="7" t="n"/>
     </row>
     <row r="349">
       <c r="A349" s="7" t="n"/>
@@ -7871,7 +7107,6 @@
       <c r="C349" s="7" t="n"/>
       <c r="D349" s="7" t="n"/>
       <c r="E349" s="7" t="n"/>
-      <c r="F349" s="7" t="n"/>
     </row>
     <row r="350">
       <c r="A350" s="7" t="n"/>
@@ -7879,7 +7114,6 @@
       <c r="C350" s="7" t="n"/>
       <c r="D350" s="7" t="n"/>
       <c r="E350" s="7" t="n"/>
-      <c r="F350" s="7" t="n"/>
     </row>
     <row r="351">
       <c r="A351" s="7" t="n"/>
@@ -7887,7 +7121,6 @@
       <c r="C351" s="7" t="n"/>
       <c r="D351" s="7" t="n"/>
       <c r="E351" s="7" t="n"/>
-      <c r="F351" s="7" t="n"/>
     </row>
     <row r="352">
       <c r="A352" s="7" t="n"/>
@@ -7895,7 +7128,6 @@
       <c r="C352" s="7" t="n"/>
       <c r="D352" s="7" t="n"/>
       <c r="E352" s="7" t="n"/>
-      <c r="F352" s="7" t="n"/>
     </row>
     <row r="353">
       <c r="A353" s="7" t="n"/>
@@ -7903,7 +7135,6 @@
       <c r="C353" s="7" t="n"/>
       <c r="D353" s="7" t="n"/>
       <c r="E353" s="7" t="n"/>
-      <c r="F353" s="7" t="n"/>
     </row>
     <row r="354">
       <c r="A354" s="7" t="n"/>
@@ -7911,7 +7142,6 @@
       <c r="C354" s="7" t="n"/>
       <c r="D354" s="7" t="n"/>
       <c r="E354" s="7" t="n"/>
-      <c r="F354" s="7" t="n"/>
     </row>
     <row r="355">
       <c r="A355" s="7" t="n"/>
@@ -7919,7 +7149,6 @@
       <c r="C355" s="7" t="n"/>
       <c r="D355" s="7" t="n"/>
       <c r="E355" s="7" t="n"/>
-      <c r="F355" s="7" t="n"/>
     </row>
     <row r="356">
       <c r="A356" s="7" t="n"/>
@@ -7927,7 +7156,6 @@
       <c r="C356" s="7" t="n"/>
       <c r="D356" s="7" t="n"/>
       <c r="E356" s="7" t="n"/>
-      <c r="F356" s="7" t="n"/>
     </row>
     <row r="357">
       <c r="A357" s="7" t="n"/>
@@ -7935,7 +7163,6 @@
       <c r="C357" s="7" t="n"/>
       <c r="D357" s="7" t="n"/>
       <c r="E357" s="7" t="n"/>
-      <c r="F357" s="7" t="n"/>
     </row>
     <row r="358">
       <c r="A358" s="7" t="n"/>
@@ -7943,7 +7170,6 @@
       <c r="C358" s="7" t="n"/>
       <c r="D358" s="7" t="n"/>
       <c r="E358" s="7" t="n"/>
-      <c r="F358" s="7" t="n"/>
     </row>
     <row r="359">
       <c r="A359" s="7" t="n"/>
@@ -7951,7 +7177,6 @@
       <c r="C359" s="7" t="n"/>
       <c r="D359" s="7" t="n"/>
       <c r="E359" s="7" t="n"/>
-      <c r="F359" s="7" t="n"/>
     </row>
     <row r="360">
       <c r="A360" s="7" t="n"/>
@@ -7959,7 +7184,6 @@
       <c r="C360" s="7" t="n"/>
       <c r="D360" s="7" t="n"/>
       <c r="E360" s="7" t="n"/>
-      <c r="F360" s="7" t="n"/>
     </row>
     <row r="361">
       <c r="A361" s="7" t="n"/>
@@ -7967,7 +7191,6 @@
       <c r="C361" s="7" t="n"/>
       <c r="D361" s="7" t="n"/>
       <c r="E361" s="7" t="n"/>
-      <c r="F361" s="7" t="n"/>
     </row>
     <row r="362">
       <c r="A362" s="7" t="n"/>
@@ -7975,7 +7198,6 @@
       <c r="C362" s="7" t="n"/>
       <c r="D362" s="7" t="n"/>
       <c r="E362" s="7" t="n"/>
-      <c r="F362" s="7" t="n"/>
     </row>
     <row r="363">
       <c r="A363" s="7" t="n"/>
@@ -7983,7 +7205,6 @@
       <c r="C363" s="7" t="n"/>
       <c r="D363" s="7" t="n"/>
       <c r="E363" s="7" t="n"/>
-      <c r="F363" s="7" t="n"/>
     </row>
     <row r="364">
       <c r="A364" s="7" t="n"/>
@@ -7991,7 +7212,6 @@
       <c r="C364" s="7" t="n"/>
       <c r="D364" s="7" t="n"/>
       <c r="E364" s="7" t="n"/>
-      <c r="F364" s="7" t="n"/>
     </row>
     <row r="365">
       <c r="A365" s="7" t="n"/>
@@ -7999,7 +7219,6 @@
       <c r="C365" s="7" t="n"/>
       <c r="D365" s="7" t="n"/>
       <c r="E365" s="7" t="n"/>
-      <c r="F365" s="7" t="n"/>
     </row>
     <row r="366">
       <c r="A366" s="7" t="n"/>
@@ -8007,7 +7226,6 @@
       <c r="C366" s="7" t="n"/>
       <c r="D366" s="7" t="n"/>
       <c r="E366" s="7" t="n"/>
-      <c r="F366" s="7" t="n"/>
     </row>
     <row r="367">
       <c r="A367" s="7" t="n"/>
@@ -8015,7 +7233,6 @@
       <c r="C367" s="7" t="n"/>
       <c r="D367" s="7" t="n"/>
       <c r="E367" s="7" t="n"/>
-      <c r="F367" s="7" t="n"/>
     </row>
     <row r="368">
       <c r="A368" s="7" t="n"/>
@@ -8023,7 +7240,6 @@
       <c r="C368" s="7" t="n"/>
       <c r="D368" s="7" t="n"/>
       <c r="E368" s="7" t="n"/>
-      <c r="F368" s="7" t="n"/>
     </row>
     <row r="369">
       <c r="A369" s="7" t="n"/>
@@ -8031,7 +7247,6 @@
       <c r="C369" s="7" t="n"/>
       <c r="D369" s="7" t="n"/>
       <c r="E369" s="7" t="n"/>
-      <c r="F369" s="7" t="n"/>
     </row>
     <row r="370">
       <c r="A370" s="7" t="n"/>
@@ -8039,7 +7254,6 @@
       <c r="C370" s="7" t="n"/>
       <c r="D370" s="7" t="n"/>
       <c r="E370" s="7" t="n"/>
-      <c r="F370" s="7" t="n"/>
     </row>
     <row r="371">
       <c r="A371" s="7" t="n"/>
@@ -8047,7 +7261,6 @@
       <c r="C371" s="7" t="n"/>
       <c r="D371" s="7" t="n"/>
       <c r="E371" s="7" t="n"/>
-      <c r="F371" s="7" t="n"/>
     </row>
     <row r="372">
       <c r="A372" s="7" t="n"/>
@@ -8055,7 +7268,6 @@
       <c r="C372" s="7" t="n"/>
       <c r="D372" s="7" t="n"/>
       <c r="E372" s="7" t="n"/>
-      <c r="F372" s="7" t="n"/>
     </row>
     <row r="373">
       <c r="A373" s="7" t="n"/>
@@ -8063,7 +7275,6 @@
       <c r="C373" s="7" t="n"/>
       <c r="D373" s="7" t="n"/>
       <c r="E373" s="7" t="n"/>
-      <c r="F373" s="7" t="n"/>
     </row>
     <row r="374">
       <c r="A374" s="7" t="n"/>
@@ -8071,7 +7282,6 @@
       <c r="C374" s="7" t="n"/>
       <c r="D374" s="7" t="n"/>
       <c r="E374" s="7" t="n"/>
-      <c r="F374" s="7" t="n"/>
     </row>
     <row r="375">
       <c r="A375" s="7" t="n"/>
@@ -8079,7 +7289,6 @@
       <c r="C375" s="7" t="n"/>
       <c r="D375" s="7" t="n"/>
       <c r="E375" s="7" t="n"/>
-      <c r="F375" s="7" t="n"/>
     </row>
     <row r="376">
       <c r="A376" s="7" t="n"/>
@@ -8087,7 +7296,6 @@
       <c r="C376" s="7" t="n"/>
       <c r="D376" s="7" t="n"/>
       <c r="E376" s="7" t="n"/>
-      <c r="F376" s="7" t="n"/>
     </row>
     <row r="377">
       <c r="A377" s="7" t="n"/>
@@ -8095,7 +7303,6 @@
       <c r="C377" s="7" t="n"/>
       <c r="D377" s="7" t="n"/>
       <c r="E377" s="7" t="n"/>
-      <c r="F377" s="7" t="n"/>
     </row>
     <row r="378">
       <c r="A378" s="7" t="n"/>
@@ -8103,7 +7310,6 @@
       <c r="C378" s="7" t="n"/>
       <c r="D378" s="7" t="n"/>
       <c r="E378" s="7" t="n"/>
-      <c r="F378" s="7" t="n"/>
     </row>
     <row r="379">
       <c r="A379" s="7" t="n"/>
@@ -8111,7 +7317,6 @@
       <c r="C379" s="7" t="n"/>
       <c r="D379" s="7" t="n"/>
       <c r="E379" s="7" t="n"/>
-      <c r="F379" s="7" t="n"/>
     </row>
     <row r="380">
       <c r="A380" s="7" t="n"/>
@@ -8119,7 +7324,6 @@
       <c r="C380" s="7" t="n"/>
       <c r="D380" s="7" t="n"/>
       <c r="E380" s="7" t="n"/>
-      <c r="F380" s="7" t="n"/>
     </row>
     <row r="381">
       <c r="A381" s="7" t="n"/>
@@ -8127,7 +7331,6 @@
       <c r="C381" s="7" t="n"/>
       <c r="D381" s="7" t="n"/>
       <c r="E381" s="7" t="n"/>
-      <c r="F381" s="7" t="n"/>
     </row>
     <row r="382">
       <c r="A382" s="7" t="n"/>
@@ -8135,7 +7338,6 @@
       <c r="C382" s="7" t="n"/>
       <c r="D382" s="7" t="n"/>
       <c r="E382" s="7" t="n"/>
-      <c r="F382" s="7" t="n"/>
     </row>
     <row r="383">
       <c r="A383" s="7" t="n"/>
@@ -8143,7 +7345,6 @@
       <c r="C383" s="7" t="n"/>
       <c r="D383" s="7" t="n"/>
       <c r="E383" s="7" t="n"/>
-      <c r="F383" s="7" t="n"/>
     </row>
     <row r="384">
       <c r="A384" s="7" t="n"/>
@@ -8151,7 +7352,6 @@
       <c r="C384" s="7" t="n"/>
       <c r="D384" s="7" t="n"/>
       <c r="E384" s="7" t="n"/>
-      <c r="F384" s="7" t="n"/>
     </row>
     <row r="385">
       <c r="A385" s="7" t="n"/>
@@ -8159,7 +7359,6 @@
       <c r="C385" s="7" t="n"/>
       <c r="D385" s="7" t="n"/>
       <c r="E385" s="7" t="n"/>
-      <c r="F385" s="7" t="n"/>
     </row>
     <row r="386">
       <c r="A386" s="7" t="n"/>
@@ -8167,7 +7366,6 @@
       <c r="C386" s="7" t="n"/>
       <c r="D386" s="7" t="n"/>
       <c r="E386" s="7" t="n"/>
-      <c r="F386" s="7" t="n"/>
     </row>
     <row r="387">
       <c r="A387" s="7" t="n"/>
@@ -8175,7 +7373,6 @@
       <c r="C387" s="7" t="n"/>
       <c r="D387" s="7" t="n"/>
       <c r="E387" s="7" t="n"/>
-      <c r="F387" s="7" t="n"/>
     </row>
     <row r="388">
       <c r="A388" s="7" t="n"/>
@@ -8183,7 +7380,6 @@
       <c r="C388" s="7" t="n"/>
       <c r="D388" s="7" t="n"/>
       <c r="E388" s="7" t="n"/>
-      <c r="F388" s="7" t="n"/>
     </row>
     <row r="389">
       <c r="A389" s="7" t="n"/>
@@ -8191,7 +7387,6 @@
       <c r="C389" s="7" t="n"/>
       <c r="D389" s="7" t="n"/>
       <c r="E389" s="7" t="n"/>
-      <c r="F389" s="7" t="n"/>
     </row>
     <row r="390">
       <c r="A390" s="7" t="n"/>
@@ -8199,7 +7394,6 @@
       <c r="C390" s="7" t="n"/>
       <c r="D390" s="7" t="n"/>
       <c r="E390" s="7" t="n"/>
-      <c r="F390" s="7" t="n"/>
     </row>
     <row r="391">
       <c r="A391" s="7" t="n"/>
@@ -8207,7 +7401,6 @@
       <c r="C391" s="7" t="n"/>
       <c r="D391" s="7" t="n"/>
       <c r="E391" s="7" t="n"/>
-      <c r="F391" s="7" t="n"/>
     </row>
     <row r="392">
       <c r="A392" s="7" t="n"/>
@@ -8215,7 +7408,6 @@
       <c r="C392" s="7" t="n"/>
       <c r="D392" s="7" t="n"/>
       <c r="E392" s="7" t="n"/>
-      <c r="F392" s="7" t="n"/>
     </row>
     <row r="393">
       <c r="A393" s="7" t="n"/>
@@ -8223,7 +7415,6 @@
       <c r="C393" s="7" t="n"/>
       <c r="D393" s="7" t="n"/>
       <c r="E393" s="7" t="n"/>
-      <c r="F393" s="7" t="n"/>
     </row>
     <row r="394">
       <c r="A394" s="7" t="n"/>
@@ -8231,7 +7422,6 @@
       <c r="C394" s="7" t="n"/>
       <c r="D394" s="7" t="n"/>
       <c r="E394" s="7" t="n"/>
-      <c r="F394" s="7" t="n"/>
     </row>
     <row r="395">
       <c r="A395" s="7" t="n"/>
@@ -8239,7 +7429,6 @@
       <c r="C395" s="7" t="n"/>
       <c r="D395" s="7" t="n"/>
       <c r="E395" s="7" t="n"/>
-      <c r="F395" s="7" t="n"/>
     </row>
     <row r="396">
       <c r="A396" s="7" t="n"/>
@@ -8247,7 +7436,6 @@
       <c r="C396" s="7" t="n"/>
       <c r="D396" s="7" t="n"/>
       <c r="E396" s="7" t="n"/>
-      <c r="F396" s="7" t="n"/>
     </row>
     <row r="397">
       <c r="A397" s="7" t="n"/>
@@ -8255,7 +7443,6 @@
       <c r="C397" s="7" t="n"/>
       <c r="D397" s="7" t="n"/>
       <c r="E397" s="7" t="n"/>
-      <c r="F397" s="7" t="n"/>
     </row>
     <row r="398">
       <c r="A398" s="7" t="n"/>
@@ -8263,7 +7450,6 @@
       <c r="C398" s="7" t="n"/>
       <c r="D398" s="7" t="n"/>
       <c r="E398" s="7" t="n"/>
-      <c r="F398" s="7" t="n"/>
     </row>
     <row r="399">
       <c r="A399" s="7" t="n"/>
@@ -8271,7 +7457,6 @@
       <c r="C399" s="7" t="n"/>
       <c r="D399" s="7" t="n"/>
       <c r="E399" s="7" t="n"/>
-      <c r="F399" s="7" t="n"/>
     </row>
     <row r="400">
       <c r="A400" s="7" t="n"/>
@@ -8279,7 +7464,6 @@
       <c r="C400" s="7" t="n"/>
       <c r="D400" s="7" t="n"/>
       <c r="E400" s="7" t="n"/>
-      <c r="F400" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -8298,13 +7482,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M120"/>
+  <dimension ref="A1:L120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -8397,11 +7581,6 @@
           <t>Sam matin</t>
         </is>
       </c>
-      <c r="M3" s="12" t="inlineStr">
-        <is>
-          <t>Précisions (horaires exacts…)</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
@@ -8464,11 +7643,6 @@
           <t>NON</t>
         </is>
       </c>
-      <c r="M4" s="16" t="inlineStr">
-        <is>
-          <t>Mercredi : cours dans un autre établissement</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="16" t="inlineStr">
@@ -8531,11 +7705,6 @@
           <t>NON</t>
         </is>
       </c>
-      <c r="M5" s="16" t="inlineStr">
-        <is>
-          <t>Lundi et jeudi après-midi : autre école</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="16" t="inlineStr">
@@ -8598,11 +7767,6 @@
           <t>NON</t>
         </is>
       </c>
-      <c r="M6" s="16" t="inlineStr">
-        <is>
-          <t>Lundi et vendredi : université d'Abidjan</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="16" t="inlineStr">
@@ -8665,11 +7829,6 @@
           <t>NON</t>
         </is>
       </c>
-      <c r="M7" s="16" t="inlineStr">
-        <is>
-          <t>Mardi : formation à la DREN</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="16" t="inlineStr">
@@ -8730,11 +7889,6 @@
       <c r="L8" s="16" t="inlineStr">
         <is>
           <t>NON</t>
-        </is>
-      </c>
-      <c r="M8" s="16" t="inlineStr">
-        <is>
-          <t>Mercredi : chorale paroissiale / Vendredi AM : autre école</t>
         </is>
       </c>
     </row>
@@ -8751,7 +7905,6 @@
       <c r="J9" s="7" t="n"/>
       <c r="K9" s="7" t="n"/>
       <c r="L9" s="7" t="n"/>
-      <c r="M9" s="7" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n"/>
@@ -8766,7 +7919,6 @@
       <c r="J10" s="7" t="n"/>
       <c r="K10" s="7" t="n"/>
       <c r="L10" s="7" t="n"/>
-      <c r="M10" s="7" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n"/>
@@ -8781,7 +7933,6 @@
       <c r="J11" s="7" t="n"/>
       <c r="K11" s="7" t="n"/>
       <c r="L11" s="7" t="n"/>
-      <c r="M11" s="7" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n"/>
@@ -8796,7 +7947,6 @@
       <c r="J12" s="7" t="n"/>
       <c r="K12" s="7" t="n"/>
       <c r="L12" s="7" t="n"/>
-      <c r="M12" s="7" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n"/>
@@ -8811,7 +7961,6 @@
       <c r="J13" s="7" t="n"/>
       <c r="K13" s="7" t="n"/>
       <c r="L13" s="7" t="n"/>
-      <c r="M13" s="7" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n"/>
@@ -8826,7 +7975,6 @@
       <c r="J14" s="7" t="n"/>
       <c r="K14" s="7" t="n"/>
       <c r="L14" s="7" t="n"/>
-      <c r="M14" s="7" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n"/>
@@ -8841,7 +7989,6 @@
       <c r="J15" s="7" t="n"/>
       <c r="K15" s="7" t="n"/>
       <c r="L15" s="7" t="n"/>
-      <c r="M15" s="7" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n"/>
@@ -8856,7 +8003,6 @@
       <c r="J16" s="7" t="n"/>
       <c r="K16" s="7" t="n"/>
       <c r="L16" s="7" t="n"/>
-      <c r="M16" s="7" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n"/>
@@ -8871,7 +8017,6 @@
       <c r="J17" s="7" t="n"/>
       <c r="K17" s="7" t="n"/>
       <c r="L17" s="7" t="n"/>
-      <c r="M17" s="7" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n"/>
@@ -8886,7 +8031,6 @@
       <c r="J18" s="7" t="n"/>
       <c r="K18" s="7" t="n"/>
       <c r="L18" s="7" t="n"/>
-      <c r="M18" s="7" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n"/>
@@ -8901,7 +8045,6 @@
       <c r="J19" s="7" t="n"/>
       <c r="K19" s="7" t="n"/>
       <c r="L19" s="7" t="n"/>
-      <c r="M19" s="7" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n"/>
@@ -8916,7 +8059,6 @@
       <c r="J20" s="7" t="n"/>
       <c r="K20" s="7" t="n"/>
       <c r="L20" s="7" t="n"/>
-      <c r="M20" s="7" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n"/>
@@ -8931,7 +8073,6 @@
       <c r="J21" s="7" t="n"/>
       <c r="K21" s="7" t="n"/>
       <c r="L21" s="7" t="n"/>
-      <c r="M21" s="7" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n"/>
@@ -8946,7 +8087,6 @@
       <c r="J22" s="7" t="n"/>
       <c r="K22" s="7" t="n"/>
       <c r="L22" s="7" t="n"/>
-      <c r="M22" s="7" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n"/>
@@ -8961,7 +8101,6 @@
       <c r="J23" s="7" t="n"/>
       <c r="K23" s="7" t="n"/>
       <c r="L23" s="7" t="n"/>
-      <c r="M23" s="7" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n"/>
@@ -8976,7 +8115,6 @@
       <c r="J24" s="7" t="n"/>
       <c r="K24" s="7" t="n"/>
       <c r="L24" s="7" t="n"/>
-      <c r="M24" s="7" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n"/>
@@ -8991,7 +8129,6 @@
       <c r="J25" s="7" t="n"/>
       <c r="K25" s="7" t="n"/>
       <c r="L25" s="7" t="n"/>
-      <c r="M25" s="7" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n"/>
@@ -9006,7 +8143,6 @@
       <c r="J26" s="7" t="n"/>
       <c r="K26" s="7" t="n"/>
       <c r="L26" s="7" t="n"/>
-      <c r="M26" s="7" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n"/>
@@ -9021,7 +8157,6 @@
       <c r="J27" s="7" t="n"/>
       <c r="K27" s="7" t="n"/>
       <c r="L27" s="7" t="n"/>
-      <c r="M27" s="7" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n"/>
@@ -9036,7 +8171,6 @@
       <c r="J28" s="7" t="n"/>
       <c r="K28" s="7" t="n"/>
       <c r="L28" s="7" t="n"/>
-      <c r="M28" s="7" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n"/>
@@ -9051,7 +8185,6 @@
       <c r="J29" s="7" t="n"/>
       <c r="K29" s="7" t="n"/>
       <c r="L29" s="7" t="n"/>
-      <c r="M29" s="7" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n"/>
@@ -9066,7 +8199,6 @@
       <c r="J30" s="7" t="n"/>
       <c r="K30" s="7" t="n"/>
       <c r="L30" s="7" t="n"/>
-      <c r="M30" s="7" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n"/>
@@ -9081,7 +8213,6 @@
       <c r="J31" s="7" t="n"/>
       <c r="K31" s="7" t="n"/>
       <c r="L31" s="7" t="n"/>
-      <c r="M31" s="7" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n"/>
@@ -9096,7 +8227,6 @@
       <c r="J32" s="7" t="n"/>
       <c r="K32" s="7" t="n"/>
       <c r="L32" s="7" t="n"/>
-      <c r="M32" s="7" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n"/>
@@ -9111,7 +8241,6 @@
       <c r="J33" s="7" t="n"/>
       <c r="K33" s="7" t="n"/>
       <c r="L33" s="7" t="n"/>
-      <c r="M33" s="7" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n"/>
@@ -9126,7 +8255,6 @@
       <c r="J34" s="7" t="n"/>
       <c r="K34" s="7" t="n"/>
       <c r="L34" s="7" t="n"/>
-      <c r="M34" s="7" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n"/>
@@ -9141,7 +8269,6 @@
       <c r="J35" s="7" t="n"/>
       <c r="K35" s="7" t="n"/>
       <c r="L35" s="7" t="n"/>
-      <c r="M35" s="7" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n"/>
@@ -9156,7 +8283,6 @@
       <c r="J36" s="7" t="n"/>
       <c r="K36" s="7" t="n"/>
       <c r="L36" s="7" t="n"/>
-      <c r="M36" s="7" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n"/>
@@ -9171,7 +8297,6 @@
       <c r="J37" s="7" t="n"/>
       <c r="K37" s="7" t="n"/>
       <c r="L37" s="7" t="n"/>
-      <c r="M37" s="7" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n"/>
@@ -9186,7 +8311,6 @@
       <c r="J38" s="7" t="n"/>
       <c r="K38" s="7" t="n"/>
       <c r="L38" s="7" t="n"/>
-      <c r="M38" s="7" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n"/>
@@ -9201,7 +8325,6 @@
       <c r="J39" s="7" t="n"/>
       <c r="K39" s="7" t="n"/>
       <c r="L39" s="7" t="n"/>
-      <c r="M39" s="7" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n"/>
@@ -9216,7 +8339,6 @@
       <c r="J40" s="7" t="n"/>
       <c r="K40" s="7" t="n"/>
       <c r="L40" s="7" t="n"/>
-      <c r="M40" s="7" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n"/>
@@ -9231,7 +8353,6 @@
       <c r="J41" s="7" t="n"/>
       <c r="K41" s="7" t="n"/>
       <c r="L41" s="7" t="n"/>
-      <c r="M41" s="7" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n"/>
@@ -9246,7 +8367,6 @@
       <c r="J42" s="7" t="n"/>
       <c r="K42" s="7" t="n"/>
       <c r="L42" s="7" t="n"/>
-      <c r="M42" s="7" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n"/>
@@ -9261,7 +8381,6 @@
       <c r="J43" s="7" t="n"/>
       <c r="K43" s="7" t="n"/>
       <c r="L43" s="7" t="n"/>
-      <c r="M43" s="7" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n"/>
@@ -9276,7 +8395,6 @@
       <c r="J44" s="7" t="n"/>
       <c r="K44" s="7" t="n"/>
       <c r="L44" s="7" t="n"/>
-      <c r="M44" s="7" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n"/>
@@ -9291,7 +8409,6 @@
       <c r="J45" s="7" t="n"/>
       <c r="K45" s="7" t="n"/>
       <c r="L45" s="7" t="n"/>
-      <c r="M45" s="7" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n"/>
@@ -9306,7 +8423,6 @@
       <c r="J46" s="7" t="n"/>
       <c r="K46" s="7" t="n"/>
       <c r="L46" s="7" t="n"/>
-      <c r="M46" s="7" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n"/>
@@ -9321,7 +8437,6 @@
       <c r="J47" s="7" t="n"/>
       <c r="K47" s="7" t="n"/>
       <c r="L47" s="7" t="n"/>
-      <c r="M47" s="7" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n"/>
@@ -9336,7 +8451,6 @@
       <c r="J48" s="7" t="n"/>
       <c r="K48" s="7" t="n"/>
       <c r="L48" s="7" t="n"/>
-      <c r="M48" s="7" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n"/>
@@ -9351,7 +8465,6 @@
       <c r="J49" s="7" t="n"/>
       <c r="K49" s="7" t="n"/>
       <c r="L49" s="7" t="n"/>
-      <c r="M49" s="7" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n"/>
@@ -9366,7 +8479,6 @@
       <c r="J50" s="7" t="n"/>
       <c r="K50" s="7" t="n"/>
       <c r="L50" s="7" t="n"/>
-      <c r="M50" s="7" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n"/>
@@ -9381,7 +8493,6 @@
       <c r="J51" s="7" t="n"/>
       <c r="K51" s="7" t="n"/>
       <c r="L51" s="7" t="n"/>
-      <c r="M51" s="7" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n"/>
@@ -9396,7 +8507,6 @@
       <c r="J52" s="7" t="n"/>
       <c r="K52" s="7" t="n"/>
       <c r="L52" s="7" t="n"/>
-      <c r="M52" s="7" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n"/>
@@ -9411,7 +8521,6 @@
       <c r="J53" s="7" t="n"/>
       <c r="K53" s="7" t="n"/>
       <c r="L53" s="7" t="n"/>
-      <c r="M53" s="7" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n"/>
@@ -9426,7 +8535,6 @@
       <c r="J54" s="7" t="n"/>
       <c r="K54" s="7" t="n"/>
       <c r="L54" s="7" t="n"/>
-      <c r="M54" s="7" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n"/>
@@ -9441,7 +8549,6 @@
       <c r="J55" s="7" t="n"/>
       <c r="K55" s="7" t="n"/>
       <c r="L55" s="7" t="n"/>
-      <c r="M55" s="7" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n"/>
@@ -9456,7 +8563,6 @@
       <c r="J56" s="7" t="n"/>
       <c r="K56" s="7" t="n"/>
       <c r="L56" s="7" t="n"/>
-      <c r="M56" s="7" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n"/>
@@ -9471,7 +8577,6 @@
       <c r="J57" s="7" t="n"/>
       <c r="K57" s="7" t="n"/>
       <c r="L57" s="7" t="n"/>
-      <c r="M57" s="7" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n"/>
@@ -9486,7 +8591,6 @@
       <c r="J58" s="7" t="n"/>
       <c r="K58" s="7" t="n"/>
       <c r="L58" s="7" t="n"/>
-      <c r="M58" s="7" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="7" t="n"/>
@@ -9501,7 +8605,6 @@
       <c r="J59" s="7" t="n"/>
       <c r="K59" s="7" t="n"/>
       <c r="L59" s="7" t="n"/>
-      <c r="M59" s="7" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n"/>
@@ -9516,7 +8619,6 @@
       <c r="J60" s="7" t="n"/>
       <c r="K60" s="7" t="n"/>
       <c r="L60" s="7" t="n"/>
-      <c r="M60" s="7" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="7" t="n"/>
@@ -9531,7 +8633,6 @@
       <c r="J61" s="7" t="n"/>
       <c r="K61" s="7" t="n"/>
       <c r="L61" s="7" t="n"/>
-      <c r="M61" s="7" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n"/>
@@ -9546,7 +8647,6 @@
       <c r="J62" s="7" t="n"/>
       <c r="K62" s="7" t="n"/>
       <c r="L62" s="7" t="n"/>
-      <c r="M62" s="7" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n"/>
@@ -9561,7 +8661,6 @@
       <c r="J63" s="7" t="n"/>
       <c r="K63" s="7" t="n"/>
       <c r="L63" s="7" t="n"/>
-      <c r="M63" s="7" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n"/>
@@ -9576,7 +8675,6 @@
       <c r="J64" s="7" t="n"/>
       <c r="K64" s="7" t="n"/>
       <c r="L64" s="7" t="n"/>
-      <c r="M64" s="7" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n"/>
@@ -9591,7 +8689,6 @@
       <c r="J65" s="7" t="n"/>
       <c r="K65" s="7" t="n"/>
       <c r="L65" s="7" t="n"/>
-      <c r="M65" s="7" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n"/>
@@ -9606,7 +8703,6 @@
       <c r="J66" s="7" t="n"/>
       <c r="K66" s="7" t="n"/>
       <c r="L66" s="7" t="n"/>
-      <c r="M66" s="7" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n"/>
@@ -9621,7 +8717,6 @@
       <c r="J67" s="7" t="n"/>
       <c r="K67" s="7" t="n"/>
       <c r="L67" s="7" t="n"/>
-      <c r="M67" s="7" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n"/>
@@ -9636,7 +8731,6 @@
       <c r="J68" s="7" t="n"/>
       <c r="K68" s="7" t="n"/>
       <c r="L68" s="7" t="n"/>
-      <c r="M68" s="7" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n"/>
@@ -9651,7 +8745,6 @@
       <c r="J69" s="7" t="n"/>
       <c r="K69" s="7" t="n"/>
       <c r="L69" s="7" t="n"/>
-      <c r="M69" s="7" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n"/>
@@ -9666,7 +8759,6 @@
       <c r="J70" s="7" t="n"/>
       <c r="K70" s="7" t="n"/>
       <c r="L70" s="7" t="n"/>
-      <c r="M70" s="7" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="7" t="n"/>
@@ -9681,7 +8773,6 @@
       <c r="J71" s="7" t="n"/>
       <c r="K71" s="7" t="n"/>
       <c r="L71" s="7" t="n"/>
-      <c r="M71" s="7" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="7" t="n"/>
@@ -9696,7 +8787,6 @@
       <c r="J72" s="7" t="n"/>
       <c r="K72" s="7" t="n"/>
       <c r="L72" s="7" t="n"/>
-      <c r="M72" s="7" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="7" t="n"/>
@@ -9711,7 +8801,6 @@
       <c r="J73" s="7" t="n"/>
       <c r="K73" s="7" t="n"/>
       <c r="L73" s="7" t="n"/>
-      <c r="M73" s="7" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n"/>
@@ -9726,7 +8815,6 @@
       <c r="J74" s="7" t="n"/>
       <c r="K74" s="7" t="n"/>
       <c r="L74" s="7" t="n"/>
-      <c r="M74" s="7" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="7" t="n"/>
@@ -9741,7 +8829,6 @@
       <c r="J75" s="7" t="n"/>
       <c r="K75" s="7" t="n"/>
       <c r="L75" s="7" t="n"/>
-      <c r="M75" s="7" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n"/>
@@ -9756,7 +8843,6 @@
       <c r="J76" s="7" t="n"/>
       <c r="K76" s="7" t="n"/>
       <c r="L76" s="7" t="n"/>
-      <c r="M76" s="7" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="7" t="n"/>
@@ -9771,7 +8857,6 @@
       <c r="J77" s="7" t="n"/>
       <c r="K77" s="7" t="n"/>
       <c r="L77" s="7" t="n"/>
-      <c r="M77" s="7" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n"/>
@@ -9786,7 +8871,6 @@
       <c r="J78" s="7" t="n"/>
       <c r="K78" s="7" t="n"/>
       <c r="L78" s="7" t="n"/>
-      <c r="M78" s="7" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="7" t="n"/>
@@ -9801,7 +8885,6 @@
       <c r="J79" s="7" t="n"/>
       <c r="K79" s="7" t="n"/>
       <c r="L79" s="7" t="n"/>
-      <c r="M79" s="7" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="7" t="n"/>
@@ -9816,7 +8899,6 @@
       <c r="J80" s="7" t="n"/>
       <c r="K80" s="7" t="n"/>
       <c r="L80" s="7" t="n"/>
-      <c r="M80" s="7" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="7" t="n"/>
@@ -9831,7 +8913,6 @@
       <c r="J81" s="7" t="n"/>
       <c r="K81" s="7" t="n"/>
       <c r="L81" s="7" t="n"/>
-      <c r="M81" s="7" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="7" t="n"/>
@@ -9846,7 +8927,6 @@
       <c r="J82" s="7" t="n"/>
       <c r="K82" s="7" t="n"/>
       <c r="L82" s="7" t="n"/>
-      <c r="M82" s="7" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="7" t="n"/>
@@ -9861,7 +8941,6 @@
       <c r="J83" s="7" t="n"/>
       <c r="K83" s="7" t="n"/>
       <c r="L83" s="7" t="n"/>
-      <c r="M83" s="7" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="7" t="n"/>
@@ -9876,7 +8955,6 @@
       <c r="J84" s="7" t="n"/>
       <c r="K84" s="7" t="n"/>
       <c r="L84" s="7" t="n"/>
-      <c r="M84" s="7" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="7" t="n"/>
@@ -9891,7 +8969,6 @@
       <c r="J85" s="7" t="n"/>
       <c r="K85" s="7" t="n"/>
       <c r="L85" s="7" t="n"/>
-      <c r="M85" s="7" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="7" t="n"/>
@@ -9906,7 +8983,6 @@
       <c r="J86" s="7" t="n"/>
       <c r="K86" s="7" t="n"/>
       <c r="L86" s="7" t="n"/>
-      <c r="M86" s="7" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="7" t="n"/>
@@ -9921,7 +8997,6 @@
       <c r="J87" s="7" t="n"/>
       <c r="K87" s="7" t="n"/>
       <c r="L87" s="7" t="n"/>
-      <c r="M87" s="7" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="7" t="n"/>
@@ -9936,7 +9011,6 @@
       <c r="J88" s="7" t="n"/>
       <c r="K88" s="7" t="n"/>
       <c r="L88" s="7" t="n"/>
-      <c r="M88" s="7" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="7" t="n"/>
@@ -9951,7 +9025,6 @@
       <c r="J89" s="7" t="n"/>
       <c r="K89" s="7" t="n"/>
       <c r="L89" s="7" t="n"/>
-      <c r="M89" s="7" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="7" t="n"/>
@@ -9966,7 +9039,6 @@
       <c r="J90" s="7" t="n"/>
       <c r="K90" s="7" t="n"/>
       <c r="L90" s="7" t="n"/>
-      <c r="M90" s="7" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="7" t="n"/>
@@ -9981,7 +9053,6 @@
       <c r="J91" s="7" t="n"/>
       <c r="K91" s="7" t="n"/>
       <c r="L91" s="7" t="n"/>
-      <c r="M91" s="7" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="7" t="n"/>
@@ -9996,7 +9067,6 @@
       <c r="J92" s="7" t="n"/>
       <c r="K92" s="7" t="n"/>
       <c r="L92" s="7" t="n"/>
-      <c r="M92" s="7" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="7" t="n"/>
@@ -10011,7 +9081,6 @@
       <c r="J93" s="7" t="n"/>
       <c r="K93" s="7" t="n"/>
       <c r="L93" s="7" t="n"/>
-      <c r="M93" s="7" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="7" t="n"/>
@@ -10026,7 +9095,6 @@
       <c r="J94" s="7" t="n"/>
       <c r="K94" s="7" t="n"/>
       <c r="L94" s="7" t="n"/>
-      <c r="M94" s="7" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="7" t="n"/>
@@ -10041,7 +9109,6 @@
       <c r="J95" s="7" t="n"/>
       <c r="K95" s="7" t="n"/>
       <c r="L95" s="7" t="n"/>
-      <c r="M95" s="7" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="7" t="n"/>
@@ -10056,7 +9123,6 @@
       <c r="J96" s="7" t="n"/>
       <c r="K96" s="7" t="n"/>
       <c r="L96" s="7" t="n"/>
-      <c r="M96" s="7" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="7" t="n"/>
@@ -10071,7 +9137,6 @@
       <c r="J97" s="7" t="n"/>
       <c r="K97" s="7" t="n"/>
       <c r="L97" s="7" t="n"/>
-      <c r="M97" s="7" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="7" t="n"/>
@@ -10086,7 +9151,6 @@
       <c r="J98" s="7" t="n"/>
       <c r="K98" s="7" t="n"/>
       <c r="L98" s="7" t="n"/>
-      <c r="M98" s="7" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="7" t="n"/>
@@ -10101,7 +9165,6 @@
       <c r="J99" s="7" t="n"/>
       <c r="K99" s="7" t="n"/>
       <c r="L99" s="7" t="n"/>
-      <c r="M99" s="7" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="7" t="n"/>
@@ -10116,7 +9179,6 @@
       <c r="J100" s="7" t="n"/>
       <c r="K100" s="7" t="n"/>
       <c r="L100" s="7" t="n"/>
-      <c r="M100" s="7" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="7" t="n"/>
@@ -10131,7 +9193,6 @@
       <c r="J101" s="7" t="n"/>
       <c r="K101" s="7" t="n"/>
       <c r="L101" s="7" t="n"/>
-      <c r="M101" s="7" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="7" t="n"/>
@@ -10146,7 +9207,6 @@
       <c r="J102" s="7" t="n"/>
       <c r="K102" s="7" t="n"/>
       <c r="L102" s="7" t="n"/>
-      <c r="M102" s="7" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="7" t="n"/>
@@ -10161,7 +9221,6 @@
       <c r="J103" s="7" t="n"/>
       <c r="K103" s="7" t="n"/>
       <c r="L103" s="7" t="n"/>
-      <c r="M103" s="7" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="7" t="n"/>
@@ -10176,7 +9235,6 @@
       <c r="J104" s="7" t="n"/>
       <c r="K104" s="7" t="n"/>
       <c r="L104" s="7" t="n"/>
-      <c r="M104" s="7" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="7" t="n"/>
@@ -10191,7 +9249,6 @@
       <c r="J105" s="7" t="n"/>
       <c r="K105" s="7" t="n"/>
       <c r="L105" s="7" t="n"/>
-      <c r="M105" s="7" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="7" t="n"/>
@@ -10206,7 +9263,6 @@
       <c r="J106" s="7" t="n"/>
       <c r="K106" s="7" t="n"/>
       <c r="L106" s="7" t="n"/>
-      <c r="M106" s="7" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="7" t="n"/>
@@ -10221,7 +9277,6 @@
       <c r="J107" s="7" t="n"/>
       <c r="K107" s="7" t="n"/>
       <c r="L107" s="7" t="n"/>
-      <c r="M107" s="7" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="7" t="n"/>
@@ -10236,7 +9291,6 @@
       <c r="J108" s="7" t="n"/>
       <c r="K108" s="7" t="n"/>
       <c r="L108" s="7" t="n"/>
-      <c r="M108" s="7" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="7" t="n"/>
@@ -10251,7 +9305,6 @@
       <c r="J109" s="7" t="n"/>
       <c r="K109" s="7" t="n"/>
       <c r="L109" s="7" t="n"/>
-      <c r="M109" s="7" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="7" t="n"/>
@@ -10266,7 +9319,6 @@
       <c r="J110" s="7" t="n"/>
       <c r="K110" s="7" t="n"/>
       <c r="L110" s="7" t="n"/>
-      <c r="M110" s="7" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="7" t="n"/>
@@ -10281,7 +9333,6 @@
       <c r="J111" s="7" t="n"/>
       <c r="K111" s="7" t="n"/>
       <c r="L111" s="7" t="n"/>
-      <c r="M111" s="7" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="7" t="n"/>
@@ -10296,7 +9347,6 @@
       <c r="J112" s="7" t="n"/>
       <c r="K112" s="7" t="n"/>
       <c r="L112" s="7" t="n"/>
-      <c r="M112" s="7" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="7" t="n"/>
@@ -10311,7 +9361,6 @@
       <c r="J113" s="7" t="n"/>
       <c r="K113" s="7" t="n"/>
       <c r="L113" s="7" t="n"/>
-      <c r="M113" s="7" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="7" t="n"/>
@@ -10326,7 +9375,6 @@
       <c r="J114" s="7" t="n"/>
       <c r="K114" s="7" t="n"/>
       <c r="L114" s="7" t="n"/>
-      <c r="M114" s="7" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="7" t="n"/>
@@ -10341,7 +9389,6 @@
       <c r="J115" s="7" t="n"/>
       <c r="K115" s="7" t="n"/>
       <c r="L115" s="7" t="n"/>
-      <c r="M115" s="7" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="7" t="n"/>
@@ -10356,7 +9403,6 @@
       <c r="J116" s="7" t="n"/>
       <c r="K116" s="7" t="n"/>
       <c r="L116" s="7" t="n"/>
-      <c r="M116" s="7" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="7" t="n"/>
@@ -10371,7 +9417,6 @@
       <c r="J117" s="7" t="n"/>
       <c r="K117" s="7" t="n"/>
       <c r="L117" s="7" t="n"/>
-      <c r="M117" s="7" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="7" t="n"/>
@@ -10386,7 +9431,6 @@
       <c r="J118" s="7" t="n"/>
       <c r="K118" s="7" t="n"/>
       <c r="L118" s="7" t="n"/>
-      <c r="M118" s="7" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="7" t="n"/>
@@ -10401,7 +9445,6 @@
       <c r="J119" s="7" t="n"/>
       <c r="K119" s="7" t="n"/>
       <c r="L119" s="7" t="n"/>
-      <c r="M119" s="7" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="7" t="n"/>
@@ -10416,7 +9459,6 @@
       <c r="J120" s="7" t="n"/>
       <c r="K120" s="7" t="n"/>
       <c r="L120" s="7" t="n"/>
-      <c r="M120" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -10462,7 +9504,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/donnees_exemple.xlsx
+++ b/donnees_exemple.xlsx
@@ -206,7 +206,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -255,6 +255,12 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -811,7 +817,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Groupe Scolaire Les Palmiers</t>
+          <t>Lycée Moderne de Cocody</t>
         </is>
       </c>
       <c r="C4" s="8" t="n"/>
@@ -1461,16 +1467,16 @@
           <t>6ème A</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="26" t="inlineStr">
         <is>
           <t>6ème</t>
         </is>
       </c>
-      <c r="C4" s="16" t="inlineStr"/>
-      <c r="D4" s="16" t="n">
-        <v>60</v>
-      </c>
-      <c r="E4" s="16" t="inlineStr">
+      <c r="C4" s="26" t="inlineStr"/>
+      <c r="D4" s="26" t="n">
+        <v>58</v>
+      </c>
+      <c r="E4" s="26" t="inlineStr">
         <is>
           <t>Salle 1</t>
         </is>
@@ -1482,16 +1488,16 @@
           <t>6ème B</t>
         </is>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="26" t="inlineStr">
         <is>
           <t>6ème</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr"/>
-      <c r="D5" s="16" t="n">
-        <v>58</v>
-      </c>
-      <c r="E5" s="16" t="inlineStr">
+      <c r="C5" s="26" t="inlineStr"/>
+      <c r="D5" s="26" t="n">
+        <v>56</v>
+      </c>
+      <c r="E5" s="26" t="inlineStr">
         <is>
           <t>Salle 2</t>
         </is>
@@ -1503,16 +1509,16 @@
           <t>5ème A</t>
         </is>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="26" t="inlineStr">
         <is>
           <t>5ème</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr"/>
-      <c r="D6" s="16" t="n">
-        <v>55</v>
-      </c>
-      <c r="E6" s="16" t="inlineStr">
+      <c r="C6" s="26" t="inlineStr"/>
+      <c r="D6" s="26" t="n">
+        <v>54</v>
+      </c>
+      <c r="E6" s="26" t="inlineStr">
         <is>
           <t>Salle 3</t>
         </is>
@@ -1524,16 +1530,16 @@
           <t>4ème A</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="26" t="inlineStr">
         <is>
           <t>4ème</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr"/>
-      <c r="D7" s="16" t="n">
+      <c r="C7" s="26" t="inlineStr"/>
+      <c r="D7" s="26" t="n">
         <v>52</v>
       </c>
-      <c r="E7" s="16" t="inlineStr">
+      <c r="E7" s="26" t="inlineStr">
         <is>
           <t>Salle 4</t>
         </is>
@@ -1545,16 +1551,16 @@
           <t>3ème A</t>
         </is>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="26" t="inlineStr">
         <is>
           <t>3ème</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr"/>
-      <c r="D8" s="16" t="n">
+      <c r="C8" s="26" t="inlineStr"/>
+      <c r="D8" s="26" t="n">
         <v>50</v>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="E8" s="26" t="inlineStr">
         <is>
           <t>Salle 5</t>
         </is>
@@ -1563,23 +1569,19 @@
     <row r="9">
       <c r="A9" s="16" t="inlineStr">
         <is>
-          <t>2nde C</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>2nde</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="n">
-        <v>48</v>
-      </c>
-      <c r="E9" s="16" t="inlineStr">
+          <t>3ème B</t>
+        </is>
+      </c>
+      <c r="B9" s="26" t="inlineStr">
+        <is>
+          <t>3ème</t>
+        </is>
+      </c>
+      <c r="C9" s="26" t="inlineStr"/>
+      <c r="D9" s="26" t="n">
+        <v>49</v>
+      </c>
+      <c r="E9" s="26" t="inlineStr">
         <is>
           <t>Salle 6</t>
         </is>
@@ -1588,23 +1590,23 @@
     <row r="10">
       <c r="A10" s="16" t="inlineStr">
         <is>
-          <t>1ère D</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>1ère</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="n">
-        <v>45</v>
-      </c>
-      <c r="E10" s="16" t="inlineStr">
+          <t>2nde A</t>
+        </is>
+      </c>
+      <c r="B10" s="26" t="inlineStr">
+        <is>
+          <t>2nde</t>
+        </is>
+      </c>
+      <c r="C10" s="26" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D10" s="26" t="n">
+        <v>47</v>
+      </c>
+      <c r="E10" s="26" t="inlineStr">
         <is>
           <t>Salle 7</t>
         </is>
@@ -1613,41 +1615,77 @@
     <row r="11">
       <c r="A11" s="16" t="inlineStr">
         <is>
+          <t>2nde C</t>
+        </is>
+      </c>
+      <c r="B11" s="26" t="inlineStr">
+        <is>
+          <t>2nde</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D11" s="26" t="n">
+        <v>45</v>
+      </c>
+      <c r="E11" s="26" t="inlineStr">
+        <is>
+          <t>Salle 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>1ère D</t>
+        </is>
+      </c>
+      <c r="B12" s="27" t="inlineStr">
+        <is>
+          <t>1ère</t>
+        </is>
+      </c>
+      <c r="C12" s="27" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D12" s="27" t="n">
+        <v>43</v>
+      </c>
+      <c r="E12" s="27" t="inlineStr">
+        <is>
+          <t>Salle 9</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
           <t>Tle D</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B13" s="27" t="inlineStr">
         <is>
           <t>Terminale</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C13" s="27" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D11" s="16" t="n">
-        <v>42</v>
-      </c>
-      <c r="E11" s="16" t="inlineStr">
-        <is>
-          <t>Salle 8</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="n"/>
-      <c r="B12" s="7" t="n"/>
-      <c r="C12" s="7" t="n"/>
-      <c r="D12" s="7" t="n"/>
-      <c r="E12" s="7" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="n"/>
-      <c r="B13" s="7" t="n"/>
-      <c r="C13" s="7" t="n"/>
-      <c r="D13" s="7" t="n"/>
-      <c r="E13" s="7" t="n"/>
+      <c r="D13" s="27" t="n">
+        <v>40</v>
+      </c>
+      <c r="E13" s="27" t="inlineStr">
+        <is>
+          <t>Salle 10</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n"/>
@@ -2210,12 +2248,12 @@
         </is>
       </c>
       <c r="C4" s="16" t="inlineStr"/>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="D4" s="26" t="inlineStr">
         <is>
           <t>Permanent</t>
         </is>
       </c>
-      <c r="E4" s="16" t="n">
+      <c r="E4" s="26" t="n">
         <v>20</v>
       </c>
       <c r="F4" s="16" t="inlineStr">
@@ -2236,12 +2274,12 @@
         </is>
       </c>
       <c r="C5" s="16" t="inlineStr"/>
-      <c r="D5" s="16" t="inlineStr">
+      <c r="D5" s="26" t="inlineStr">
         <is>
           <t>Permanent</t>
         </is>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="E5" s="26" t="n">
         <v>20</v>
       </c>
       <c r="F5" s="16" t="inlineStr">
@@ -2262,12 +2300,12 @@
         </is>
       </c>
       <c r="C6" s="16" t="inlineStr"/>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D6" s="26" t="inlineStr">
         <is>
           <t>Permanent</t>
         </is>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="E6" s="26" t="n">
         <v>20</v>
       </c>
       <c r="F6" s="16" t="inlineStr">
@@ -2288,12 +2326,12 @@
         </is>
       </c>
       <c r="C7" s="16" t="inlineStr"/>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D7" s="26" t="inlineStr">
         <is>
           <t>Permanent</t>
         </is>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="E7" s="26" t="n">
         <v>18</v>
       </c>
       <c r="F7" s="16" t="inlineStr">
@@ -2305,340 +2343,434 @@
     <row r="8">
       <c r="A8" s="16" t="inlineStr">
         <is>
-          <t>M. DIALLO Ibrahim</t>
+          <t>M. DIABATÉ Souleymane</t>
         </is>
       </c>
       <c r="B8" s="16" t="inlineStr">
         <is>
-          <t>Anglais</t>
+          <t>Français</t>
         </is>
       </c>
       <c r="C8" s="16" t="inlineStr"/>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>Vacataire</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="n">
-        <v>14</v>
+      <c r="D8" s="26" t="inlineStr">
+        <is>
+          <t>Permanent</t>
+        </is>
+      </c>
+      <c r="E8" s="26" t="n">
+        <v>18</v>
       </c>
       <c r="F8" s="16" t="inlineStr">
         <is>
-          <t>05 41 42 43 44</t>
+          <t>07 35 36 37 38</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="16" t="inlineStr">
         <is>
-          <t>Mme COULIBALY Awa</t>
+          <t>M. DIALLO Ibrahim</t>
         </is>
       </c>
       <c r="B9" s="16" t="inlineStr">
         <is>
-          <t>Histoire-Géographie</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>EDHC</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>Permanent</t>
-        </is>
-      </c>
-      <c r="E9" s="16" t="n">
-        <v>20</v>
+          <t>Anglais</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr"/>
+      <c r="D9" s="26" t="inlineStr">
+        <is>
+          <t>Vacataire</t>
+        </is>
+      </c>
+      <c r="E9" s="26" t="n">
+        <v>16</v>
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
-          <t>07 51 52 53 54</t>
+          <t>05 41 42 43 44</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="16" t="inlineStr">
         <is>
-          <t>M. ASSI Kouadio</t>
+          <t>Mme KONAN Adjoua</t>
         </is>
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>Histoire-Géographie</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>EDHC</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
+          <t>Anglais</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="inlineStr"/>
+      <c r="D10" s="26" t="inlineStr">
         <is>
           <t>Permanent</t>
         </is>
       </c>
-      <c r="E10" s="16" t="n">
+      <c r="E10" s="26" t="n">
         <v>18</v>
       </c>
       <c r="F10" s="16" t="inlineStr">
         <is>
-          <t>07 61 62 63 64</t>
+          <t>07 45 46 47 48</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="16" t="inlineStr">
         <is>
-          <t>M. N'GUESSAN Koffi</t>
+          <t>Mme COULIBALY Awa</t>
         </is>
       </c>
       <c r="B11" s="16" t="inlineStr">
         <is>
-          <t>Physique-Chimie</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr"/>
-      <c r="D11" s="16" t="inlineStr">
+          <t>Histoire-Géographie</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="inlineStr">
+        <is>
+          <t>EDHC</t>
+        </is>
+      </c>
+      <c r="D11" s="26" t="inlineStr">
         <is>
           <t>Permanent</t>
         </is>
       </c>
-      <c r="E11" s="16" t="n">
-        <v>25</v>
+      <c r="E11" s="26" t="n">
+        <v>20</v>
       </c>
       <c r="F11" s="16" t="inlineStr">
         <is>
-          <t>07 71 72 73 74</t>
+          <t>07 51 52 53 54</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="16" t="inlineStr">
         <is>
-          <t>Mme AHOU Marie</t>
+          <t>M. ASSI Kouadio</t>
         </is>
       </c>
       <c r="B12" s="16" t="inlineStr">
         <is>
-          <t>SVT</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr"/>
-      <c r="D12" s="16" t="inlineStr">
+          <t>Histoire-Géographie</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="inlineStr">
+        <is>
+          <t>EDHC</t>
+        </is>
+      </c>
+      <c r="D12" s="26" t="inlineStr">
         <is>
           <t>Permanent</t>
         </is>
       </c>
-      <c r="E12" s="16" t="n">
-        <v>22</v>
+      <c r="E12" s="26" t="n">
+        <v>18</v>
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
-          <t>07 81 82 83 84</t>
+          <t>07 61 62 63 64</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="16" t="inlineStr">
         <is>
-          <t>M. OUATTARA Seydou</t>
+          <t>M. N'GUESSAN Koffi</t>
         </is>
       </c>
       <c r="B13" s="16" t="inlineStr">
         <is>
-          <t>EPS</t>
+          <t>Physique-Chimie</t>
         </is>
       </c>
       <c r="C13" s="16" t="inlineStr"/>
-      <c r="D13" s="16" t="inlineStr">
+      <c r="D13" s="26" t="inlineStr">
         <is>
           <t>Permanent</t>
         </is>
       </c>
-      <c r="E13" s="16" t="n">
-        <v>20</v>
+      <c r="E13" s="26" t="n">
+        <v>22</v>
       </c>
       <c r="F13" s="16" t="inlineStr">
         <is>
-          <t>05 91 92 93 94</t>
+          <t>07 71 72 73 74</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="16" t="inlineStr">
         <is>
-          <t>Mme KONAN Adjoua</t>
+          <t>Mme YÉBOUÉ Sylvie</t>
         </is>
       </c>
       <c r="B14" s="16" t="inlineStr">
         <is>
-          <t>Espagnol</t>
+          <t>Physique-Chimie</t>
         </is>
       </c>
       <c r="C14" s="16" t="inlineStr"/>
-      <c r="D14" s="16" t="inlineStr">
-        <is>
-          <t>Vacataire</t>
-        </is>
-      </c>
-      <c r="E14" s="16" t="n">
-        <v>12</v>
+      <c r="D14" s="26" t="inlineStr">
+        <is>
+          <t>Permanent</t>
+        </is>
+      </c>
+      <c r="E14" s="26" t="n">
+        <v>20</v>
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
-          <t>05 01 02 03 05</t>
+          <t>07 75 76 77 78</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="16" t="inlineStr">
         <is>
-          <t>M. TRA Bi Zéphirin</t>
+          <t>Mme AHOU Marie</t>
         </is>
       </c>
       <c r="B15" s="16" t="inlineStr">
         <is>
-          <t>Philosophie</t>
+          <t>SVT</t>
         </is>
       </c>
       <c r="C15" s="16" t="inlineStr"/>
-      <c r="D15" s="16" t="inlineStr">
-        <is>
-          <t>Vacataire</t>
-        </is>
-      </c>
-      <c r="E15" s="16" t="n">
-        <v>10</v>
+      <c r="D15" s="26" t="inlineStr">
+        <is>
+          <t>Permanent</t>
+        </is>
+      </c>
+      <c r="E15" s="26" t="n">
+        <v>22</v>
       </c>
       <c r="F15" s="16" t="inlineStr">
         <is>
-          <t>05 11 12 13 15</t>
+          <t>07 81 82 83 84</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="16" t="inlineStr">
         <is>
-          <t>Mme YAO Ahou</t>
+          <t>M. ZADI Gérard</t>
         </is>
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>Informatique</t>
+          <t>SVT</t>
         </is>
       </c>
       <c r="C16" s="16" t="inlineStr"/>
-      <c r="D16" s="16" t="inlineStr">
-        <is>
-          <t>Vacataire</t>
-        </is>
-      </c>
-      <c r="E16" s="16" t="n">
-        <v>8</v>
+      <c r="D16" s="26" t="inlineStr">
+        <is>
+          <t>Permanent</t>
+        </is>
+      </c>
+      <c r="E16" s="26" t="n">
+        <v>20</v>
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
-          <t>05 21 22 23 25</t>
+          <t>07 85 86 87 88</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="16" t="inlineStr">
         <is>
-          <t>M. GNAHORÉ Jacques</t>
+          <t>M. TRA Bi Zéphirin</t>
         </is>
       </c>
       <c r="B17" s="16" t="inlineStr">
         <is>
-          <t>Musique</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>Arts plastiques</t>
-        </is>
-      </c>
-      <c r="D17" s="16" t="inlineStr">
+          <t>Espagnol</t>
+        </is>
+      </c>
+      <c r="C17" s="16" t="inlineStr"/>
+      <c r="D17" s="26" t="inlineStr">
         <is>
           <t>Vacataire</t>
         </is>
       </c>
-      <c r="E17" s="16" t="n">
-        <v>10</v>
+      <c r="E17" s="26" t="n">
+        <v>14</v>
       </c>
       <c r="F17" s="16" t="inlineStr">
         <is>
-          <t>05 31 32 33 35</t>
+          <t>05 91 92 93 94</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="16" t="inlineStr">
         <is>
-          <t>M. ADOU Michel</t>
+          <t>Mme SANGARÉ Mariam</t>
         </is>
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t>Anglais</t>
+          <t>Espagnol</t>
         </is>
       </c>
       <c r="C18" s="16" t="inlineStr"/>
-      <c r="D18" s="16" t="inlineStr">
+      <c r="D18" s="26" t="inlineStr">
+        <is>
+          <t>Vacataire</t>
+        </is>
+      </c>
+      <c r="E18" s="26" t="n">
+        <v>12</v>
+      </c>
+      <c r="F18" s="16" t="inlineStr">
+        <is>
+          <t>05 95 96 97 98</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>M. OUATTARA Seydou</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr"/>
+      <c r="D19" s="27" t="inlineStr">
         <is>
           <t>Permanent</t>
         </is>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="E19" s="27" t="n">
         <v>18</v>
       </c>
-      <c r="F18" s="16" t="inlineStr">
-        <is>
-          <t>07 41 42 43 45</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="n"/>
-      <c r="B19" s="7" t="n"/>
-      <c r="C19" s="7" t="n"/>
-      <c r="D19" s="7" t="n"/>
-      <c r="E19" s="7" t="n"/>
-      <c r="F19" s="7" t="n"/>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>07 02 04 06 08</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="n"/>
-      <c r="B20" s="7" t="n"/>
-      <c r="C20" s="7" t="n"/>
-      <c r="D20" s="7" t="n"/>
-      <c r="E20" s="7" t="n"/>
-      <c r="F20" s="7" t="n"/>
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>M. GNAHORÉ Jacques</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Arts plastiques</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>Musique</t>
+        </is>
+      </c>
+      <c r="D20" s="27" t="inlineStr">
+        <is>
+          <t>Vacataire</t>
+        </is>
+      </c>
+      <c r="E20" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>05 12 14 16 18</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="n"/>
-      <c r="B21" s="7" t="n"/>
-      <c r="C21" s="7" t="n"/>
-      <c r="D21" s="7" t="n"/>
-      <c r="E21" s="7" t="n"/>
-      <c r="F21" s="7" t="n"/>
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>M. BROU Aristide</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Philosophie</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr"/>
+      <c r="D21" s="27" t="inlineStr">
+        <is>
+          <t>Vacataire</t>
+        </is>
+      </c>
+      <c r="E21" s="27" t="n">
+        <v>12</v>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>05 22 24 26 28</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="n"/>
-      <c r="B22" s="7" t="n"/>
-      <c r="C22" s="7" t="n"/>
-      <c r="D22" s="7" t="n"/>
-      <c r="E22" s="7" t="n"/>
-      <c r="F22" s="7" t="n"/>
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>M. KOUADIO Léon</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Mathématiques</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr"/>
+      <c r="D22" s="27" t="inlineStr">
+        <is>
+          <t>Permanent</t>
+        </is>
+      </c>
+      <c r="E22" s="27" t="n">
+        <v>20</v>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>07 03 05 07 09</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="n"/>
-      <c r="B23" s="7" t="n"/>
-      <c r="C23" s="7" t="n"/>
-      <c r="D23" s="7" t="n"/>
-      <c r="E23" s="7" t="n"/>
-      <c r="F23" s="7" t="n"/>
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>Mme ADJÉ Pascaline</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>EDHC</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>Histoire-Géographie</t>
+        </is>
+      </c>
+      <c r="D23" s="27" t="inlineStr">
+        <is>
+          <t>Permanent</t>
+        </is>
+      </c>
+      <c r="E23" s="27" t="n">
+        <v>16</v>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>07 13 15 17 19</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n"/>
@@ -3436,7 +3568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E400"/>
+  <dimension ref="A1:F400"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3491,7 +3623,7 @@
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t>M. KOUASSI Yao</t>
+          <t>M. KONÉ Mamadou</t>
         </is>
       </c>
       <c r="B4" s="16" t="inlineStr">
@@ -3501,18 +3633,19 @@
       </c>
       <c r="C4" s="16" t="inlineStr">
         <is>
-          <t>Mathématiques</t>
-        </is>
-      </c>
-      <c r="D4" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="E4" s="16" t="inlineStr"/>
+          <t>Français</t>
+        </is>
+      </c>
+      <c r="D4" s="26" t="n">
+        <v>6</v>
+      </c>
+      <c r="E4" s="26" t="inlineStr"/>
+      <c r="F4" s="7" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="16" t="inlineStr">
         <is>
-          <t>M. KONÉ Mamadou</t>
+          <t>M. KOUASSI Yao</t>
         </is>
       </c>
       <c r="B5" s="16" t="inlineStr">
@@ -3522,18 +3655,19 @@
       </c>
       <c r="C5" s="16" t="inlineStr">
         <is>
-          <t>Français</t>
-        </is>
-      </c>
-      <c r="D5" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="E5" s="16" t="inlineStr"/>
+          <t>Mathématiques</t>
+        </is>
+      </c>
+      <c r="D5" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" s="26" t="inlineStr"/>
+      <c r="F5" s="7" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="16" t="inlineStr">
         <is>
-          <t>M. DIALLO Ibrahim</t>
+          <t>Mme KONAN Adjoua</t>
         </is>
       </c>
       <c r="B6" s="16" t="inlineStr">
@@ -3546,10 +3680,11 @@
           <t>Anglais</t>
         </is>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="D6" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="E6" s="16" t="inlineStr"/>
+      <c r="E6" s="26" t="inlineStr"/>
+      <c r="F6" s="7" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="16" t="inlineStr">
@@ -3567,15 +3702,16 @@
           <t>Histoire-Géographie</t>
         </is>
       </c>
-      <c r="D7" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="E7" s="16" t="inlineStr"/>
+      <c r="D7" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" s="26" t="inlineStr"/>
+      <c r="F7" s="7" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="16" t="inlineStr">
         <is>
-          <t>Mme COULIBALY Awa</t>
+          <t>Mme AHOU Marie</t>
         </is>
       </c>
       <c r="B8" s="16" t="inlineStr">
@@ -3585,13 +3721,14 @@
       </c>
       <c r="C8" s="16" t="inlineStr">
         <is>
-          <t>EDHC</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" s="16" t="inlineStr"/>
+          <t>SVT</t>
+        </is>
+      </c>
+      <c r="D8" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" s="26" t="inlineStr"/>
+      <c r="F8" s="7" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="16" t="inlineStr">
@@ -3609,15 +3746,16 @@
           <t>Physique-Chimie</t>
         </is>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="D9" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="E9" s="16" t="inlineStr"/>
+      <c r="E9" s="26" t="inlineStr"/>
+      <c r="F9" s="7" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="16" t="inlineStr">
         <is>
-          <t>Mme AHOU Marie</t>
+          <t>M. OUATTARA Seydou</t>
         </is>
       </c>
       <c r="B10" s="16" t="inlineStr">
@@ -3627,18 +3765,23 @@
       </c>
       <c r="C10" s="16" t="inlineStr">
         <is>
-          <t>SVT</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="n">
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="D10" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="E10" s="16" t="inlineStr"/>
+      <c r="E10" s="26" t="inlineStr">
+        <is>
+          <t>Vendredi</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="16" t="inlineStr">
         <is>
-          <t>M. OUATTARA Seydou</t>
+          <t>Mme ADJÉ Pascaline</t>
         </is>
       </c>
       <c r="B11" s="16" t="inlineStr">
@@ -3648,22 +3791,19 @@
       </c>
       <c r="C11" s="16" t="inlineStr">
         <is>
-          <t>EPS</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="E11" s="16" t="inlineStr">
-        <is>
-          <t>Vendredi</t>
-        </is>
-      </c>
+          <t>EDHC</t>
+        </is>
+      </c>
+      <c r="D11" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="26" t="inlineStr"/>
+      <c r="F11" s="7" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="16" t="inlineStr">
         <is>
-          <t>Mme YAO Ahou</t>
+          <t>M. GNAHORÉ Jacques</t>
         </is>
       </c>
       <c r="B12" s="16" t="inlineStr">
@@ -3673,60 +3813,63 @@
       </c>
       <c r="C12" s="16" t="inlineStr">
         <is>
-          <t>Informatique</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="n">
+          <t>Arts plastiques</t>
+        </is>
+      </c>
+      <c r="D12" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="E12" s="16" t="inlineStr"/>
+      <c r="E12" s="26" t="inlineStr"/>
+      <c r="F12" s="7" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="16" t="inlineStr">
         <is>
-          <t>M. GNAHORÉ Jacques</t>
+          <t>Mme TOURÉ Aminata</t>
         </is>
       </c>
       <c r="B13" s="16" t="inlineStr">
         <is>
-          <t>6ème A</t>
+          <t>6ème B</t>
         </is>
       </c>
       <c r="C13" s="16" t="inlineStr">
         <is>
-          <t>Musique</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" s="16" t="inlineStr"/>
+          <t>Français</t>
+        </is>
+      </c>
+      <c r="D13" s="26" t="n">
+        <v>6</v>
+      </c>
+      <c r="E13" s="26" t="inlineStr"/>
+      <c r="F13" s="7" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="16" t="inlineStr">
         <is>
-          <t>M. GNAHORÉ Jacques</t>
+          <t>Mme BAMBA Fatou</t>
         </is>
       </c>
       <c r="B14" s="16" t="inlineStr">
         <is>
-          <t>6ème A</t>
+          <t>6ème B</t>
         </is>
       </c>
       <c r="C14" s="16" t="inlineStr">
         <is>
-          <t>Arts plastiques</t>
-        </is>
-      </c>
-      <c r="D14" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" s="16" t="inlineStr"/>
+          <t>Mathématiques</t>
+        </is>
+      </c>
+      <c r="D14" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E14" s="26" t="inlineStr"/>
+      <c r="F14" s="7" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="16" t="inlineStr">
         <is>
-          <t>Mme BAMBA Fatou</t>
+          <t>M. DIALLO Ibrahim</t>
         </is>
       </c>
       <c r="B15" s="16" t="inlineStr">
@@ -3736,18 +3879,19 @@
       </c>
       <c r="C15" s="16" t="inlineStr">
         <is>
-          <t>Mathématiques</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="E15" s="16" t="inlineStr"/>
+          <t>Anglais</t>
+        </is>
+      </c>
+      <c r="D15" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" s="26" t="inlineStr"/>
+      <c r="F15" s="7" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="16" t="inlineStr">
         <is>
-          <t>Mme TOURÉ Aminata</t>
+          <t>M. ASSI Kouadio</t>
         </is>
       </c>
       <c r="B16" s="16" t="inlineStr">
@@ -3757,18 +3901,19 @@
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>Français</t>
-        </is>
-      </c>
-      <c r="D16" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="E16" s="16" t="inlineStr"/>
+          <t>Histoire-Géographie</t>
+        </is>
+      </c>
+      <c r="D16" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="E16" s="26" t="inlineStr"/>
+      <c r="F16" s="7" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="16" t="inlineStr">
         <is>
-          <t>M. ADOU Michel</t>
+          <t>M. ZADI Gérard</t>
         </is>
       </c>
       <c r="B17" s="16" t="inlineStr">
@@ -3778,18 +3923,19 @@
       </c>
       <c r="C17" s="16" t="inlineStr">
         <is>
-          <t>Anglais</t>
-        </is>
-      </c>
-      <c r="D17" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="E17" s="16" t="inlineStr"/>
+          <t>SVT</t>
+        </is>
+      </c>
+      <c r="D17" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" s="26" t="inlineStr"/>
+      <c r="F17" s="7" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="16" t="inlineStr">
         <is>
-          <t>M. ASSI Kouadio</t>
+          <t>Mme YÉBOUÉ Sylvie</t>
         </is>
       </c>
       <c r="B18" s="16" t="inlineStr">
@@ -3799,18 +3945,19 @@
       </c>
       <c r="C18" s="16" t="inlineStr">
         <is>
-          <t>Histoire-Géographie</t>
-        </is>
-      </c>
-      <c r="D18" s="16" t="n">
+          <t>Physique-Chimie</t>
+        </is>
+      </c>
+      <c r="D18" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="E18" s="16" t="inlineStr"/>
+      <c r="E18" s="26" t="inlineStr"/>
+      <c r="F18" s="7" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="16" t="inlineStr">
         <is>
-          <t>M. ASSI Kouadio</t>
+          <t>M. OUATTARA Seydou</t>
         </is>
       </c>
       <c r="B19" s="16" t="inlineStr">
@@ -3820,18 +3967,23 @@
       </c>
       <c r="C19" s="16" t="inlineStr">
         <is>
-          <t>EDHC</t>
-        </is>
-      </c>
-      <c r="D19" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" s="16" t="inlineStr"/>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="D19" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" s="26" t="inlineStr">
+        <is>
+          <t>Mardi</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="16" t="inlineStr">
         <is>
-          <t>M. N'GUESSAN Koffi</t>
+          <t>Mme COULIBALY Awa</t>
         </is>
       </c>
       <c r="B20" s="16" t="inlineStr">
@@ -3841,18 +3993,19 @@
       </c>
       <c r="C20" s="16" t="inlineStr">
         <is>
-          <t>Physique-Chimie</t>
-        </is>
-      </c>
-      <c r="D20" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="E20" s="16" t="inlineStr"/>
+          <t>EDHC</t>
+        </is>
+      </c>
+      <c r="D20" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="26" t="inlineStr"/>
+      <c r="F20" s="7" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="16" t="inlineStr">
         <is>
-          <t>Mme AHOU Marie</t>
+          <t>M. GNAHORÉ Jacques</t>
         </is>
       </c>
       <c r="B21" s="16" t="inlineStr">
@@ -3862,102 +4015,107 @@
       </c>
       <c r="C21" s="16" t="inlineStr">
         <is>
-          <t>SVT</t>
-        </is>
-      </c>
-      <c r="D21" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="E21" s="16" t="inlineStr"/>
+          <t>Arts plastiques</t>
+        </is>
+      </c>
+      <c r="D21" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="26" t="inlineStr"/>
+      <c r="F21" s="7" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="16" t="inlineStr">
         <is>
-          <t>M. OUATTARA Seydou</t>
+          <t>M. DIABATÉ Souleymane</t>
         </is>
       </c>
       <c r="B22" s="16" t="inlineStr">
         <is>
-          <t>6ème B</t>
+          <t>5ème A</t>
         </is>
       </c>
       <c r="C22" s="16" t="inlineStr">
         <is>
-          <t>EPS</t>
-        </is>
-      </c>
-      <c r="D22" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="E22" s="16" t="inlineStr"/>
+          <t>Français</t>
+        </is>
+      </c>
+      <c r="D22" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="E22" s="26" t="inlineStr"/>
+      <c r="F22" s="7" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="16" t="inlineStr">
         <is>
-          <t>Mme YAO Ahou</t>
+          <t>M. KOUADIO Léon</t>
         </is>
       </c>
       <c r="B23" s="16" t="inlineStr">
         <is>
-          <t>6ème B</t>
+          <t>5ème A</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr">
         <is>
-          <t>Informatique</t>
-        </is>
-      </c>
-      <c r="D23" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E23" s="16" t="inlineStr"/>
+          <t>Mathématiques</t>
+        </is>
+      </c>
+      <c r="D23" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E23" s="26" t="inlineStr"/>
+      <c r="F23" s="7" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="16" t="inlineStr">
         <is>
-          <t>M. GNAHORÉ Jacques</t>
+          <t>Mme KONAN Adjoua</t>
         </is>
       </c>
       <c r="B24" s="16" t="inlineStr">
         <is>
-          <t>6ème B</t>
+          <t>5ème A</t>
         </is>
       </c>
       <c r="C24" s="16" t="inlineStr">
         <is>
-          <t>Musique</t>
-        </is>
-      </c>
-      <c r="D24" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E24" s="16" t="inlineStr"/>
+          <t>Anglais</t>
+        </is>
+      </c>
+      <c r="D24" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E24" s="26" t="inlineStr"/>
+      <c r="F24" s="7" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="16" t="inlineStr">
         <is>
-          <t>M. GNAHORÉ Jacques</t>
+          <t>Mme ADJÉ Pascaline</t>
         </is>
       </c>
       <c r="B25" s="16" t="inlineStr">
         <is>
-          <t>6ème B</t>
+          <t>5ème A</t>
         </is>
       </c>
       <c r="C25" s="16" t="inlineStr">
         <is>
-          <t>Arts plastiques</t>
-        </is>
-      </c>
-      <c r="D25" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" s="16" t="inlineStr"/>
+          <t>Histoire-Géographie</t>
+        </is>
+      </c>
+      <c r="D25" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="E25" s="26" t="inlineStr"/>
+      <c r="F25" s="7" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="16" t="inlineStr">
         <is>
-          <t>Mme BAMBA Fatou</t>
+          <t>Mme AHOU Marie</t>
         </is>
       </c>
       <c r="B26" s="16" t="inlineStr">
@@ -3967,18 +4125,19 @@
       </c>
       <c r="C26" s="16" t="inlineStr">
         <is>
-          <t>Mathématiques</t>
-        </is>
-      </c>
-      <c r="D26" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="E26" s="16" t="inlineStr"/>
+          <t>SVT</t>
+        </is>
+      </c>
+      <c r="D26" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" s="26" t="inlineStr"/>
+      <c r="F26" s="7" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="16" t="inlineStr">
         <is>
-          <t>M. KONÉ Mamadou</t>
+          <t>M. N'GUESSAN Koffi</t>
         </is>
       </c>
       <c r="B27" s="16" t="inlineStr">
@@ -3988,18 +4147,19 @@
       </c>
       <c r="C27" s="16" t="inlineStr">
         <is>
-          <t>Français</t>
-        </is>
-      </c>
-      <c r="D27" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="E27" s="16" t="inlineStr"/>
+          <t>Physique-Chimie</t>
+        </is>
+      </c>
+      <c r="D27" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" s="26" t="inlineStr"/>
+      <c r="F27" s="7" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="16" t="inlineStr">
         <is>
-          <t>M. DIALLO Ibrahim</t>
+          <t>M. OUATTARA Seydou</t>
         </is>
       </c>
       <c r="B28" s="16" t="inlineStr">
@@ -4009,18 +4169,19 @@
       </c>
       <c r="C28" s="16" t="inlineStr">
         <is>
-          <t>Anglais</t>
-        </is>
-      </c>
-      <c r="D28" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="E28" s="16" t="inlineStr"/>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="D28" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" s="26" t="inlineStr"/>
+      <c r="F28" s="7" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="16" t="inlineStr">
         <is>
-          <t>Mme COULIBALY Awa</t>
+          <t>M. ASSI Kouadio</t>
         </is>
       </c>
       <c r="B29" s="16" t="inlineStr">
@@ -4030,18 +4191,19 @@
       </c>
       <c r="C29" s="16" t="inlineStr">
         <is>
-          <t>Histoire-Géographie</t>
-        </is>
-      </c>
-      <c r="D29" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="E29" s="16" t="inlineStr"/>
+          <t>EDHC</t>
+        </is>
+      </c>
+      <c r="D29" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" s="26" t="inlineStr"/>
+      <c r="F29" s="7" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="16" t="inlineStr">
         <is>
-          <t>Mme COULIBALY Awa</t>
+          <t>M. GNAHORÉ Jacques</t>
         </is>
       </c>
       <c r="B30" s="16" t="inlineStr">
@@ -4051,144 +4213,151 @@
       </c>
       <c r="C30" s="16" t="inlineStr">
         <is>
-          <t>EDHC</t>
-        </is>
-      </c>
-      <c r="D30" s="16" t="n">
+          <t>Arts plastiques</t>
+        </is>
+      </c>
+      <c r="D30" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="E30" s="16" t="inlineStr"/>
+      <c r="E30" s="26" t="inlineStr"/>
+      <c r="F30" s="7" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="16" t="inlineStr">
         <is>
-          <t>M. N'GUESSAN Koffi</t>
+          <t>M. DIABATÉ Souleymane</t>
         </is>
       </c>
       <c r="B31" s="16" t="inlineStr">
         <is>
-          <t>5ème A</t>
+          <t>4ème A</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
         <is>
-          <t>Physique-Chimie</t>
-        </is>
-      </c>
-      <c r="D31" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="E31" s="16" t="inlineStr"/>
+          <t>Français</t>
+        </is>
+      </c>
+      <c r="D31" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="E31" s="26" t="inlineStr"/>
+      <c r="F31" s="7" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="16" t="inlineStr">
         <is>
-          <t>Mme AHOU Marie</t>
+          <t>M. KOUASSI Yao</t>
         </is>
       </c>
       <c r="B32" s="16" t="inlineStr">
         <is>
-          <t>5ème A</t>
+          <t>4ème A</t>
         </is>
       </c>
       <c r="C32" s="16" t="inlineStr">
         <is>
-          <t>SVT</t>
-        </is>
-      </c>
-      <c r="D32" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="E32" s="16" t="inlineStr"/>
+          <t>Mathématiques</t>
+        </is>
+      </c>
+      <c r="D32" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E32" s="26" t="inlineStr"/>
+      <c r="F32" s="7" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="16" t="inlineStr">
         <is>
-          <t>M. OUATTARA Seydou</t>
+          <t>M. DIALLO Ibrahim</t>
         </is>
       </c>
       <c r="B33" s="16" t="inlineStr">
         <is>
-          <t>5ème A</t>
+          <t>4ème A</t>
         </is>
       </c>
       <c r="C33" s="16" t="inlineStr">
         <is>
-          <t>EPS</t>
-        </is>
-      </c>
-      <c r="D33" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="E33" s="16" t="inlineStr"/>
+          <t>Anglais</t>
+        </is>
+      </c>
+      <c r="D33" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E33" s="26" t="inlineStr"/>
+      <c r="F33" s="7" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="16" t="inlineStr">
         <is>
-          <t>Mme YAO Ahou</t>
+          <t>Mme COULIBALY Awa</t>
         </is>
       </c>
       <c r="B34" s="16" t="inlineStr">
         <is>
-          <t>5ème A</t>
+          <t>4ème A</t>
         </is>
       </c>
       <c r="C34" s="16" t="inlineStr">
         <is>
-          <t>Informatique</t>
-        </is>
-      </c>
-      <c r="D34" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E34" s="16" t="inlineStr"/>
+          <t>Histoire-Géographie</t>
+        </is>
+      </c>
+      <c r="D34" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="E34" s="26" t="inlineStr"/>
+      <c r="F34" s="7" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="16" t="inlineStr">
         <is>
-          <t>M. GNAHORÉ Jacques</t>
+          <t>M. ZADI Gérard</t>
         </is>
       </c>
       <c r="B35" s="16" t="inlineStr">
         <is>
-          <t>5ème A</t>
+          <t>4ème A</t>
         </is>
       </c>
       <c r="C35" s="16" t="inlineStr">
         <is>
-          <t>Musique</t>
-        </is>
-      </c>
-      <c r="D35" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E35" s="16" t="inlineStr"/>
+          <t>SVT</t>
+        </is>
+      </c>
+      <c r="D35" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E35" s="26" t="inlineStr"/>
+      <c r="F35" s="7" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="16" t="inlineStr">
         <is>
-          <t>M. GNAHORÉ Jacques</t>
+          <t>Mme YÉBOUÉ Sylvie</t>
         </is>
       </c>
       <c r="B36" s="16" t="inlineStr">
         <is>
-          <t>5ème A</t>
+          <t>4ème A</t>
         </is>
       </c>
       <c r="C36" s="16" t="inlineStr">
         <is>
-          <t>Arts plastiques</t>
-        </is>
-      </c>
-      <c r="D36" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E36" s="16" t="inlineStr"/>
+          <t>Physique-Chimie</t>
+        </is>
+      </c>
+      <c r="D36" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E36" s="26" t="inlineStr"/>
+      <c r="F36" s="7" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="16" t="inlineStr">
         <is>
-          <t>M. KOUASSI Yao</t>
+          <t>M. OUATTARA Seydou</t>
         </is>
       </c>
       <c r="B37" s="16" t="inlineStr">
@@ -4198,18 +4367,19 @@
       </c>
       <c r="C37" s="16" t="inlineStr">
         <is>
-          <t>Mathématiques</t>
-        </is>
-      </c>
-      <c r="D37" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="E37" s="16" t="inlineStr"/>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="D37" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E37" s="26" t="inlineStr"/>
+      <c r="F37" s="7" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="16" t="inlineStr">
         <is>
-          <t>Mme TOURÉ Aminata</t>
+          <t>Mme ADJÉ Pascaline</t>
         </is>
       </c>
       <c r="B38" s="16" t="inlineStr">
@@ -4219,18 +4389,19 @@
       </c>
       <c r="C38" s="16" t="inlineStr">
         <is>
-          <t>Français</t>
-        </is>
-      </c>
-      <c r="D38" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="E38" s="16" t="inlineStr"/>
+          <t>EDHC</t>
+        </is>
+      </c>
+      <c r="D38" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" s="26" t="inlineStr"/>
+      <c r="F38" s="7" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="16" t="inlineStr">
         <is>
-          <t>M. ADOU Michel</t>
+          <t>M. GNAHORÉ Jacques</t>
         </is>
       </c>
       <c r="B39" s="16" t="inlineStr">
@@ -4240,244 +4411,260 @@
       </c>
       <c r="C39" s="16" t="inlineStr">
         <is>
-          <t>Anglais</t>
-        </is>
-      </c>
-      <c r="D39" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="E39" s="16" t="inlineStr"/>
+          <t>Arts plastiques</t>
+        </is>
+      </c>
+      <c r="D39" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" s="26" t="inlineStr"/>
+      <c r="F39" s="7" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="16" t="inlineStr">
         <is>
-          <t>M. ASSI Kouadio</t>
+          <t>M. KONÉ Mamadou</t>
         </is>
       </c>
       <c r="B40" s="16" t="inlineStr">
         <is>
-          <t>4ème A</t>
+          <t>3ème A</t>
         </is>
       </c>
       <c r="C40" s="16" t="inlineStr">
         <is>
-          <t>Histoire-Géographie</t>
-        </is>
-      </c>
-      <c r="D40" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="E40" s="16" t="inlineStr"/>
+          <t>Français</t>
+        </is>
+      </c>
+      <c r="D40" s="26" t="n">
+        <v>6</v>
+      </c>
+      <c r="E40" s="26" t="inlineStr"/>
+      <c r="F40" s="7" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="16" t="inlineStr">
         <is>
-          <t>M. ASSI Kouadio</t>
+          <t>Mme BAMBA Fatou</t>
         </is>
       </c>
       <c r="B41" s="16" t="inlineStr">
         <is>
-          <t>4ème A</t>
+          <t>3ème A</t>
         </is>
       </c>
       <c r="C41" s="16" t="inlineStr">
         <is>
-          <t>EDHC</t>
-        </is>
-      </c>
-      <c r="D41" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E41" s="16" t="inlineStr"/>
+          <t>Mathématiques</t>
+        </is>
+      </c>
+      <c r="D41" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E41" s="26" t="inlineStr"/>
+      <c r="F41" s="7" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="16" t="inlineStr">
         <is>
-          <t>M. N'GUESSAN Koffi</t>
+          <t>Mme KONAN Adjoua</t>
         </is>
       </c>
       <c r="B42" s="16" t="inlineStr">
         <is>
-          <t>4ème A</t>
+          <t>3ème A</t>
         </is>
       </c>
       <c r="C42" s="16" t="inlineStr">
         <is>
-          <t>Physique-Chimie</t>
-        </is>
-      </c>
-      <c r="D42" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="E42" s="16" t="inlineStr"/>
+          <t>Anglais</t>
+        </is>
+      </c>
+      <c r="D42" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="E42" s="26" t="inlineStr"/>
+      <c r="F42" s="7" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="16" t="inlineStr">
         <is>
-          <t>Mme AHOU Marie</t>
+          <t>M. TRA Bi Zéphirin</t>
         </is>
       </c>
       <c r="B43" s="16" t="inlineStr">
         <is>
-          <t>4ème A</t>
+          <t>3ème A</t>
         </is>
       </c>
       <c r="C43" s="16" t="inlineStr">
         <is>
-          <t>SVT</t>
-        </is>
-      </c>
-      <c r="D43" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="E43" s="16" t="inlineStr"/>
+          <t>Espagnol</t>
+        </is>
+      </c>
+      <c r="D43" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="E43" s="26" t="inlineStr"/>
+      <c r="F43" s="7" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="16" t="inlineStr">
         <is>
-          <t>M. OUATTARA Seydou</t>
+          <t>M. ASSI Kouadio</t>
         </is>
       </c>
       <c r="B44" s="16" t="inlineStr">
         <is>
-          <t>4ème A</t>
+          <t>3ème A</t>
         </is>
       </c>
       <c r="C44" s="16" t="inlineStr">
         <is>
-          <t>EPS</t>
-        </is>
-      </c>
-      <c r="D44" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="E44" s="16" t="inlineStr"/>
+          <t>Histoire-Géographie</t>
+        </is>
+      </c>
+      <c r="D44" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E44" s="26" t="inlineStr"/>
+      <c r="F44" s="7" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="16" t="inlineStr">
         <is>
-          <t>Mme KONAN Adjoua</t>
+          <t>Mme AHOU Marie</t>
         </is>
       </c>
       <c r="B45" s="16" t="inlineStr">
         <is>
-          <t>4ème A</t>
+          <t>3ème A</t>
         </is>
       </c>
       <c r="C45" s="16" t="inlineStr">
         <is>
-          <t>Espagnol</t>
-        </is>
-      </c>
-      <c r="D45" s="16" t="n">
+          <t>SVT</t>
+        </is>
+      </c>
+      <c r="D45" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="E45" s="16" t="inlineStr"/>
+      <c r="E45" s="26" t="inlineStr"/>
+      <c r="F45" s="7" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="16" t="inlineStr">
         <is>
-          <t>Mme YAO Ahou</t>
+          <t>M. N'GUESSAN Koffi</t>
         </is>
       </c>
       <c r="B46" s="16" t="inlineStr">
         <is>
-          <t>4ème A</t>
+          <t>3ème A</t>
         </is>
       </c>
       <c r="C46" s="16" t="inlineStr">
         <is>
-          <t>Informatique</t>
-        </is>
-      </c>
-      <c r="D46" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E46" s="16" t="inlineStr"/>
+          <t>Physique-Chimie</t>
+        </is>
+      </c>
+      <c r="D46" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E46" s="26" t="inlineStr"/>
+      <c r="F46" s="7" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="16" t="inlineStr">
         <is>
-          <t>M. GNAHORÉ Jacques</t>
+          <t>M. OUATTARA Seydou</t>
         </is>
       </c>
       <c r="B47" s="16" t="inlineStr">
         <is>
-          <t>4ème A</t>
+          <t>3ème A</t>
         </is>
       </c>
       <c r="C47" s="16" t="inlineStr">
         <is>
-          <t>Musique</t>
-        </is>
-      </c>
-      <c r="D47" s="16" t="n">
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="D47" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="E47" s="16" t="inlineStr"/>
+      <c r="E47" s="26" t="inlineStr">
+        <is>
+          <t>Jeudi</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="16" t="inlineStr">
         <is>
-          <t>M. GNAHORÉ Jacques</t>
+          <t>Mme COULIBALY Awa</t>
         </is>
       </c>
       <c r="B48" s="16" t="inlineStr">
         <is>
-          <t>4ème A</t>
+          <t>3ème A</t>
         </is>
       </c>
       <c r="C48" s="16" t="inlineStr">
         <is>
-          <t>Arts plastiques</t>
-        </is>
-      </c>
-      <c r="D48" s="16" t="n">
+          <t>EDHC</t>
+        </is>
+      </c>
+      <c r="D48" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="E48" s="16" t="inlineStr"/>
+      <c r="E48" s="26" t="inlineStr"/>
+      <c r="F48" s="7" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="16" t="inlineStr">
         <is>
-          <t>M. KOUASSI Yao</t>
+          <t>Mme TOURÉ Aminata</t>
         </is>
       </c>
       <c r="B49" s="16" t="inlineStr">
         <is>
-          <t>3ème A</t>
+          <t>3ème B</t>
         </is>
       </c>
       <c r="C49" s="16" t="inlineStr">
         <is>
-          <t>Mathématiques</t>
-        </is>
-      </c>
-      <c r="D49" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="E49" s="16" t="inlineStr"/>
+          <t>Français</t>
+        </is>
+      </c>
+      <c r="D49" s="26" t="n">
+        <v>6</v>
+      </c>
+      <c r="E49" s="26" t="inlineStr"/>
+      <c r="F49" s="7" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="16" t="inlineStr">
         <is>
-          <t>M. KONÉ Mamadou</t>
+          <t>M. KOUADIO Léon</t>
         </is>
       </c>
       <c r="B50" s="16" t="inlineStr">
         <is>
-          <t>3ème A</t>
+          <t>3ème B</t>
         </is>
       </c>
       <c r="C50" s="16" t="inlineStr">
         <is>
-          <t>Français</t>
-        </is>
-      </c>
-      <c r="D50" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="E50" s="16" t="inlineStr"/>
+          <t>Mathématiques</t>
+        </is>
+      </c>
+      <c r="D50" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E50" s="26" t="inlineStr"/>
+      <c r="F50" s="7" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="16" t="inlineStr">
@@ -4487,7 +4674,7 @@
       </c>
       <c r="B51" s="16" t="inlineStr">
         <is>
-          <t>3ème A</t>
+          <t>3ème B</t>
         </is>
       </c>
       <c r="C51" s="16" t="inlineStr">
@@ -4495,94 +4682,99 @@
           <t>Anglais</t>
         </is>
       </c>
-      <c r="D51" s="16" t="n">
+      <c r="D51" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="E51" s="16" t="inlineStr"/>
+      <c r="E51" s="26" t="inlineStr"/>
+      <c r="F51" s="7" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="16" t="inlineStr">
         <is>
-          <t>Mme COULIBALY Awa</t>
+          <t>Mme SANGARÉ Mariam</t>
         </is>
       </c>
       <c r="B52" s="16" t="inlineStr">
         <is>
-          <t>3ème A</t>
+          <t>3ème B</t>
         </is>
       </c>
       <c r="C52" s="16" t="inlineStr">
         <is>
-          <t>Histoire-Géographie</t>
-        </is>
-      </c>
-      <c r="D52" s="16" t="n">
+          <t>Espagnol</t>
+        </is>
+      </c>
+      <c r="D52" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="E52" s="16" t="inlineStr"/>
+      <c r="E52" s="26" t="inlineStr"/>
+      <c r="F52" s="7" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="16" t="inlineStr">
         <is>
-          <t>Mme COULIBALY Awa</t>
+          <t>Mme ADJÉ Pascaline</t>
         </is>
       </c>
       <c r="B53" s="16" t="inlineStr">
         <is>
-          <t>3ème A</t>
+          <t>3ème B</t>
         </is>
       </c>
       <c r="C53" s="16" t="inlineStr">
         <is>
-          <t>EDHC</t>
-        </is>
-      </c>
-      <c r="D53" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E53" s="16" t="inlineStr"/>
+          <t>Histoire-Géographie</t>
+        </is>
+      </c>
+      <c r="D53" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E53" s="26" t="inlineStr"/>
+      <c r="F53" s="7" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="16" t="inlineStr">
         <is>
-          <t>M. N'GUESSAN Koffi</t>
+          <t>M. ZADI Gérard</t>
         </is>
       </c>
       <c r="B54" s="16" t="inlineStr">
         <is>
-          <t>3ème A</t>
+          <t>3ème B</t>
         </is>
       </c>
       <c r="C54" s="16" t="inlineStr">
         <is>
-          <t>Physique-Chimie</t>
-        </is>
-      </c>
-      <c r="D54" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="E54" s="16" t="inlineStr"/>
+          <t>SVT</t>
+        </is>
+      </c>
+      <c r="D54" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E54" s="26" t="inlineStr"/>
+      <c r="F54" s="7" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="16" t="inlineStr">
         <is>
-          <t>Mme AHOU Marie</t>
+          <t>Mme YÉBOUÉ Sylvie</t>
         </is>
       </c>
       <c r="B55" s="16" t="inlineStr">
         <is>
-          <t>3ème A</t>
+          <t>3ème B</t>
         </is>
       </c>
       <c r="C55" s="16" t="inlineStr">
         <is>
-          <t>SVT</t>
-        </is>
-      </c>
-      <c r="D55" s="16" t="n">
+          <t>Physique-Chimie</t>
+        </is>
+      </c>
+      <c r="D55" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="E55" s="16" t="inlineStr"/>
+      <c r="E55" s="26" t="inlineStr"/>
+      <c r="F55" s="7" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="16" t="inlineStr">
@@ -4592,7 +4784,7 @@
       </c>
       <c r="B56" s="16" t="inlineStr">
         <is>
-          <t>3ème A</t>
+          <t>3ème B</t>
         </is>
       </c>
       <c r="C56" s="16" t="inlineStr">
@@ -4600,246 +4792,258 @@
           <t>EPS</t>
         </is>
       </c>
-      <c r="D56" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="E56" s="16" t="inlineStr"/>
+      <c r="D56" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" s="26" t="inlineStr"/>
+      <c r="F56" s="7" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="16" t="inlineStr">
         <is>
-          <t>Mme KONAN Adjoua</t>
+          <t>M. ASSI Kouadio</t>
         </is>
       </c>
       <c r="B57" s="16" t="inlineStr">
         <is>
-          <t>3ème A</t>
+          <t>3ème B</t>
         </is>
       </c>
       <c r="C57" s="16" t="inlineStr">
         <is>
-          <t>Espagnol</t>
-        </is>
-      </c>
-      <c r="D57" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="E57" s="16" t="inlineStr"/>
+          <t>EDHC</t>
+        </is>
+      </c>
+      <c r="D57" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" s="26" t="inlineStr"/>
+      <c r="F57" s="7" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="16" t="inlineStr">
         <is>
-          <t>Mme YAO Ahou</t>
+          <t>M. DIABATÉ Souleymane</t>
         </is>
       </c>
       <c r="B58" s="16" t="inlineStr">
         <is>
-          <t>3ème A</t>
+          <t>2nde A</t>
         </is>
       </c>
       <c r="C58" s="16" t="inlineStr">
         <is>
-          <t>Informatique</t>
-        </is>
-      </c>
-      <c r="D58" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E58" s="16" t="inlineStr"/>
+          <t>Français</t>
+        </is>
+      </c>
+      <c r="D58" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="E58" s="26" t="inlineStr"/>
+      <c r="F58" s="7" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="16" t="inlineStr">
         <is>
-          <t>M. GNAHORÉ Jacques</t>
+          <t>M. KOUASSI Yao</t>
         </is>
       </c>
       <c r="B59" s="16" t="inlineStr">
         <is>
-          <t>3ème A</t>
+          <t>2nde A</t>
         </is>
       </c>
       <c r="C59" s="16" t="inlineStr">
         <is>
-          <t>Musique</t>
-        </is>
-      </c>
-      <c r="D59" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E59" s="16" t="inlineStr"/>
+          <t>Mathématiques</t>
+        </is>
+      </c>
+      <c r="D59" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="E59" s="26" t="inlineStr"/>
+      <c r="F59" s="7" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="16" t="inlineStr">
         <is>
-          <t>M. GNAHORÉ Jacques</t>
+          <t>Mme KONAN Adjoua</t>
         </is>
       </c>
       <c r="B60" s="16" t="inlineStr">
         <is>
-          <t>3ème A</t>
+          <t>2nde A</t>
         </is>
       </c>
       <c r="C60" s="16" t="inlineStr">
         <is>
-          <t>Arts plastiques</t>
-        </is>
-      </c>
-      <c r="D60" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E60" s="16" t="inlineStr"/>
+          <t>Anglais</t>
+        </is>
+      </c>
+      <c r="D60" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E60" s="26" t="inlineStr"/>
+      <c r="F60" s="7" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="16" t="inlineStr">
         <is>
-          <t>Mme BAMBA Fatou</t>
+          <t>M. TRA Bi Zéphirin</t>
         </is>
       </c>
       <c r="B61" s="16" t="inlineStr">
         <is>
-          <t>2nde C</t>
+          <t>2nde A</t>
         </is>
       </c>
       <c r="C61" s="16" t="inlineStr">
         <is>
-          <t>Mathématiques</t>
-        </is>
-      </c>
-      <c r="D61" s="16" t="n">
-        <v>6</v>
-      </c>
-      <c r="E61" s="16" t="inlineStr"/>
+          <t>Espagnol</t>
+        </is>
+      </c>
+      <c r="D61" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="E61" s="26" t="inlineStr"/>
+      <c r="F61" s="7" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="16" t="inlineStr">
         <is>
-          <t>Mme TOURÉ Aminata</t>
+          <t>Mme COULIBALY Awa</t>
         </is>
       </c>
       <c r="B62" s="16" t="inlineStr">
         <is>
-          <t>2nde C</t>
+          <t>2nde A</t>
         </is>
       </c>
       <c r="C62" s="16" t="inlineStr">
         <is>
-          <t>Français</t>
-        </is>
-      </c>
-      <c r="D62" s="16" t="n">
+          <t>Histoire-Géographie</t>
+        </is>
+      </c>
+      <c r="D62" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="E62" s="16" t="inlineStr"/>
+      <c r="E62" s="26" t="inlineStr"/>
+      <c r="F62" s="7" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="16" t="inlineStr">
         <is>
-          <t>M. ADOU Michel</t>
+          <t>Mme AHOU Marie</t>
         </is>
       </c>
       <c r="B63" s="16" t="inlineStr">
         <is>
-          <t>2nde C</t>
+          <t>2nde A</t>
         </is>
       </c>
       <c r="C63" s="16" t="inlineStr">
         <is>
-          <t>Anglais</t>
-        </is>
-      </c>
-      <c r="D63" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="E63" s="16" t="inlineStr"/>
+          <t>SVT</t>
+        </is>
+      </c>
+      <c r="D63" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E63" s="26" t="inlineStr"/>
+      <c r="F63" s="7" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="16" t="inlineStr">
         <is>
-          <t>M. ASSI Kouadio</t>
+          <t>M. N'GUESSAN Koffi</t>
         </is>
       </c>
       <c r="B64" s="16" t="inlineStr">
         <is>
-          <t>2nde C</t>
+          <t>2nde A</t>
         </is>
       </c>
       <c r="C64" s="16" t="inlineStr">
         <is>
-          <t>Histoire-Géographie</t>
-        </is>
-      </c>
-      <c r="D64" s="16" t="n">
+          <t>Physique-Chimie</t>
+        </is>
+      </c>
+      <c r="D64" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="E64" s="16" t="inlineStr"/>
+      <c r="E64" s="26" t="inlineStr"/>
+      <c r="F64" s="7" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="16" t="inlineStr">
         <is>
-          <t>M. N'GUESSAN Koffi</t>
+          <t>M. OUATTARA Seydou</t>
         </is>
       </c>
       <c r="B65" s="16" t="inlineStr">
         <is>
-          <t>2nde C</t>
+          <t>2nde A</t>
         </is>
       </c>
       <c r="C65" s="16" t="inlineStr">
         <is>
-          <t>Physique-Chimie</t>
-        </is>
-      </c>
-      <c r="D65" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="E65" s="16" t="inlineStr"/>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="D65" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E65" s="26" t="inlineStr"/>
+      <c r="F65" s="7" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="16" t="inlineStr">
         <is>
-          <t>Mme AHOU Marie</t>
+          <t>M. BROU Aristide</t>
         </is>
       </c>
       <c r="B66" s="16" t="inlineStr">
         <is>
-          <t>2nde C</t>
+          <t>2nde A</t>
         </is>
       </c>
       <c r="C66" s="16" t="inlineStr">
         <is>
-          <t>SVT</t>
-        </is>
-      </c>
-      <c r="D66" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="E66" s="16" t="inlineStr"/>
+          <t>Philosophie</t>
+        </is>
+      </c>
+      <c r="D66" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E66" s="26" t="inlineStr"/>
+      <c r="F66" s="7" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="16" t="inlineStr">
         <is>
-          <t>M. OUATTARA Seydou</t>
+          <t>Mme ADJÉ Pascaline</t>
         </is>
       </c>
       <c r="B67" s="16" t="inlineStr">
         <is>
-          <t>2nde C</t>
+          <t>2nde A</t>
         </is>
       </c>
       <c r="C67" s="16" t="inlineStr">
         <is>
-          <t>EPS</t>
-        </is>
-      </c>
-      <c r="D67" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="E67" s="16" t="inlineStr"/>
+          <t>EDHC</t>
+        </is>
+      </c>
+      <c r="D67" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E67" s="26" t="inlineStr"/>
+      <c r="F67" s="7" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="16" t="inlineStr">
         <is>
-          <t>Mme KONAN Adjoua</t>
+          <t>M. KONÉ Mamadou</t>
         </is>
       </c>
       <c r="B68" s="16" t="inlineStr">
@@ -4849,18 +5053,19 @@
       </c>
       <c r="C68" s="16" t="inlineStr">
         <is>
-          <t>Espagnol</t>
-        </is>
-      </c>
-      <c r="D68" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="E68" s="16" t="inlineStr"/>
+          <t>Français</t>
+        </is>
+      </c>
+      <c r="D68" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E68" s="26" t="inlineStr"/>
+      <c r="F68" s="7" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="16" t="inlineStr">
         <is>
-          <t>M. TRA Bi Zéphirin</t>
+          <t>Mme BAMBA Fatou</t>
         </is>
       </c>
       <c r="B69" s="16" t="inlineStr">
@@ -4870,18 +5075,19 @@
       </c>
       <c r="C69" s="16" t="inlineStr">
         <is>
-          <t>Philosophie</t>
-        </is>
-      </c>
-      <c r="D69" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="E69" s="16" t="inlineStr"/>
+          <t>Mathématiques</t>
+        </is>
+      </c>
+      <c r="D69" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="E69" s="26" t="inlineStr"/>
+      <c r="F69" s="7" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="16" t="inlineStr">
         <is>
-          <t>Mme YAO Ahou</t>
+          <t>M. DIALLO Ibrahim</t>
         </is>
       </c>
       <c r="B70" s="16" t="inlineStr">
@@ -4891,144 +5097,151 @@
       </c>
       <c r="C70" s="16" t="inlineStr">
         <is>
-          <t>Informatique</t>
-        </is>
-      </c>
-      <c r="D70" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E70" s="16" t="inlineStr"/>
+          <t>Anglais</t>
+        </is>
+      </c>
+      <c r="D70" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="E70" s="26" t="inlineStr"/>
+      <c r="F70" s="7" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="16" t="inlineStr">
         <is>
-          <t>M. KOUASSI Yao</t>
+          <t>Mme SANGARÉ Mariam</t>
         </is>
       </c>
       <c r="B71" s="16" t="inlineStr">
         <is>
-          <t>1ère D</t>
+          <t>2nde C</t>
         </is>
       </c>
       <c r="C71" s="16" t="inlineStr">
         <is>
-          <t>Mathématiques</t>
-        </is>
-      </c>
-      <c r="D71" s="16" t="n">
-        <v>6</v>
-      </c>
-      <c r="E71" s="16" t="inlineStr"/>
+          <t>Espagnol</t>
+        </is>
+      </c>
+      <c r="D71" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="E71" s="26" t="inlineStr"/>
+      <c r="F71" s="7" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="16" t="inlineStr">
         <is>
-          <t>M. KONÉ Mamadou</t>
+          <t>M. ASSI Kouadio</t>
         </is>
       </c>
       <c r="B72" s="16" t="inlineStr">
         <is>
-          <t>1ère D</t>
+          <t>2nde C</t>
         </is>
       </c>
       <c r="C72" s="16" t="inlineStr">
         <is>
-          <t>Français</t>
-        </is>
-      </c>
-      <c r="D72" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="E72" s="16" t="inlineStr"/>
+          <t>Histoire-Géographie</t>
+        </is>
+      </c>
+      <c r="D72" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="E72" s="26" t="inlineStr"/>
+      <c r="F72" s="7" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="16" t="inlineStr">
         <is>
-          <t>M. ADOU Michel</t>
+          <t>M. ZADI Gérard</t>
         </is>
       </c>
       <c r="B73" s="16" t="inlineStr">
         <is>
-          <t>1ère D</t>
+          <t>2nde C</t>
         </is>
       </c>
       <c r="C73" s="16" t="inlineStr">
         <is>
-          <t>Anglais</t>
-        </is>
-      </c>
-      <c r="D73" s="16" t="n">
+          <t>SVT</t>
+        </is>
+      </c>
+      <c r="D73" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="E73" s="16" t="inlineStr"/>
+      <c r="E73" s="26" t="inlineStr"/>
+      <c r="F73" s="7" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="16" t="inlineStr">
         <is>
-          <t>Mme COULIBALY Awa</t>
+          <t>Mme YÉBOUÉ Sylvie</t>
         </is>
       </c>
       <c r="B74" s="16" t="inlineStr">
         <is>
-          <t>1ère D</t>
+          <t>2nde C</t>
         </is>
       </c>
       <c r="C74" s="16" t="inlineStr">
         <is>
-          <t>Histoire-Géographie</t>
-        </is>
-      </c>
-      <c r="D74" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="E74" s="16" t="inlineStr"/>
+          <t>Physique-Chimie</t>
+        </is>
+      </c>
+      <c r="D74" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E74" s="26" t="inlineStr"/>
+      <c r="F74" s="7" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="16" t="inlineStr">
         <is>
-          <t>M. N'GUESSAN Koffi</t>
+          <t>M. OUATTARA Seydou</t>
         </is>
       </c>
       <c r="B75" s="16" t="inlineStr">
         <is>
-          <t>1ère D</t>
+          <t>2nde C</t>
         </is>
       </c>
       <c r="C75" s="16" t="inlineStr">
         <is>
-          <t>Physique-Chimie</t>
-        </is>
-      </c>
-      <c r="D75" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="E75" s="16" t="inlineStr"/>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="D75" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E75" s="26" t="inlineStr"/>
+      <c r="F75" s="7" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="16" t="inlineStr">
         <is>
-          <t>Mme AHOU Marie</t>
+          <t>Mme COULIBALY Awa</t>
         </is>
       </c>
       <c r="B76" s="16" t="inlineStr">
         <is>
-          <t>1ère D</t>
+          <t>2nde C</t>
         </is>
       </c>
       <c r="C76" s="16" t="inlineStr">
         <is>
-          <t>SVT</t>
-        </is>
-      </c>
-      <c r="D76" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="E76" s="16" t="inlineStr"/>
+          <t>EDHC</t>
+        </is>
+      </c>
+      <c r="D76" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E76" s="26" t="inlineStr"/>
+      <c r="F76" s="7" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="16" t="inlineStr">
         <is>
-          <t>M. OUATTARA Seydou</t>
+          <t>Mme TOURÉ Aminata</t>
         </is>
       </c>
       <c r="B77" s="16" t="inlineStr">
@@ -5038,18 +5251,19 @@
       </c>
       <c r="C77" s="16" t="inlineStr">
         <is>
-          <t>EPS</t>
-        </is>
-      </c>
-      <c r="D77" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="E77" s="16" t="inlineStr"/>
+          <t>Français</t>
+        </is>
+      </c>
+      <c r="D77" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E77" s="26" t="inlineStr"/>
+      <c r="F77" s="7" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="16" t="inlineStr">
         <is>
-          <t>Mme KONAN Adjoua</t>
+          <t>M. KOUADIO Léon</t>
         </is>
       </c>
       <c r="B78" s="16" t="inlineStr">
@@ -5059,18 +5273,19 @@
       </c>
       <c r="C78" s="16" t="inlineStr">
         <is>
-          <t>Espagnol</t>
-        </is>
-      </c>
-      <c r="D78" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="E78" s="16" t="inlineStr"/>
+          <t>Mathématiques</t>
+        </is>
+      </c>
+      <c r="D78" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="E78" s="26" t="inlineStr"/>
+      <c r="F78" s="7" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="16" t="inlineStr">
         <is>
-          <t>M. TRA Bi Zéphirin</t>
+          <t>M. DIALLO Ibrahim</t>
         </is>
       </c>
       <c r="B79" s="16" t="inlineStr">
@@ -5080,169 +5295,173 @@
       </c>
       <c r="C79" s="16" t="inlineStr">
         <is>
-          <t>Philosophie</t>
-        </is>
-      </c>
-      <c r="D79" s="16" t="n">
+          <t>Anglais</t>
+        </is>
+      </c>
+      <c r="D79" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="E79" s="16" t="inlineStr"/>
+      <c r="E79" s="26" t="inlineStr"/>
+      <c r="F79" s="7" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="16" t="inlineStr">
         <is>
-          <t>Mme BAMBA Fatou</t>
+          <t>M. TRA Bi Zéphirin</t>
         </is>
       </c>
       <c r="B80" s="16" t="inlineStr">
         <is>
-          <t>Tle D</t>
+          <t>1ère D</t>
         </is>
       </c>
       <c r="C80" s="16" t="inlineStr">
         <is>
-          <t>Mathématiques</t>
-        </is>
-      </c>
-      <c r="D80" s="16" t="n">
-        <v>6</v>
-      </c>
-      <c r="E80" s="16" t="inlineStr"/>
+          <t>Espagnol</t>
+        </is>
+      </c>
+      <c r="D80" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E80" s="26" t="inlineStr"/>
+      <c r="F80" s="7" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="16" t="inlineStr">
         <is>
-          <t>Mme TOURÉ Aminata</t>
+          <t>Mme ADJÉ Pascaline</t>
         </is>
       </c>
       <c r="B81" s="16" t="inlineStr">
         <is>
-          <t>Tle D</t>
+          <t>1ère D</t>
         </is>
       </c>
       <c r="C81" s="16" t="inlineStr">
         <is>
-          <t>Français</t>
-        </is>
-      </c>
-      <c r="D81" s="16" t="n">
+          <t>Histoire-Géographie</t>
+        </is>
+      </c>
+      <c r="D81" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="E81" s="16" t="inlineStr"/>
+      <c r="E81" s="26" t="inlineStr"/>
+      <c r="F81" s="7" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="16" t="inlineStr">
         <is>
-          <t>M. DIALLO Ibrahim</t>
+          <t>Mme AHOU Marie</t>
         </is>
       </c>
       <c r="B82" s="16" t="inlineStr">
         <is>
-          <t>Tle D</t>
+          <t>1ère D</t>
         </is>
       </c>
       <c r="C82" s="16" t="inlineStr">
         <is>
-          <t>Anglais</t>
-        </is>
-      </c>
-      <c r="D82" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="E82" s="16" t="inlineStr"/>
+          <t>SVT</t>
+        </is>
+      </c>
+      <c r="D82" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E82" s="26" t="inlineStr"/>
+      <c r="F82" s="7" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="16" t="inlineStr">
         <is>
-          <t>M. ASSI Kouadio</t>
+          <t>M. N'GUESSAN Koffi</t>
         </is>
       </c>
       <c r="B83" s="16" t="inlineStr">
         <is>
-          <t>Tle D</t>
+          <t>1ère D</t>
         </is>
       </c>
       <c r="C83" s="16" t="inlineStr">
         <is>
-          <t>Histoire-Géographie</t>
-        </is>
-      </c>
-      <c r="D83" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="E83" s="16" t="inlineStr"/>
+          <t>Physique-Chimie</t>
+        </is>
+      </c>
+      <c r="D83" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E83" s="26" t="inlineStr"/>
+      <c r="F83" s="7" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="16" t="inlineStr">
         <is>
-          <t>M. N'GUESSAN Koffi</t>
+          <t>M. OUATTARA Seydou</t>
         </is>
       </c>
       <c r="B84" s="16" t="inlineStr">
         <is>
-          <t>Tle D</t>
+          <t>1ère D</t>
         </is>
       </c>
       <c r="C84" s="16" t="inlineStr">
         <is>
-          <t>Physique-Chimie</t>
-        </is>
-      </c>
-      <c r="D84" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="E84" s="16" t="inlineStr"/>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="D84" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E84" s="26" t="inlineStr"/>
+      <c r="F84" s="7" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="16" t="inlineStr">
         <is>
-          <t>Mme AHOU Marie</t>
+          <t>M. BROU Aristide</t>
         </is>
       </c>
       <c r="B85" s="16" t="inlineStr">
         <is>
-          <t>Tle D</t>
+          <t>1ère D</t>
         </is>
       </c>
       <c r="C85" s="16" t="inlineStr">
         <is>
-          <t>SVT</t>
-        </is>
-      </c>
-      <c r="D85" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="E85" s="16" t="inlineStr">
-        <is>
-          <t>Mardi</t>
-        </is>
-      </c>
+          <t>Philosophie</t>
+        </is>
+      </c>
+      <c r="D85" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E85" s="26" t="inlineStr"/>
+      <c r="F85" s="7" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="16" t="inlineStr">
         <is>
-          <t>M. OUATTARA Seydou</t>
+          <t>M. ASSI Kouadio</t>
         </is>
       </c>
       <c r="B86" s="16" t="inlineStr">
         <is>
-          <t>Tle D</t>
+          <t>1ère D</t>
         </is>
       </c>
       <c r="C86" s="16" t="inlineStr">
         <is>
-          <t>EPS</t>
-        </is>
-      </c>
-      <c r="D86" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="E86" s="16" t="inlineStr"/>
+          <t>EDHC</t>
+        </is>
+      </c>
+      <c r="D86" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E86" s="26" t="inlineStr"/>
+      <c r="F86" s="7" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="16" t="inlineStr">
         <is>
-          <t>Mme KONAN Adjoua</t>
+          <t>M. KOUASSI Yao</t>
         </is>
       </c>
       <c r="B87" s="16" t="inlineStr">
@@ -5252,18 +5471,19 @@
       </c>
       <c r="C87" s="16" t="inlineStr">
         <is>
-          <t>Espagnol</t>
-        </is>
-      </c>
-      <c r="D87" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="E87" s="16" t="inlineStr"/>
+          <t>Mathématiques</t>
+        </is>
+      </c>
+      <c r="D87" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="E87" s="26" t="inlineStr"/>
+      <c r="F87" s="7" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="16" t="inlineStr">
         <is>
-          <t>M. TRA Bi Zéphirin</t>
+          <t>Mme KONAN Adjoua</t>
         </is>
       </c>
       <c r="B88" s="16" t="inlineStr">
@@ -5273,62 +5493,168 @@
       </c>
       <c r="C88" s="16" t="inlineStr">
         <is>
+          <t>Anglais</t>
+        </is>
+      </c>
+      <c r="D88" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="E88" s="26" t="inlineStr"/>
+      <c r="F88" s="7" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="7" t="inlineStr">
+        <is>
+          <t>Mme SANGARÉ Mariam</t>
+        </is>
+      </c>
+      <c r="B89" s="7" t="inlineStr">
+        <is>
+          <t>Tle D</t>
+        </is>
+      </c>
+      <c r="C89" s="7" t="inlineStr">
+        <is>
+          <t>Espagnol</t>
+        </is>
+      </c>
+      <c r="D89" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E89" s="27" t="inlineStr"/>
+      <c r="F89" s="7" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="7" t="inlineStr">
+        <is>
+          <t>Mme COULIBALY Awa</t>
+        </is>
+      </c>
+      <c r="B90" s="7" t="inlineStr">
+        <is>
+          <t>Tle D</t>
+        </is>
+      </c>
+      <c r="C90" s="7" t="inlineStr">
+        <is>
+          <t>Histoire-Géographie</t>
+        </is>
+      </c>
+      <c r="D90" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E90" s="27" t="inlineStr"/>
+      <c r="F90" s="7" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="7" t="inlineStr">
+        <is>
+          <t>M. ZADI Gérard</t>
+        </is>
+      </c>
+      <c r="B91" s="7" t="inlineStr">
+        <is>
+          <t>Tle D</t>
+        </is>
+      </c>
+      <c r="C91" s="7" t="inlineStr">
+        <is>
+          <t>SVT</t>
+        </is>
+      </c>
+      <c r="D91" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="E91" s="27" t="inlineStr"/>
+      <c r="F91" s="7" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="7" t="inlineStr">
+        <is>
+          <t>Mme YÉBOUÉ Sylvie</t>
+        </is>
+      </c>
+      <c r="B92" s="7" t="inlineStr">
+        <is>
+          <t>Tle D</t>
+        </is>
+      </c>
+      <c r="C92" s="7" t="inlineStr">
+        <is>
+          <t>Physique-Chimie</t>
+        </is>
+      </c>
+      <c r="D92" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="E92" s="27" t="inlineStr"/>
+      <c r="F92" s="7" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="7" t="inlineStr">
+        <is>
+          <t>M. OUATTARA Seydou</t>
+        </is>
+      </c>
+      <c r="B93" s="7" t="inlineStr">
+        <is>
+          <t>Tle D</t>
+        </is>
+      </c>
+      <c r="C93" s="7" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="D93" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E93" s="27" t="inlineStr"/>
+      <c r="F93" s="7" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="7" t="inlineStr">
+        <is>
+          <t>M. BROU Aristide</t>
+        </is>
+      </c>
+      <c r="B94" s="7" t="inlineStr">
+        <is>
+          <t>Tle D</t>
+        </is>
+      </c>
+      <c r="C94" s="7" t="inlineStr">
+        <is>
           <t>Philosophie</t>
         </is>
       </c>
-      <c r="D88" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="E88" s="16" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="7" t="n"/>
-      <c r="B89" s="7" t="n"/>
-      <c r="C89" s="7" t="n"/>
-      <c r="D89" s="7" t="n"/>
-      <c r="E89" s="7" t="n"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="7" t="n"/>
-      <c r="B90" s="7" t="n"/>
-      <c r="C90" s="7" t="n"/>
-      <c r="D90" s="7" t="n"/>
-      <c r="E90" s="7" t="n"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="7" t="n"/>
-      <c r="B91" s="7" t="n"/>
-      <c r="C91" s="7" t="n"/>
-      <c r="D91" s="7" t="n"/>
-      <c r="E91" s="7" t="n"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="7" t="n"/>
-      <c r="B92" s="7" t="n"/>
-      <c r="C92" s="7" t="n"/>
-      <c r="D92" s="7" t="n"/>
-      <c r="E92" s="7" t="n"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="7" t="n"/>
-      <c r="B93" s="7" t="n"/>
-      <c r="C93" s="7" t="n"/>
-      <c r="D93" s="7" t="n"/>
-      <c r="E93" s="7" t="n"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="7" t="n"/>
-      <c r="B94" s="7" t="n"/>
-      <c r="C94" s="7" t="n"/>
-      <c r="D94" s="7" t="n"/>
-      <c r="E94" s="7" t="n"/>
+      <c r="D94" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="E94" s="27" t="inlineStr"/>
+      <c r="F94" s="7" t="n"/>
     </row>
     <row r="95">
-      <c r="A95" s="7" t="n"/>
-      <c r="B95" s="7" t="n"/>
-      <c r="C95" s="7" t="n"/>
-      <c r="D95" s="7" t="n"/>
-      <c r="E95" s="7" t="n"/>
+      <c r="A95" s="7" t="inlineStr">
+        <is>
+          <t>Mme ADJÉ Pascaline</t>
+        </is>
+      </c>
+      <c r="B95" s="7" t="inlineStr">
+        <is>
+          <t>Tle D</t>
+        </is>
+      </c>
+      <c r="C95" s="7" t="inlineStr">
+        <is>
+          <t>EDHC</t>
+        </is>
+      </c>
+      <c r="D95" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E95" s="27" t="inlineStr"/>
+      <c r="F95" s="7" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="7" t="n"/>
@@ -7488,7 +7814,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L120"/>
+  <dimension ref="A1:M120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -7588,57 +7914,57 @@
           <t>M. DIALLO Ibrahim</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="26" t="inlineStr">
         <is>
           <t>OUI</t>
         </is>
       </c>
-      <c r="C4" s="16" t="inlineStr">
+      <c r="C4" s="26" t="inlineStr">
         <is>
           <t>OUI</t>
         </is>
       </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="D4" s="26" t="inlineStr">
         <is>
           <t>OUI</t>
         </is>
       </c>
-      <c r="E4" s="16" t="inlineStr">
+      <c r="E4" s="26" t="inlineStr">
         <is>
           <t>OUI</t>
         </is>
       </c>
-      <c r="F4" s="16" t="inlineStr">
+      <c r="F4" s="26" t="inlineStr">
         <is>
           <t>NON</t>
         </is>
       </c>
-      <c r="G4" s="16" t="inlineStr">
+      <c r="G4" s="26" t="inlineStr">
         <is>
           <t>NON</t>
         </is>
       </c>
-      <c r="H4" s="16" t="inlineStr">
+      <c r="H4" s="26" t="inlineStr">
         <is>
           <t>OUI</t>
         </is>
       </c>
-      <c r="I4" s="16" t="inlineStr">
+      <c r="I4" s="26" t="inlineStr">
         <is>
           <t>OUI</t>
         </is>
       </c>
-      <c r="J4" s="16" t="inlineStr">
+      <c r="J4" s="26" t="inlineStr">
         <is>
           <t>OUI</t>
         </is>
       </c>
-      <c r="K4" s="16" t="inlineStr">
+      <c r="K4" s="26" t="inlineStr">
         <is>
           <t>NON</t>
         </is>
       </c>
-      <c r="L4" s="16" t="inlineStr">
+      <c r="L4" s="26" t="inlineStr">
         <is>
           <t>NON</t>
         </is>
@@ -7647,60 +7973,60 @@
     <row r="5">
       <c r="A5" s="16" t="inlineStr">
         <is>
-          <t>Mme KONAN Adjoua</t>
-        </is>
-      </c>
-      <c r="B5" s="16" t="inlineStr">
+          <t>M. TRA Bi Zéphirin</t>
+        </is>
+      </c>
+      <c r="B5" s="26" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="C5" s="26" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="D5" s="26" t="inlineStr">
         <is>
           <t>OUI</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="E5" s="26" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="F5" s="26" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="G5" s="26" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="H5" s="26" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="I5" s="26" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="J5" s="26" t="inlineStr">
         <is>
           <t>NON</t>
         </is>
       </c>
-      <c r="D5" s="16" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
-      <c r="E5" s="16" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
-      <c r="F5" s="16" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
-      <c r="G5" s="16" t="inlineStr">
+      <c r="K5" s="26" t="inlineStr">
         <is>
           <t>NON</t>
         </is>
       </c>
-      <c r="H5" s="16" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
-      <c r="I5" s="16" t="inlineStr">
-        <is>
-          <t>NON</t>
-        </is>
-      </c>
-      <c r="J5" s="16" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
-      <c r="K5" s="16" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
-      <c r="L5" s="16" t="inlineStr">
+      <c r="L5" s="26" t="inlineStr">
         <is>
           <t>NON</t>
         </is>
@@ -7709,60 +8035,60 @@
     <row r="6">
       <c r="A6" s="16" t="inlineStr">
         <is>
-          <t>M. TRA Bi Zéphirin</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
+          <t>M. GNAHORÉ Jacques</t>
+        </is>
+      </c>
+      <c r="B6" s="26" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="C6" s="26" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="D6" s="26" t="inlineStr">
         <is>
           <t>NON</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="E6" s="26" t="inlineStr">
         <is>
           <t>NON</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="F6" s="26" t="inlineStr">
         <is>
           <t>OUI</t>
         </is>
       </c>
-      <c r="E6" s="16" t="inlineStr">
+      <c r="G6" s="26" t="inlineStr">
         <is>
           <t>OUI</t>
         </is>
       </c>
-      <c r="F6" s="16" t="inlineStr">
+      <c r="H6" s="26" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="I6" s="26" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="J6" s="26" t="inlineStr">
         <is>
           <t>OUI</t>
         </is>
       </c>
-      <c r="G6" s="16" t="inlineStr">
+      <c r="K6" s="26" t="inlineStr">
         <is>
           <t>OUI</t>
         </is>
       </c>
-      <c r="H6" s="16" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
-      <c r="I6" s="16" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
-      <c r="J6" s="16" t="inlineStr">
-        <is>
-          <t>NON</t>
-        </is>
-      </c>
-      <c r="K6" s="16" t="inlineStr">
-        <is>
-          <t>NON</t>
-        </is>
-      </c>
-      <c r="L6" s="16" t="inlineStr">
+      <c r="L6" s="26" t="inlineStr">
         <is>
           <t>NON</t>
         </is>
@@ -7771,126 +8097,78 @@
     <row r="7">
       <c r="A7" s="16" t="inlineStr">
         <is>
-          <t>Mme YAO Ahou</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
+          <t>M. BROU Aristide</t>
+        </is>
+      </c>
+      <c r="B7" s="26" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="C7" s="26" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="D7" s="26" t="inlineStr">
         <is>
           <t>OUI</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="E7" s="26" t="inlineStr">
         <is>
           <t>OUI</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="F7" s="26" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="G7" s="26" t="inlineStr">
         <is>
           <t>NON</t>
         </is>
       </c>
-      <c r="E7" s="16" t="inlineStr">
+      <c r="H7" s="26" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="I7" s="26" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="J7" s="26" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="K7" s="26" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="L7" s="26" t="inlineStr">
         <is>
           <t>NON</t>
         </is>
       </c>
-      <c r="F7" s="16" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
-      <c r="G7" s="16" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
-      <c r="H7" s="16" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
-      <c r="I7" s="16" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
-      <c r="J7" s="16" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
-      <c r="K7" s="16" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
-      <c r="L7" s="16" t="inlineStr">
-        <is>
-          <t>NON</t>
-        </is>
-      </c>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="inlineStr">
-        <is>
-          <t>M. GNAHORÉ Jacques</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
-      <c r="F8" s="16" t="inlineStr">
-        <is>
-          <t>NON</t>
-        </is>
-      </c>
-      <c r="G8" s="16" t="inlineStr">
-        <is>
-          <t>NON</t>
-        </is>
-      </c>
-      <c r="H8" s="16" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
-      <c r="I8" s="16" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
-      <c r="J8" s="16" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
-      <c r="K8" s="16" t="inlineStr">
-        <is>
-          <t>NON</t>
-        </is>
-      </c>
-      <c r="L8" s="16" t="inlineStr">
-        <is>
-          <t>NON</t>
-        </is>
-      </c>
+      <c r="A8" s="16" t="n"/>
+      <c r="B8" s="16" t="n"/>
+      <c r="C8" s="16" t="n"/>
+      <c r="D8" s="16" t="n"/>
+      <c r="E8" s="16" t="n"/>
+      <c r="F8" s="16" t="n"/>
+      <c r="G8" s="16" t="n"/>
+      <c r="H8" s="16" t="n"/>
+      <c r="I8" s="16" t="n"/>
+      <c r="J8" s="16" t="n"/>
+      <c r="K8" s="16" t="n"/>
+      <c r="L8" s="16" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n"/>
@@ -9606,7 +9884,7 @@
     <row r="9">
       <c r="A9" s="17" t="inlineStr">
         <is>
-          <t>Les classes d'examen (3ème A et Tle D) ne doivent pas finir après 16h30</t>
+          <t>Les classes d'examen (3ème A, 3ème B et Tle D) ne doivent pas finir après 16h30</t>
         </is>
       </c>
       <c r="B9" s="16" t="inlineStr">

--- a/donnees_exemple.xlsx
+++ b/donnees_exemple.xlsx
@@ -2179,7 +2179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F120"/>
+  <dimension ref="A1:I120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2276,7 +2276,7 @@
       <c r="C5" s="16" t="inlineStr"/>
       <c r="D5" s="26" t="inlineStr">
         <is>
-          <t>Permanent</t>
+          <t>Vacataire</t>
         </is>
       </c>
       <c r="E5" s="26" t="n">
@@ -2328,7 +2328,7 @@
       <c r="C7" s="16" t="inlineStr"/>
       <c r="D7" s="26" t="inlineStr">
         <is>
-          <t>Permanent</t>
+          <t>Vacataire</t>
         </is>
       </c>
       <c r="E7" s="26" t="n">
@@ -2354,7 +2354,7 @@
       <c r="C8" s="16" t="inlineStr"/>
       <c r="D8" s="26" t="inlineStr">
         <is>
-          <t>Permanent</t>
+          <t>Vacataire</t>
         </is>
       </c>
       <c r="E8" s="26" t="n">
@@ -2406,7 +2406,7 @@
       <c r="C10" s="16" t="inlineStr"/>
       <c r="D10" s="26" t="inlineStr">
         <is>
-          <t>Permanent</t>
+          <t>Vacataire</t>
         </is>
       </c>
       <c r="E10" s="26" t="n">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="D12" s="26" t="inlineStr">
         <is>
-          <t>Permanent</t>
+          <t>Vacataire</t>
         </is>
       </c>
       <c r="E12" s="26" t="n">
@@ -2492,7 +2492,7 @@
       <c r="C13" s="16" t="inlineStr"/>
       <c r="D13" s="26" t="inlineStr">
         <is>
-          <t>Permanent</t>
+          <t>Vacataire</t>
         </is>
       </c>
       <c r="E13" s="26" t="n">
@@ -2570,7 +2570,7 @@
       <c r="C16" s="16" t="inlineStr"/>
       <c r="D16" s="26" t="inlineStr">
         <is>
-          <t>Permanent</t>
+          <t>Vacataire</t>
         </is>
       </c>
       <c r="E16" s="26" t="n">
@@ -2730,7 +2730,7 @@
       <c r="C22" s="7" t="inlineStr"/>
       <c r="D22" s="27" t="inlineStr">
         <is>
-          <t>Permanent</t>
+          <t>Vacataire</t>
         </is>
       </c>
       <c r="E22" s="27" t="n">
@@ -2760,7 +2760,7 @@
       </c>
       <c r="D23" s="27" t="inlineStr">
         <is>
-          <t>Permanent</t>
+          <t>Vacataire</t>
         </is>
       </c>
       <c r="E23" s="27" t="n">
@@ -8157,130 +8157,562 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="n"/>
-      <c r="B8" s="16" t="n"/>
-      <c r="C8" s="16" t="n"/>
-      <c r="D8" s="16" t="n"/>
-      <c r="E8" s="16" t="n"/>
-      <c r="F8" s="16" t="n"/>
-      <c r="G8" s="16" t="n"/>
-      <c r="H8" s="16" t="n"/>
-      <c r="I8" s="16" t="n"/>
-      <c r="J8" s="16" t="n"/>
-      <c r="K8" s="16" t="n"/>
-      <c r="L8" s="16" t="n"/>
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>Mme KONAN Adjoua</t>
+        </is>
+      </c>
+      <c r="B8" s="26" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="C8" s="26" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="D8" s="26" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="E8" s="26" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="F8" s="26" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="G8" s="26" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="H8" s="26" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="I8" s="26" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="J8" s="26" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="K8" s="26" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="L8" s="26" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="n"/>
-      <c r="B9" s="7" t="n"/>
-      <c r="C9" s="7" t="n"/>
-      <c r="D9" s="7" t="n"/>
-      <c r="E9" s="7" t="n"/>
-      <c r="F9" s="7" t="n"/>
-      <c r="G9" s="7" t="n"/>
-      <c r="H9" s="7" t="n"/>
-      <c r="I9" s="7" t="n"/>
-      <c r="J9" s="7" t="n"/>
-      <c r="K9" s="7" t="n"/>
-      <c r="L9" s="7" t="n"/>
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>Mme TOURÉ Aminata</t>
+        </is>
+      </c>
+      <c r="B9" s="26" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="C9" s="26" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="D9" s="26" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="E9" s="26" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="F9" s="26" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="G9" s="26" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="H9" s="26" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="I9" s="26" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="J9" s="26" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="K9" s="26" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="L9" s="26" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="n"/>
-      <c r="B10" s="7" t="n"/>
-      <c r="C10" s="7" t="n"/>
-      <c r="D10" s="7" t="n"/>
-      <c r="E10" s="7" t="n"/>
-      <c r="F10" s="7" t="n"/>
-      <c r="G10" s="7" t="n"/>
-      <c r="H10" s="7" t="n"/>
-      <c r="I10" s="7" t="n"/>
-      <c r="J10" s="7" t="n"/>
-      <c r="K10" s="7" t="n"/>
-      <c r="L10" s="7" t="n"/>
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>M. DIABATÉ Souleymane</t>
+        </is>
+      </c>
+      <c r="B10" s="26" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="C10" s="26" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="D10" s="26" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="E10" s="26" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="F10" s="26" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="G10" s="26" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="H10" s="26" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="I10" s="26" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="J10" s="26" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="K10" s="26" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="L10" s="26" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="n"/>
-      <c r="B11" s="7" t="n"/>
-      <c r="C11" s="7" t="n"/>
-      <c r="D11" s="7" t="n"/>
-      <c r="E11" s="7" t="n"/>
-      <c r="F11" s="7" t="n"/>
-      <c r="G11" s="7" t="n"/>
-      <c r="H11" s="7" t="n"/>
-      <c r="I11" s="7" t="n"/>
-      <c r="J11" s="7" t="n"/>
-      <c r="K11" s="7" t="n"/>
-      <c r="L11" s="7" t="n"/>
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>Mme ADJÉ Pascaline</t>
+        </is>
+      </c>
+      <c r="B11" s="26" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="D11" s="26" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="E11" s="26" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="F11" s="26" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="G11" s="26" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="H11" s="26" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="I11" s="26" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="J11" s="26" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="K11" s="26" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="L11" s="26" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="n"/>
-      <c r="B12" s="7" t="n"/>
-      <c r="C12" s="7" t="n"/>
-      <c r="D12" s="7" t="n"/>
-      <c r="E12" s="7" t="n"/>
-      <c r="F12" s="7" t="n"/>
-      <c r="G12" s="7" t="n"/>
-      <c r="H12" s="7" t="n"/>
-      <c r="I12" s="7" t="n"/>
-      <c r="J12" s="7" t="n"/>
-      <c r="K12" s="7" t="n"/>
-      <c r="L12" s="7" t="n"/>
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>M. ZADI Gérard</t>
+        </is>
+      </c>
+      <c r="B12" s="26" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="C12" s="26" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="D12" s="26" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="E12" s="26" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="F12" s="26" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="G12" s="26" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="H12" s="26" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="I12" s="26" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="J12" s="26" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="K12" s="26" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="L12" s="26" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="n"/>
-      <c r="B13" s="7" t="n"/>
-      <c r="C13" s="7" t="n"/>
-      <c r="D13" s="7" t="n"/>
-      <c r="E13" s="7" t="n"/>
-      <c r="F13" s="7" t="n"/>
-      <c r="G13" s="7" t="n"/>
-      <c r="H13" s="7" t="n"/>
-      <c r="I13" s="7" t="n"/>
-      <c r="J13" s="7" t="n"/>
-      <c r="K13" s="7" t="n"/>
-      <c r="L13" s="7" t="n"/>
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>Mme BAMBA Fatou</t>
+        </is>
+      </c>
+      <c r="B13" s="26" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="C13" s="26" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="D13" s="26" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="E13" s="26" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="F13" s="26" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="G13" s="26" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="H13" s="26" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="I13" s="26" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="J13" s="26" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="K13" s="26" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="L13" s="26" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="n"/>
-      <c r="B14" s="7" t="n"/>
-      <c r="C14" s="7" t="n"/>
-      <c r="D14" s="7" t="n"/>
-      <c r="E14" s="7" t="n"/>
-      <c r="F14" s="7" t="n"/>
-      <c r="G14" s="7" t="n"/>
-      <c r="H14" s="7" t="n"/>
-      <c r="I14" s="7" t="n"/>
-      <c r="J14" s="7" t="n"/>
-      <c r="K14" s="7" t="n"/>
-      <c r="L14" s="7" t="n"/>
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>M. ASSI Kouadio</t>
+        </is>
+      </c>
+      <c r="B14" s="26" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="C14" s="26" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="D14" s="26" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="E14" s="26" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="F14" s="26" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="G14" s="26" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="H14" s="26" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="I14" s="26" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="J14" s="26" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="K14" s="26" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="L14" s="26" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="n"/>
-      <c r="B15" s="7" t="n"/>
-      <c r="C15" s="7" t="n"/>
-      <c r="D15" s="7" t="n"/>
-      <c r="E15" s="7" t="n"/>
-      <c r="F15" s="7" t="n"/>
-      <c r="G15" s="7" t="n"/>
-      <c r="H15" s="7" t="n"/>
-      <c r="I15" s="7" t="n"/>
-      <c r="J15" s="7" t="n"/>
-      <c r="K15" s="7" t="n"/>
-      <c r="L15" s="7" t="n"/>
+      <c r="A15" s="16" t="inlineStr">
+        <is>
+          <t>M. KOUADIO Léon</t>
+        </is>
+      </c>
+      <c r="B15" s="26" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="C15" s="26" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="D15" s="26" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="E15" s="26" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="F15" s="26" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="G15" s="26" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="H15" s="26" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="I15" s="26" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="J15" s="26" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="K15" s="26" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="L15" s="26" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="n"/>
-      <c r="B16" s="7" t="n"/>
-      <c r="C16" s="7" t="n"/>
-      <c r="D16" s="7" t="n"/>
-      <c r="E16" s="7" t="n"/>
-      <c r="F16" s="7" t="n"/>
-      <c r="G16" s="7" t="n"/>
-      <c r="H16" s="7" t="n"/>
-      <c r="I16" s="7" t="n"/>
-      <c r="J16" s="7" t="n"/>
-      <c r="K16" s="7" t="n"/>
-      <c r="L16" s="7" t="n"/>
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>M. N'GUESSAN Koffi</t>
+        </is>
+      </c>
+      <c r="B16" s="26" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="C16" s="26" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="D16" s="26" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="E16" s="26" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="F16" s="26" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="G16" s="26" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="H16" s="26" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="I16" s="26" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="J16" s="26" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="K16" s="26" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
+      <c r="L16" s="26" t="inlineStr">
+        <is>
+          <t>NON</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n"/>
